--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q383"/>
+  <dimension ref="A1:Q396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="b">
+      <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -575,7 +575,7 @@
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="b">
+      <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -620,7 +620,7 @@
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" t="b">
+      <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -669,7 +669,7 @@
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
-      <c r="C5" t="b">
+      <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
-      <c r="C6" t="b">
+      <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="b">
+      <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
-      <c r="C8" t="b">
+      <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" t="b">
+      <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -946,7 +946,7 @@
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" t="b">
+      <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -1011,7 +1011,7 @@
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
-      <c r="C11" t="b">
+      <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
-      <c r="C12" t="b">
+      <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
-      <c r="C13" t="b">
+      <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -1186,7 +1186,7 @@
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
-      <c r="C14" t="b">
+      <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -1235,7 +1235,7 @@
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
-      <c r="C15" t="b">
+      <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
-      <c r="C16" t="b">
+      <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -1333,7 +1333,7 @@
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
-      <c r="C17" t="b">
+      <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -1398,7 +1398,7 @@
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
-      <c r="C18" t="b">
+      <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
-      <c r="C19" t="b">
+      <c r="C19" t="n">
         <v>0</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="b">
+      <c r="C20" t="n">
         <v>0</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -1581,7 +1581,7 @@
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
-      <c r="C21" t="b">
+      <c r="C21" t="n">
         <v>0</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
-      <c r="C22" t="b">
+      <c r="C22" t="n">
         <v>0</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
-      <c r="C23" t="b">
+      <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
-      <c r="C24" t="b">
+      <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
-      <c r="C25" t="b">
+      <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -1874,7 +1874,7 @@
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
-      <c r="C26" t="b">
+      <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -1935,7 +1935,7 @@
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
-      <c r="C27" t="b">
+      <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -2000,7 +2000,7 @@
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
-      <c r="C28" t="b">
+      <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
-      <c r="C29" t="b">
+      <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -2098,7 +2098,7 @@
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
-      <c r="C30" t="b">
+      <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -2163,7 +2163,7 @@
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
-      <c r="C31" t="b">
+      <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
-      <c r="C32" t="b">
+      <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
-      <c r="C33" t="b">
+      <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="B34" t="inlineStr"/>
-      <c r="C34" t="b">
+      <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
-      <c r="C35" t="b">
+      <c r="C35" t="n">
         <v>0</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
-      <c r="C36" t="b">
+      <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
-      <c r="C37" t="b">
+      <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -2574,7 +2574,7 @@
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
-      <c r="C38" t="b">
+      <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
-      <c r="C39" t="b">
+      <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
-      <c r="C40" t="b">
+      <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
-      <c r="C41" t="b">
+      <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
-      <c r="C42" t="b">
+      <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
-      <c r="C43" t="b">
+      <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -2952,7 +2952,7 @@
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
-      <c r="C44" t="b">
+      <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
-      <c r="C45" t="b">
+      <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -3066,7 +3066,7 @@
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
-      <c r="C46" t="b">
+      <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -3127,7 +3127,7 @@
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
-      <c r="C47" t="b">
+      <c r="C47" t="n">
         <v>0</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
-      <c r="C48" t="b">
+      <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="B49" t="inlineStr"/>
-      <c r="C49" t="b">
+      <c r="C49" t="n">
         <v>0</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
-      <c r="C50" t="b">
+      <c r="C50" t="n">
         <v>0</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -3343,7 +3343,7 @@
         </is>
       </c>
       <c r="B51" t="inlineStr"/>
-      <c r="C51" t="b">
+      <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -3400,7 +3400,7 @@
         </is>
       </c>
       <c r="B52" t="inlineStr"/>
-      <c r="C52" t="b">
+      <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="B53" t="inlineStr"/>
-      <c r="C53" t="b">
+      <c r="C53" t="n">
         <v>0</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="B54" t="inlineStr"/>
-      <c r="C54" t="b">
+      <c r="C54" t="n">
         <v>0</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -3575,7 +3575,7 @@
         </is>
       </c>
       <c r="B55" t="inlineStr"/>
-      <c r="C55" t="b">
+      <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -3628,7 +3628,7 @@
         </is>
       </c>
       <c r="B56" t="inlineStr"/>
-      <c r="C56" t="b">
+      <c r="C56" t="n">
         <v>0</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -3681,7 +3681,7 @@
         </is>
       </c>
       <c r="B57" t="inlineStr"/>
-      <c r="C57" t="b">
+      <c r="C57" t="n">
         <v>0</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -3738,7 +3738,7 @@
         </is>
       </c>
       <c r="B58" t="inlineStr"/>
-      <c r="C58" t="b">
+      <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -3795,7 +3795,7 @@
         </is>
       </c>
       <c r="B59" t="inlineStr"/>
-      <c r="C59" t="b">
+      <c r="C59" t="n">
         <v>0</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -3852,7 +3852,7 @@
         </is>
       </c>
       <c r="B60" t="inlineStr"/>
-      <c r="C60" t="b">
+      <c r="C60" t="n">
         <v>0</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -3909,7 +3909,7 @@
         </is>
       </c>
       <c r="B61" t="inlineStr"/>
-      <c r="C61" t="b">
+      <c r="C61" t="n">
         <v>0</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="B62" t="inlineStr"/>
-      <c r="C62" t="b">
+      <c r="C62" t="n">
         <v>0</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -4023,7 +4023,7 @@
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
-      <c r="C63" t="b">
+      <c r="C63" t="n">
         <v>0</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="B64" t="inlineStr"/>
-      <c r="C64" t="b">
+      <c r="C64" t="n">
         <v>0</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="B65" t="inlineStr"/>
-      <c r="C65" t="b">
+      <c r="C65" t="n">
         <v>0</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -4194,7 +4194,7 @@
         </is>
       </c>
       <c r="B66" t="inlineStr"/>
-      <c r="C66" t="b">
+      <c r="C66" t="n">
         <v>0</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="B67" t="inlineStr"/>
-      <c r="C67" t="b">
+      <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -4308,7 +4308,7 @@
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
-      <c r="C68" t="b">
+      <c r="C68" t="n">
         <v>0</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -4365,7 +4365,7 @@
         </is>
       </c>
       <c r="B69" t="inlineStr"/>
-      <c r="C69" t="b">
+      <c r="C69" t="n">
         <v>0</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -4418,7 +4418,7 @@
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
-      <c r="C70" t="b">
+      <c r="C70" t="n">
         <v>0</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -4471,7 +4471,7 @@
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
-      <c r="C71" t="b">
+      <c r="C71" t="n">
         <v>0</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -4528,7 +4528,7 @@
         </is>
       </c>
       <c r="B72" t="inlineStr"/>
-      <c r="C72" t="b">
+      <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -4581,7 +4581,7 @@
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
-      <c r="C73" t="b">
+      <c r="C73" t="n">
         <v>0</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -4638,7 +4638,7 @@
         </is>
       </c>
       <c r="B74" t="inlineStr"/>
-      <c r="C74" t="b">
+      <c r="C74" t="n">
         <v>0</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -4691,7 +4691,7 @@
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
-      <c r="C75" t="b">
+      <c r="C75" t="n">
         <v>0</v>
       </c>
       <c r="D75" t="inlineStr">
@@ -4748,7 +4748,7 @@
         </is>
       </c>
       <c r="B76" t="inlineStr"/>
-      <c r="C76" t="b">
+      <c r="C76" t="n">
         <v>0</v>
       </c>
       <c r="D76" t="inlineStr">
@@ -4801,7 +4801,7 @@
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
-      <c r="C77" t="b">
+      <c r="C77" t="n">
         <v>0</v>
       </c>
       <c r="D77" t="inlineStr">
@@ -4866,7 +4866,7 @@
         </is>
       </c>
       <c r="B78" t="inlineStr"/>
-      <c r="C78" t="b">
+      <c r="C78" t="n">
         <v>0</v>
       </c>
       <c r="D78" t="inlineStr">
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="B79" t="inlineStr"/>
-      <c r="C79" t="b">
+      <c r="C79" t="n">
         <v>0</v>
       </c>
       <c r="D79" t="inlineStr">
@@ -4988,7 +4988,7 @@
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
-      <c r="C80" t="b">
+      <c r="C80" t="n">
         <v>0</v>
       </c>
       <c r="D80" t="inlineStr">
@@ -5049,7 +5049,7 @@
         </is>
       </c>
       <c r="B81" t="inlineStr"/>
-      <c r="C81" t="b">
+      <c r="C81" t="n">
         <v>0</v>
       </c>
       <c r="D81" t="inlineStr">
@@ -5110,7 +5110,7 @@
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
-      <c r="C82" t="b">
+      <c r="C82" t="n">
         <v>0</v>
       </c>
       <c r="D82" t="inlineStr">
@@ -5171,7 +5171,7 @@
         </is>
       </c>
       <c r="B83" t="inlineStr"/>
-      <c r="C83" t="b">
+      <c r="C83" t="n">
         <v>0</v>
       </c>
       <c r="D83" t="inlineStr">
@@ -5230,7 +5230,7 @@
         </is>
       </c>
       <c r="B84" t="inlineStr"/>
-      <c r="C84" t="b">
+      <c r="C84" t="n">
         <v>0</v>
       </c>
       <c r="D84" t="inlineStr">
@@ -5291,7 +5291,7 @@
         </is>
       </c>
       <c r="B85" t="inlineStr"/>
-      <c r="C85" t="b">
+      <c r="C85" t="n">
         <v>0</v>
       </c>
       <c r="D85" t="inlineStr">
@@ -5348,7 +5348,7 @@
         </is>
       </c>
       <c r="B86" t="inlineStr"/>
-      <c r="C86" t="b">
+      <c r="C86" t="n">
         <v>0</v>
       </c>
       <c r="D86" t="inlineStr">
@@ -5407,7 +5407,7 @@
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
-      <c r="C87" t="b">
+      <c r="C87" t="n">
         <v>0</v>
       </c>
       <c r="D87" t="inlineStr">
@@ -5468,7 +5468,7 @@
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
-      <c r="C88" t="b">
+      <c r="C88" t="n">
         <v>0</v>
       </c>
       <c r="D88" t="inlineStr">
@@ -5533,7 +5533,7 @@
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
-      <c r="C89" t="b">
+      <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="inlineStr">
@@ -5594,7 +5594,7 @@
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
-      <c r="C90" t="b">
+      <c r="C90" t="n">
         <v>0</v>
       </c>
       <c r="D90" t="inlineStr">
@@ -5655,7 +5655,7 @@
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
-      <c r="C91" t="b">
+      <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" t="inlineStr">
@@ -5716,7 +5716,7 @@
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
-      <c r="C92" t="b">
+      <c r="C92" t="n">
         <v>0</v>
       </c>
       <c r="D92" t="inlineStr">
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
-      <c r="C93" t="b">
+      <c r="C93" t="n">
         <v>0</v>
       </c>
       <c r="D93" t="inlineStr">
@@ -5834,7 +5834,7 @@
         </is>
       </c>
       <c r="B94" t="inlineStr"/>
-      <c r="C94" t="b">
+      <c r="C94" t="n">
         <v>0</v>
       </c>
       <c r="D94" t="inlineStr">
@@ -5891,7 +5891,7 @@
         </is>
       </c>
       <c r="B95" t="inlineStr"/>
-      <c r="C95" t="b">
+      <c r="C95" t="n">
         <v>0</v>
       </c>
       <c r="D95" t="inlineStr">
@@ -5948,7 +5948,7 @@
         </is>
       </c>
       <c r="B96" t="inlineStr"/>
-      <c r="C96" t="b">
+      <c r="C96" t="n">
         <v>0</v>
       </c>
       <c r="D96" t="inlineStr">
@@ -6005,7 +6005,7 @@
         </is>
       </c>
       <c r="B97" t="inlineStr"/>
-      <c r="C97" t="b">
+      <c r="C97" t="n">
         <v>0</v>
       </c>
       <c r="D97" t="inlineStr">
@@ -6062,7 +6062,7 @@
         </is>
       </c>
       <c r="B98" t="inlineStr"/>
-      <c r="C98" t="b">
+      <c r="C98" t="n">
         <v>0</v>
       </c>
       <c r="D98" t="inlineStr">
@@ -6119,7 +6119,7 @@
         </is>
       </c>
       <c r="B99" t="inlineStr"/>
-      <c r="C99" t="b">
+      <c r="C99" t="n">
         <v>0</v>
       </c>
       <c r="D99" t="inlineStr">
@@ -6184,7 +6184,7 @@
         </is>
       </c>
       <c r="B100" t="inlineStr"/>
-      <c r="C100" t="b">
+      <c r="C100" t="n">
         <v>0</v>
       </c>
       <c r="D100" t="inlineStr">
@@ -6249,7 +6249,7 @@
         </is>
       </c>
       <c r="B101" t="inlineStr"/>
-      <c r="C101" t="b">
+      <c r="C101" t="n">
         <v>0</v>
       </c>
       <c r="D101" t="inlineStr">
@@ -6306,7 +6306,7 @@
         </is>
       </c>
       <c r="B102" t="inlineStr"/>
-      <c r="C102" t="b">
+      <c r="C102" t="n">
         <v>0</v>
       </c>
       <c r="D102" t="inlineStr">
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="B103" t="inlineStr"/>
-      <c r="C103" t="b">
+      <c r="C103" t="n">
         <v>0</v>
       </c>
       <c r="D103" t="inlineStr">
@@ -6426,7 +6426,7 @@
         </is>
       </c>
       <c r="B104" t="inlineStr"/>
-      <c r="C104" t="b">
+      <c r="C104" t="n">
         <v>0</v>
       </c>
       <c r="D104" t="inlineStr">
@@ -6483,7 +6483,7 @@
         </is>
       </c>
       <c r="B105" t="inlineStr"/>
-      <c r="C105" t="b">
+      <c r="C105" t="n">
         <v>0</v>
       </c>
       <c r="D105" t="inlineStr">
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="B106" t="inlineStr"/>
-      <c r="C106" t="b">
+      <c r="C106" t="n">
         <v>0</v>
       </c>
       <c r="D106" t="inlineStr">
@@ -6597,7 +6597,7 @@
         </is>
       </c>
       <c r="B107" t="inlineStr"/>
-      <c r="C107" t="b">
+      <c r="C107" t="n">
         <v>0</v>
       </c>
       <c r="D107" t="inlineStr">
@@ -6662,7 +6662,7 @@
         </is>
       </c>
       <c r="B108" t="inlineStr"/>
-      <c r="C108" t="b">
+      <c r="C108" t="n">
         <v>0</v>
       </c>
       <c r="D108" t="inlineStr">
@@ -6723,7 +6723,7 @@
         </is>
       </c>
       <c r="B109" t="inlineStr"/>
-      <c r="C109" t="b">
+      <c r="C109" t="n">
         <v>0</v>
       </c>
       <c r="D109" t="inlineStr">
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="B110" t="inlineStr"/>
-      <c r="C110" t="b">
+      <c r="C110" t="n">
         <v>0</v>
       </c>
       <c r="D110" t="inlineStr">
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="B111" t="inlineStr"/>
-      <c r="C111" t="b">
+      <c r="C111" t="n">
         <v>0</v>
       </c>
       <c r="D111" t="inlineStr">
@@ -6894,7 +6894,7 @@
         </is>
       </c>
       <c r="B112" t="inlineStr"/>
-      <c r="C112" t="b">
+      <c r="C112" t="n">
         <v>0</v>
       </c>
       <c r="D112" t="inlineStr">
@@ -6951,7 +6951,7 @@
         </is>
       </c>
       <c r="B113" t="inlineStr"/>
-      <c r="C113" t="b">
+      <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="inlineStr">
@@ -7008,7 +7008,7 @@
         </is>
       </c>
       <c r="B114" t="inlineStr"/>
-      <c r="C114" t="b">
+      <c r="C114" t="n">
         <v>0</v>
       </c>
       <c r="D114" t="inlineStr">
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="B115" t="inlineStr"/>
-      <c r="C115" t="b">
+      <c r="C115" t="n">
         <v>0</v>
       </c>
       <c r="D115" t="inlineStr">
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="B116" t="inlineStr"/>
-      <c r="C116" t="b">
+      <c r="C116" t="n">
         <v>0</v>
       </c>
       <c r="D116" t="inlineStr">
@@ -7183,7 +7183,7 @@
         </is>
       </c>
       <c r="B117" t="inlineStr"/>
-      <c r="C117" t="b">
+      <c r="C117" t="n">
         <v>0</v>
       </c>
       <c r="D117" t="inlineStr">
@@ -7244,7 +7244,7 @@
         </is>
       </c>
       <c r="B118" t="inlineStr"/>
-      <c r="C118" t="b">
+      <c r="C118" t="n">
         <v>0</v>
       </c>
       <c r="D118" t="inlineStr">
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
-      <c r="C119" t="b">
+      <c r="C119" t="n">
         <v>0</v>
       </c>
       <c r="D119" t="inlineStr">
@@ -7358,7 +7358,7 @@
         </is>
       </c>
       <c r="B120" t="inlineStr"/>
-      <c r="C120" t="b">
+      <c r="C120" t="n">
         <v>0</v>
       </c>
       <c r="D120" t="inlineStr">
@@ -7415,7 +7415,7 @@
         </is>
       </c>
       <c r="B121" t="inlineStr"/>
-      <c r="C121" t="b">
+      <c r="C121" t="n">
         <v>0</v>
       </c>
       <c r="D121" t="inlineStr">
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="B122" t="inlineStr"/>
-      <c r="C122" t="b">
+      <c r="C122" t="n">
         <v>0</v>
       </c>
       <c r="D122" t="inlineStr">
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="B123" t="inlineStr"/>
-      <c r="C123" t="b">
+      <c r="C123" t="n">
         <v>0</v>
       </c>
       <c r="D123" t="inlineStr">
@@ -7590,7 +7590,7 @@
         </is>
       </c>
       <c r="B124" t="inlineStr"/>
-      <c r="C124" t="b">
+      <c r="C124" t="n">
         <v>0</v>
       </c>
       <c r="D124" t="inlineStr">
@@ -7647,7 +7647,7 @@
         </is>
       </c>
       <c r="B125" t="inlineStr"/>
-      <c r="C125" t="b">
+      <c r="C125" t="n">
         <v>0</v>
       </c>
       <c r="D125" t="inlineStr">
@@ -7708,7 +7708,7 @@
         </is>
       </c>
       <c r="B126" t="inlineStr"/>
-      <c r="C126" t="b">
+      <c r="C126" t="n">
         <v>0</v>
       </c>
       <c r="D126" t="inlineStr">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="B127" t="inlineStr"/>
-      <c r="C127" t="b">
+      <c r="C127" t="n">
         <v>0</v>
       </c>
       <c r="D127" t="inlineStr">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
-      <c r="C128" t="b">
+      <c r="C128" t="n">
         <v>0</v>
       </c>
       <c r="D128" t="inlineStr">
@@ -7893,7 +7893,7 @@
         </is>
       </c>
       <c r="B129" t="inlineStr"/>
-      <c r="C129" t="b">
+      <c r="C129" t="n">
         <v>0</v>
       </c>
       <c r="D129" t="inlineStr">
@@ -7948,7 +7948,7 @@
         </is>
       </c>
       <c r="B130" t="inlineStr"/>
-      <c r="C130" t="b">
+      <c r="C130" t="n">
         <v>0</v>
       </c>
       <c r="D130" t="inlineStr">
@@ -8009,7 +8009,7 @@
         </is>
       </c>
       <c r="B131" t="inlineStr"/>
-      <c r="C131" t="b">
+      <c r="C131" t="n">
         <v>0</v>
       </c>
       <c r="D131" t="inlineStr">
@@ -8068,7 +8068,7 @@
         </is>
       </c>
       <c r="B132" t="inlineStr"/>
-      <c r="C132" t="b">
+      <c r="C132" t="n">
         <v>0</v>
       </c>
       <c r="D132" t="inlineStr">
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="B133" t="inlineStr"/>
-      <c r="C133" t="b">
+      <c r="C133" t="n">
         <v>0</v>
       </c>
       <c r="D133" t="inlineStr">
@@ -8190,7 +8190,7 @@
         </is>
       </c>
       <c r="B134" t="inlineStr"/>
-      <c r="C134" t="b">
+      <c r="C134" t="n">
         <v>0</v>
       </c>
       <c r="D134" t="inlineStr">
@@ -8251,7 +8251,7 @@
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
-      <c r="C135" t="b">
+      <c r="C135" t="n">
         <v>0</v>
       </c>
       <c r="D135" t="inlineStr">
@@ -8308,7 +8308,7 @@
         </is>
       </c>
       <c r="B136" t="inlineStr"/>
-      <c r="C136" t="b">
+      <c r="C136" t="n">
         <v>0</v>
       </c>
       <c r="D136" t="inlineStr">
@@ -8367,7 +8367,7 @@
         </is>
       </c>
       <c r="B137" t="inlineStr"/>
-      <c r="C137" t="b">
+      <c r="C137" t="n">
         <v>0</v>
       </c>
       <c r="D137" t="inlineStr">
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="B138" t="inlineStr"/>
-      <c r="C138" t="b">
+      <c r="C138" t="n">
         <v>0</v>
       </c>
       <c r="D138" t="inlineStr">
@@ -8485,7 +8485,7 @@
         </is>
       </c>
       <c r="B139" t="inlineStr"/>
-      <c r="C139" t="b">
+      <c r="C139" t="n">
         <v>0</v>
       </c>
       <c r="D139" t="inlineStr">
@@ -8542,7 +8542,7 @@
         </is>
       </c>
       <c r="B140" t="inlineStr"/>
-      <c r="C140" t="b">
+      <c r="C140" t="n">
         <v>0</v>
       </c>
       <c r="D140" t="inlineStr">
@@ -8602,7 +8602,7 @@
         </is>
       </c>
       <c r="B141" t="inlineStr"/>
-      <c r="C141" t="b">
+      <c r="C141" t="n">
         <v>0</v>
       </c>
       <c r="D141" t="inlineStr">
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="B142" t="inlineStr"/>
-      <c r="C142" t="b">
+      <c r="C142" t="n">
         <v>0</v>
       </c>
       <c r="D142" t="inlineStr">
@@ -8723,7 +8723,7 @@
         </is>
       </c>
       <c r="B143" t="inlineStr"/>
-      <c r="C143" t="b">
+      <c r="C143" t="n">
         <v>0</v>
       </c>
       <c r="D143" t="inlineStr">
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="B144" t="inlineStr"/>
-      <c r="C144" t="b">
+      <c r="C144" t="n">
         <v>0</v>
       </c>
       <c r="D144" t="inlineStr">
@@ -8845,7 +8845,7 @@
         </is>
       </c>
       <c r="B145" t="inlineStr"/>
-      <c r="C145" t="b">
+      <c r="C145" t="n">
         <v>0</v>
       </c>
       <c r="D145" t="inlineStr">
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="B146" t="inlineStr"/>
-      <c r="C146" t="b">
+      <c r="C146" t="n">
         <v>0</v>
       </c>
       <c r="D146" t="inlineStr">
@@ -8966,7 +8966,7 @@
         </is>
       </c>
       <c r="B147" t="inlineStr"/>
-      <c r="C147" t="b">
+      <c r="C147" t="n">
         <v>0</v>
       </c>
       <c r="D147" t="inlineStr">
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
-      <c r="C148" t="b">
+      <c r="C148" t="n">
         <v>0</v>
       </c>
       <c r="D148" t="inlineStr">
@@ -9083,7 +9083,7 @@
         </is>
       </c>
       <c r="B149" t="inlineStr"/>
-      <c r="C149" t="b">
+      <c r="C149" t="n">
         <v>0</v>
       </c>
       <c r="D149" t="inlineStr">
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="B150" t="inlineStr"/>
-      <c r="C150" t="b">
+      <c r="C150" t="n">
         <v>0</v>
       </c>
       <c r="D150" t="inlineStr">
@@ -9203,7 +9203,7 @@
         </is>
       </c>
       <c r="B151" t="inlineStr"/>
-      <c r="C151" t="b">
+      <c r="C151" t="n">
         <v>0</v>
       </c>
       <c r="D151" t="inlineStr">
@@ -9262,7 +9262,7 @@
         </is>
       </c>
       <c r="B152" t="inlineStr"/>
-      <c r="C152" t="b">
+      <c r="C152" t="n">
         <v>0</v>
       </c>
       <c r="D152" t="inlineStr">
@@ -9321,7 +9321,7 @@
         </is>
       </c>
       <c r="B153" t="inlineStr"/>
-      <c r="C153" t="b">
+      <c r="C153" t="n">
         <v>0</v>
       </c>
       <c r="D153" t="inlineStr">
@@ -9381,7 +9381,7 @@
         </is>
       </c>
       <c r="B154" t="inlineStr"/>
-      <c r="C154" t="b">
+      <c r="C154" t="n">
         <v>0</v>
       </c>
       <c r="D154" t="inlineStr">
@@ -9446,7 +9446,7 @@
         </is>
       </c>
       <c r="B155" t="inlineStr"/>
-      <c r="C155" t="b">
+      <c r="C155" t="n">
         <v>0</v>
       </c>
       <c r="D155" t="inlineStr">
@@ -9511,7 +9511,7 @@
         </is>
       </c>
       <c r="B156" t="inlineStr"/>
-      <c r="C156" t="b">
+      <c r="C156" t="n">
         <v>0</v>
       </c>
       <c r="D156" t="inlineStr">
@@ -9576,7 +9576,7 @@
         </is>
       </c>
       <c r="B157" t="inlineStr"/>
-      <c r="C157" t="b">
+      <c r="C157" t="n">
         <v>0</v>
       </c>
       <c r="D157" t="inlineStr">
@@ -9636,7 +9636,7 @@
         </is>
       </c>
       <c r="B158" t="inlineStr"/>
-      <c r="C158" t="b">
+      <c r="C158" t="n">
         <v>0</v>
       </c>
       <c r="D158" t="inlineStr">
@@ -9701,7 +9701,7 @@
         </is>
       </c>
       <c r="B159" t="inlineStr"/>
-      <c r="C159" t="b">
+      <c r="C159" t="n">
         <v>0</v>
       </c>
       <c r="D159" t="inlineStr">
@@ -9760,7 +9760,7 @@
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
-      <c r="C160" t="b">
+      <c r="C160" t="n">
         <v>0</v>
       </c>
       <c r="D160" t="inlineStr">
@@ -9822,7 +9822,7 @@
         </is>
       </c>
       <c r="B161" t="inlineStr"/>
-      <c r="C161" t="b">
+      <c r="C161" t="n">
         <v>0</v>
       </c>
       <c r="D161" t="inlineStr">
@@ -9884,7 +9884,7 @@
         </is>
       </c>
       <c r="B162" t="inlineStr"/>
-      <c r="C162" t="b">
+      <c r="C162" t="n">
         <v>0</v>
       </c>
       <c r="D162" t="inlineStr">
@@ -9946,7 +9946,7 @@
         </is>
       </c>
       <c r="B163" t="inlineStr"/>
-      <c r="C163" t="b">
+      <c r="C163" t="n">
         <v>0</v>
       </c>
       <c r="D163" t="inlineStr">
@@ -10003,7 +10003,7 @@
         </is>
       </c>
       <c r="B164" t="inlineStr"/>
-      <c r="C164" t="b">
+      <c r="C164" t="n">
         <v>0</v>
       </c>
       <c r="D164" t="inlineStr">
@@ -10060,7 +10060,7 @@
         </is>
       </c>
       <c r="B165" t="inlineStr"/>
-      <c r="C165" t="b">
+      <c r="C165" t="n">
         <v>0</v>
       </c>
       <c r="D165" t="inlineStr">
@@ -10120,7 +10120,7 @@
         </is>
       </c>
       <c r="B166" t="inlineStr"/>
-      <c r="C166" t="b">
+      <c r="C166" t="n">
         <v>0</v>
       </c>
       <c r="D166" t="inlineStr">
@@ -10180,7 +10180,7 @@
         </is>
       </c>
       <c r="B167" t="inlineStr"/>
-      <c r="C167" t="b">
+      <c r="C167" t="n">
         <v>0</v>
       </c>
       <c r="D167" t="inlineStr">
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="B168" t="inlineStr"/>
-      <c r="C168" t="b">
+      <c r="C168" t="n">
         <v>0</v>
       </c>
       <c r="D168" t="inlineStr">
@@ -10297,7 +10297,7 @@
         </is>
       </c>
       <c r="B169" t="inlineStr"/>
-      <c r="C169" t="b">
+      <c r="C169" t="n">
         <v>0</v>
       </c>
       <c r="D169" t="inlineStr">
@@ -10357,7 +10357,7 @@
         </is>
       </c>
       <c r="B170" t="inlineStr"/>
-      <c r="C170" t="b">
+      <c r="C170" t="n">
         <v>0</v>
       </c>
       <c r="D170" t="inlineStr">
@@ -10416,7 +10416,7 @@
         </is>
       </c>
       <c r="B171" t="inlineStr"/>
-      <c r="C171" t="b">
+      <c r="C171" t="n">
         <v>0</v>
       </c>
       <c r="D171" t="inlineStr">
@@ -10471,7 +10471,7 @@
         </is>
       </c>
       <c r="B172" t="inlineStr"/>
-      <c r="C172" t="b">
+      <c r="C172" t="n">
         <v>0</v>
       </c>
       <c r="D172" t="inlineStr">
@@ -10530,7 +10530,7 @@
         </is>
       </c>
       <c r="B173" t="inlineStr"/>
-      <c r="C173" t="b">
+      <c r="C173" t="n">
         <v>0</v>
       </c>
       <c r="D173" t="inlineStr">
@@ -10589,7 +10589,7 @@
         </is>
       </c>
       <c r="B174" t="inlineStr"/>
-      <c r="C174" t="b">
+      <c r="C174" t="n">
         <v>0</v>
       </c>
       <c r="D174" t="inlineStr">
@@ -10650,7 +10650,7 @@
         </is>
       </c>
       <c r="B175" t="inlineStr"/>
-      <c r="C175" t="b">
+      <c r="C175" t="n">
         <v>0</v>
       </c>
       <c r="D175" t="inlineStr">
@@ -10711,7 +10711,7 @@
         </is>
       </c>
       <c r="B176" t="inlineStr"/>
-      <c r="C176" t="b">
+      <c r="C176" t="n">
         <v>0</v>
       </c>
       <c r="D176" t="inlineStr">
@@ -10772,7 +10772,7 @@
         </is>
       </c>
       <c r="B177" t="inlineStr"/>
-      <c r="C177" t="b">
+      <c r="C177" t="n">
         <v>0</v>
       </c>
       <c r="D177" t="inlineStr">
@@ -10831,7 +10831,7 @@
         </is>
       </c>
       <c r="B178" t="inlineStr"/>
-      <c r="C178" t="b">
+      <c r="C178" t="n">
         <v>0</v>
       </c>
       <c r="D178" t="inlineStr">
@@ -10894,7 +10894,7 @@
         </is>
       </c>
       <c r="B179" t="inlineStr"/>
-      <c r="C179" t="b">
+      <c r="C179" t="n">
         <v>0</v>
       </c>
       <c r="D179" t="inlineStr">
@@ -10953,7 +10953,7 @@
         </is>
       </c>
       <c r="B180" t="inlineStr"/>
-      <c r="C180" t="b">
+      <c r="C180" t="n">
         <v>0</v>
       </c>
       <c r="D180" t="inlineStr">
@@ -11012,7 +11012,7 @@
         </is>
       </c>
       <c r="B181" t="inlineStr"/>
-      <c r="C181" t="b">
+      <c r="C181" t="n">
         <v>0</v>
       </c>
       <c r="D181" t="inlineStr">
@@ -11072,7 +11072,7 @@
         </is>
       </c>
       <c r="B182" t="inlineStr"/>
-      <c r="C182" t="b">
+      <c r="C182" t="n">
         <v>0</v>
       </c>
       <c r="D182" t="inlineStr">
@@ -11132,7 +11132,7 @@
         </is>
       </c>
       <c r="B183" t="inlineStr"/>
-      <c r="C183" t="b">
+      <c r="C183" t="n">
         <v>0</v>
       </c>
       <c r="D183" t="inlineStr">
@@ -11192,7 +11192,7 @@
         </is>
       </c>
       <c r="B184" t="inlineStr"/>
-      <c r="C184" t="b">
+      <c r="C184" t="n">
         <v>0</v>
       </c>
       <c r="D184" t="inlineStr">
@@ -11251,7 +11251,7 @@
         </is>
       </c>
       <c r="B185" t="inlineStr"/>
-      <c r="C185" t="b">
+      <c r="C185" t="n">
         <v>0</v>
       </c>
       <c r="D185" t="inlineStr">
@@ -11310,7 +11310,7 @@
         </is>
       </c>
       <c r="B186" t="inlineStr"/>
-      <c r="C186" t="b">
+      <c r="C186" t="n">
         <v>0</v>
       </c>
       <c r="D186" t="inlineStr">
@@ -11371,7 +11371,7 @@
         </is>
       </c>
       <c r="B187" t="inlineStr"/>
-      <c r="C187" t="b">
+      <c r="C187" t="n">
         <v>0</v>
       </c>
       <c r="D187" t="inlineStr">
@@ -11430,7 +11430,7 @@
         </is>
       </c>
       <c r="B188" t="inlineStr"/>
-      <c r="C188" t="b">
+      <c r="C188" t="n">
         <v>0</v>
       </c>
       <c r="D188" t="inlineStr">
@@ -11491,7 +11491,7 @@
         </is>
       </c>
       <c r="B189" t="inlineStr"/>
-      <c r="C189" t="b">
+      <c r="C189" t="n">
         <v>0</v>
       </c>
       <c r="D189" t="inlineStr">
@@ -11554,7 +11554,7 @@
         </is>
       </c>
       <c r="B190" t="inlineStr"/>
-      <c r="C190" t="b">
+      <c r="C190" t="n">
         <v>0</v>
       </c>
       <c r="D190" t="inlineStr">
@@ -11615,7 +11615,7 @@
         </is>
       </c>
       <c r="B191" t="inlineStr"/>
-      <c r="C191" t="b">
+      <c r="C191" t="n">
         <v>0</v>
       </c>
       <c r="D191" t="inlineStr">
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B192" t="inlineStr"/>
-      <c r="C192" t="b">
+      <c r="C192" t="n">
         <v>0</v>
       </c>
       <c r="D192" t="inlineStr">
@@ -11739,7 +11739,7 @@
         </is>
       </c>
       <c r="B193" t="inlineStr"/>
-      <c r="C193" t="b">
+      <c r="C193" t="n">
         <v>0</v>
       </c>
       <c r="D193" t="inlineStr">
@@ -11801,7 +11801,7 @@
         </is>
       </c>
       <c r="B194" t="inlineStr"/>
-      <c r="C194" t="b">
+      <c r="C194" t="n">
         <v>0</v>
       </c>
       <c r="D194" t="inlineStr">
@@ -11856,7 +11856,7 @@
         </is>
       </c>
       <c r="B195" t="inlineStr"/>
-      <c r="C195" t="b">
+      <c r="C195" t="n">
         <v>0</v>
       </c>
       <c r="D195" t="inlineStr">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="B196" t="inlineStr"/>
-      <c r="C196" t="b">
+      <c r="C196" t="n">
         <v>0</v>
       </c>
       <c r="D196" t="inlineStr">
@@ -11974,7 +11974,7 @@
         </is>
       </c>
       <c r="B197" t="inlineStr"/>
-      <c r="C197" t="b">
+      <c r="C197" t="n">
         <v>0</v>
       </c>
       <c r="D197" t="inlineStr">
@@ -12033,7 +12033,7 @@
         </is>
       </c>
       <c r="B198" t="inlineStr"/>
-      <c r="C198" t="b">
+      <c r="C198" t="n">
         <v>0</v>
       </c>
       <c r="D198" t="inlineStr">
@@ -12088,7 +12088,7 @@
         </is>
       </c>
       <c r="B199" t="inlineStr"/>
-      <c r="C199" t="b">
+      <c r="C199" t="n">
         <v>0</v>
       </c>
       <c r="D199" t="inlineStr">
@@ -12143,7 +12143,7 @@
         </is>
       </c>
       <c r="B200" t="inlineStr"/>
-      <c r="C200" t="b">
+      <c r="C200" t="n">
         <v>0</v>
       </c>
       <c r="D200" t="inlineStr">
@@ -12204,7 +12204,7 @@
         </is>
       </c>
       <c r="B201" t="inlineStr"/>
-      <c r="C201" t="b">
+      <c r="C201" t="n">
         <v>0</v>
       </c>
       <c r="D201" t="inlineStr">
@@ -12265,7 +12265,7 @@
         </is>
       </c>
       <c r="B202" t="inlineStr"/>
-      <c r="C202" t="b">
+      <c r="C202" t="n">
         <v>0</v>
       </c>
       <c r="D202" t="inlineStr">
@@ -12330,7 +12330,7 @@
         </is>
       </c>
       <c r="B203" t="inlineStr"/>
-      <c r="C203" t="b">
+      <c r="C203" t="n">
         <v>0</v>
       </c>
       <c r="D203" t="inlineStr">
@@ -12391,7 +12391,7 @@
         </is>
       </c>
       <c r="B204" t="inlineStr"/>
-      <c r="C204" t="b">
+      <c r="C204" t="n">
         <v>0</v>
       </c>
       <c r="D204" t="inlineStr">
@@ -12452,7 +12452,7 @@
         </is>
       </c>
       <c r="B205" t="inlineStr"/>
-      <c r="C205" t="b">
+      <c r="C205" t="n">
         <v>0</v>
       </c>
       <c r="D205" t="inlineStr">
@@ -12512,7 +12512,7 @@
         </is>
       </c>
       <c r="B206" t="inlineStr"/>
-      <c r="C206" t="b">
+      <c r="C206" t="n">
         <v>0</v>
       </c>
       <c r="D206" t="inlineStr">
@@ -12572,7 +12572,7 @@
         </is>
       </c>
       <c r="B207" t="inlineStr"/>
-      <c r="C207" t="b">
+      <c r="C207" t="n">
         <v>0</v>
       </c>
       <c r="D207" t="inlineStr">
@@ -12631,7 +12631,7 @@
         </is>
       </c>
       <c r="B208" t="inlineStr"/>
-      <c r="C208" t="b">
+      <c r="C208" t="n">
         <v>0</v>
       </c>
       <c r="D208" t="inlineStr">
@@ -12691,7 +12691,7 @@
         </is>
       </c>
       <c r="B209" t="inlineStr"/>
-      <c r="C209" t="b">
+      <c r="C209" t="n">
         <v>0</v>
       </c>
       <c r="D209" t="inlineStr">
@@ -12750,7 +12750,7 @@
         </is>
       </c>
       <c r="B210" t="inlineStr"/>
-      <c r="C210" t="b">
+      <c r="C210" t="n">
         <v>0</v>
       </c>
       <c r="D210" t="inlineStr">
@@ -12809,7 +12809,7 @@
         </is>
       </c>
       <c r="B211" t="inlineStr"/>
-      <c r="C211" t="b">
+      <c r="C211" t="n">
         <v>0</v>
       </c>
       <c r="D211" t="inlineStr">
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="B212" t="inlineStr"/>
-      <c r="C212" t="b">
+      <c r="C212" t="n">
         <v>0</v>
       </c>
       <c r="D212" t="inlineStr">
@@ -12928,7 +12928,7 @@
         </is>
       </c>
       <c r="B213" t="inlineStr"/>
-      <c r="C213" t="b">
+      <c r="C213" t="n">
         <v>0</v>
       </c>
       <c r="D213" t="inlineStr">
@@ -12989,7 +12989,7 @@
         </is>
       </c>
       <c r="B214" t="inlineStr"/>
-      <c r="C214" t="b">
+      <c r="C214" t="n">
         <v>0</v>
       </c>
       <c r="D214" t="inlineStr">
@@ -13049,7 +13049,7 @@
         </is>
       </c>
       <c r="B215" t="inlineStr"/>
-      <c r="C215" t="b">
+      <c r="C215" t="n">
         <v>0</v>
       </c>
       <c r="D215" t="inlineStr">
@@ -13112,7 +13112,7 @@
         </is>
       </c>
       <c r="B216" t="inlineStr"/>
-      <c r="C216" t="b">
+      <c r="C216" t="n">
         <v>0</v>
       </c>
       <c r="D216" t="inlineStr">
@@ -13172,7 +13172,7 @@
         </is>
       </c>
       <c r="B217" t="inlineStr"/>
-      <c r="C217" t="b">
+      <c r="C217" t="n">
         <v>0</v>
       </c>
       <c r="D217" t="inlineStr">
@@ -13232,7 +13232,7 @@
         </is>
       </c>
       <c r="B218" t="inlineStr"/>
-      <c r="C218" t="b">
+      <c r="C218" t="n">
         <v>0</v>
       </c>
       <c r="D218" t="inlineStr">
@@ -13292,7 +13292,7 @@
         </is>
       </c>
       <c r="B219" t="inlineStr"/>
-      <c r="C219" t="b">
+      <c r="C219" t="n">
         <v>0</v>
       </c>
       <c r="D219" t="inlineStr">
@@ -13353,7 +13353,7 @@
         </is>
       </c>
       <c r="B220" t="inlineStr"/>
-      <c r="C220" t="b">
+      <c r="C220" t="n">
         <v>0</v>
       </c>
       <c r="D220" t="inlineStr">
@@ -13414,7 +13414,7 @@
         </is>
       </c>
       <c r="B221" t="inlineStr"/>
-      <c r="C221" t="b">
+      <c r="C221" t="n">
         <v>0</v>
       </c>
       <c r="D221" t="inlineStr">
@@ -13469,7 +13469,7 @@
         </is>
       </c>
       <c r="B222" t="inlineStr"/>
-      <c r="C222" t="b">
+      <c r="C222" t="n">
         <v>0</v>
       </c>
       <c r="D222" t="inlineStr">
@@ -13524,7 +13524,7 @@
         </is>
       </c>
       <c r="B223" t="inlineStr"/>
-      <c r="C223" t="b">
+      <c r="C223" t="n">
         <v>0</v>
       </c>
       <c r="D223" t="inlineStr">
@@ -13583,7 +13583,7 @@
         </is>
       </c>
       <c r="B224" t="inlineStr"/>
-      <c r="C224" t="b">
+      <c r="C224" t="n">
         <v>0</v>
       </c>
       <c r="D224" t="inlineStr"/>
@@ -13642,7 +13642,7 @@
         </is>
       </c>
       <c r="B225" t="inlineStr"/>
-      <c r="C225" t="b">
+      <c r="C225" t="n">
         <v>0</v>
       </c>
       <c r="D225" t="inlineStr"/>
@@ -13697,7 +13697,7 @@
         </is>
       </c>
       <c r="B226" t="inlineStr"/>
-      <c r="C226" t="b">
+      <c r="C226" t="n">
         <v>0</v>
       </c>
       <c r="D226" t="inlineStr"/>
@@ -13756,7 +13756,7 @@
         </is>
       </c>
       <c r="B227" t="inlineStr"/>
-      <c r="C227" t="b">
+      <c r="C227" t="n">
         <v>0</v>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -13807,7 +13807,7 @@
         </is>
       </c>
       <c r="B228" t="inlineStr"/>
-      <c r="C228" t="b">
+      <c r="C228" t="n">
         <v>0</v>
       </c>
       <c r="D228" t="inlineStr">
@@ -13858,7 +13858,7 @@
         </is>
       </c>
       <c r="B229" t="inlineStr"/>
-      <c r="C229" t="b">
+      <c r="C229" t="n">
         <v>1</v>
       </c>
       <c r="D229" t="inlineStr">
@@ -13917,7 +13917,7 @@
         </is>
       </c>
       <c r="B230" t="inlineStr"/>
-      <c r="C230" t="b">
+      <c r="C230" t="n">
         <v>0</v>
       </c>
       <c r="D230" t="inlineStr">
@@ -13972,7 +13972,7 @@
         </is>
       </c>
       <c r="B231" t="inlineStr"/>
-      <c r="C231" t="b">
+      <c r="C231" t="n">
         <v>0</v>
       </c>
       <c r="D231" t="inlineStr">
@@ -14031,7 +14031,7 @@
         </is>
       </c>
       <c r="B232" t="inlineStr"/>
-      <c r="C232" t="b">
+      <c r="C232" t="n">
         <v>0</v>
       </c>
       <c r="D232" t="inlineStr">
@@ -14078,7 +14078,7 @@
         </is>
       </c>
       <c r="B233" t="inlineStr"/>
-      <c r="C233" t="b">
+      <c r="C233" t="n">
         <v>0</v>
       </c>
       <c r="D233" t="inlineStr">
@@ -14137,7 +14137,7 @@
         </is>
       </c>
       <c r="B234" t="inlineStr"/>
-      <c r="C234" t="b">
+      <c r="C234" t="n">
         <v>0</v>
       </c>
       <c r="D234" t="inlineStr">
@@ -14192,7 +14192,7 @@
         </is>
       </c>
       <c r="B235" t="inlineStr"/>
-      <c r="C235" t="b">
+      <c r="C235" t="n">
         <v>0</v>
       </c>
       <c r="D235" t="inlineStr">
@@ -14243,7 +14243,7 @@
         </is>
       </c>
       <c r="B236" t="inlineStr"/>
-      <c r="C236" t="b">
+      <c r="C236" t="n">
         <v>0</v>
       </c>
       <c r="D236" t="inlineStr">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="B237" t="inlineStr"/>
-      <c r="C237" t="b">
+      <c r="C237" t="n">
         <v>0</v>
       </c>
       <c r="D237" t="inlineStr">
@@ -14345,7 +14345,7 @@
         </is>
       </c>
       <c r="B238" t="inlineStr"/>
-      <c r="C238" t="b">
+      <c r="C238" t="n">
         <v>0</v>
       </c>
       <c r="D238" t="inlineStr">
@@ -14392,7 +14392,7 @@
         </is>
       </c>
       <c r="B239" t="inlineStr"/>
-      <c r="C239" t="b">
+      <c r="C239" t="n">
         <v>0</v>
       </c>
       <c r="D239" t="inlineStr"/>
@@ -14451,7 +14451,7 @@
         </is>
       </c>
       <c r="B240" t="inlineStr"/>
-      <c r="C240" t="b">
+      <c r="C240" t="n">
         <v>0</v>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -14506,7 +14506,7 @@
         </is>
       </c>
       <c r="B241" t="inlineStr"/>
-      <c r="C241" t="b">
+      <c r="C241" t="n">
         <v>0</v>
       </c>
       <c r="D241" t="inlineStr">
@@ -14565,7 +14565,7 @@
         </is>
       </c>
       <c r="B242" t="inlineStr"/>
-      <c r="C242" t="b">
+      <c r="C242" t="n">
         <v>0</v>
       </c>
       <c r="D242" t="inlineStr"/>
@@ -14612,7 +14612,7 @@
         </is>
       </c>
       <c r="B243" t="inlineStr"/>
-      <c r="C243" t="b">
+      <c r="C243" t="n">
         <v>0</v>
       </c>
       <c r="D243" t="inlineStr">
@@ -14675,7 +14675,7 @@
         </is>
       </c>
       <c r="B244" t="inlineStr"/>
-      <c r="C244" t="b">
+      <c r="C244" t="n">
         <v>0</v>
       </c>
       <c r="D244" t="inlineStr">
@@ -14726,7 +14726,7 @@
         </is>
       </c>
       <c r="B245" t="inlineStr"/>
-      <c r="C245" t="b">
+      <c r="C245" t="n">
         <v>0</v>
       </c>
       <c r="D245" t="inlineStr"/>
@@ -14785,7 +14785,7 @@
         </is>
       </c>
       <c r="B246" t="inlineStr"/>
-      <c r="C246" t="b">
+      <c r="C246" t="n">
         <v>0</v>
       </c>
       <c r="D246" t="inlineStr">
@@ -14836,7 +14836,7 @@
         </is>
       </c>
       <c r="B247" t="inlineStr"/>
-      <c r="C247" t="b">
+      <c r="C247" t="n">
         <v>0</v>
       </c>
       <c r="D247" t="inlineStr">
@@ -14895,7 +14895,7 @@
         </is>
       </c>
       <c r="B248" t="inlineStr"/>
-      <c r="C248" t="b">
+      <c r="C248" t="n">
         <v>0</v>
       </c>
       <c r="D248" t="inlineStr">
@@ -14958,7 +14958,7 @@
         </is>
       </c>
       <c r="B249" t="inlineStr"/>
-      <c r="C249" t="b">
+      <c r="C249" t="n">
         <v>0</v>
       </c>
       <c r="D249" t="inlineStr">
@@ -15017,7 +15017,7 @@
         </is>
       </c>
       <c r="B250" t="inlineStr"/>
-      <c r="C250" t="b">
+      <c r="C250" t="n">
         <v>0</v>
       </c>
       <c r="D250" t="inlineStr"/>
@@ -15064,7 +15064,7 @@
         </is>
       </c>
       <c r="B251" t="inlineStr"/>
-      <c r="C251" t="b">
+      <c r="C251" t="n">
         <v>0</v>
       </c>
       <c r="D251" t="inlineStr"/>
@@ -15119,7 +15119,7 @@
         </is>
       </c>
       <c r="B252" t="inlineStr"/>
-      <c r="C252" t="b">
+      <c r="C252" t="n">
         <v>0</v>
       </c>
       <c r="D252" t="inlineStr">
@@ -15166,7 +15166,7 @@
         </is>
       </c>
       <c r="B253" t="inlineStr"/>
-      <c r="C253" t="b">
+      <c r="C253" t="n">
         <v>0</v>
       </c>
       <c r="D253" t="inlineStr">
@@ -15213,7 +15213,7 @@
         </is>
       </c>
       <c r="B254" t="inlineStr"/>
-      <c r="C254" t="b">
+      <c r="C254" t="n">
         <v>0</v>
       </c>
       <c r="D254" t="inlineStr">
@@ -15256,7 +15256,7 @@
         </is>
       </c>
       <c r="B255" t="inlineStr"/>
-      <c r="C255" t="b">
+      <c r="C255" t="n">
         <v>0</v>
       </c>
       <c r="D255" t="inlineStr"/>
@@ -15299,7 +15299,7 @@
         </is>
       </c>
       <c r="B256" t="inlineStr"/>
-      <c r="C256" t="b">
+      <c r="C256" t="n">
         <v>0</v>
       </c>
       <c r="D256" t="inlineStr">
@@ -15350,7 +15350,7 @@
         </is>
       </c>
       <c r="B257" t="inlineStr"/>
-      <c r="C257" t="b">
+      <c r="C257" t="n">
         <v>0</v>
       </c>
       <c r="D257" t="inlineStr">
@@ -15401,7 +15401,7 @@
         </is>
       </c>
       <c r="B258" t="inlineStr"/>
-      <c r="C258" t="b">
+      <c r="C258" t="n">
         <v>0</v>
       </c>
       <c r="D258" t="inlineStr">
@@ -15452,7 +15452,7 @@
         </is>
       </c>
       <c r="B259" t="inlineStr"/>
-      <c r="C259" t="b">
+      <c r="C259" t="n">
         <v>0</v>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -15499,7 +15499,7 @@
         </is>
       </c>
       <c r="B260" t="inlineStr"/>
-      <c r="C260" t="b">
+      <c r="C260" t="n">
         <v>0</v>
       </c>
       <c r="D260" t="inlineStr">
@@ -15554,7 +15554,7 @@
         </is>
       </c>
       <c r="B261" t="inlineStr"/>
-      <c r="C261" t="b">
+      <c r="C261" t="n">
         <v>0</v>
       </c>
       <c r="D261" t="inlineStr">
@@ -15605,7 +15605,7 @@
         </is>
       </c>
       <c r="B262" t="inlineStr"/>
-      <c r="C262" t="b">
+      <c r="C262" t="n">
         <v>0</v>
       </c>
       <c r="D262" t="inlineStr">
@@ -15656,7 +15656,7 @@
         </is>
       </c>
       <c r="B263" t="inlineStr"/>
-      <c r="C263" t="b">
+      <c r="C263" t="n">
         <v>0</v>
       </c>
       <c r="D263" t="inlineStr">
@@ -15707,7 +15707,7 @@
         </is>
       </c>
       <c r="B264" t="inlineStr"/>
-      <c r="C264" t="b">
+      <c r="C264" t="n">
         <v>0</v>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="B265" t="inlineStr"/>
-      <c r="C265" t="b">
+      <c r="C265" t="n">
         <v>0</v>
       </c>
       <c r="D265" t="inlineStr"/>
@@ -15809,7 +15809,7 @@
         </is>
       </c>
       <c r="B266" t="inlineStr"/>
-      <c r="C266" t="b">
+      <c r="C266" t="n">
         <v>0</v>
       </c>
       <c r="D266" t="inlineStr">
@@ -15860,7 +15860,7 @@
         </is>
       </c>
       <c r="B267" t="inlineStr"/>
-      <c r="C267" t="b">
+      <c r="C267" t="n">
         <v>0</v>
       </c>
       <c r="D267" t="inlineStr"/>
@@ -15911,7 +15911,7 @@
         </is>
       </c>
       <c r="B268" t="inlineStr"/>
-      <c r="C268" t="b">
+      <c r="C268" t="n">
         <v>0</v>
       </c>
       <c r="D268" t="inlineStr">
@@ -15962,7 +15962,7 @@
         </is>
       </c>
       <c r="B269" t="inlineStr"/>
-      <c r="C269" t="b">
+      <c r="C269" t="n">
         <v>0</v>
       </c>
       <c r="D269" t="inlineStr">
@@ -16009,7 +16009,7 @@
         </is>
       </c>
       <c r="B270" t="inlineStr"/>
-      <c r="C270" t="b">
+      <c r="C270" t="n">
         <v>0</v>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -16056,7 +16056,7 @@
         </is>
       </c>
       <c r="B271" t="inlineStr"/>
-      <c r="C271" t="b">
+      <c r="C271" t="n">
         <v>0</v>
       </c>
       <c r="D271" t="inlineStr">
@@ -16103,7 +16103,7 @@
         </is>
       </c>
       <c r="B272" t="inlineStr"/>
-      <c r="C272" t="b">
+      <c r="C272" t="n">
         <v>0</v>
       </c>
       <c r="D272" t="inlineStr">
@@ -16158,7 +16158,7 @@
         </is>
       </c>
       <c r="B273" t="inlineStr"/>
-      <c r="C273" t="b">
+      <c r="C273" t="n">
         <v>0</v>
       </c>
       <c r="D273" t="inlineStr">
@@ -16209,7 +16209,7 @@
         </is>
       </c>
       <c r="B274" t="inlineStr"/>
-      <c r="C274" t="b">
+      <c r="C274" t="n">
         <v>0</v>
       </c>
       <c r="D274" t="inlineStr">
@@ -16264,7 +16264,7 @@
         </is>
       </c>
       <c r="B275" t="inlineStr"/>
-      <c r="C275" t="b">
+      <c r="C275" t="n">
         <v>0</v>
       </c>
       <c r="D275" t="inlineStr"/>
@@ -16311,7 +16311,7 @@
         </is>
       </c>
       <c r="B276" t="inlineStr"/>
-      <c r="C276" t="b">
+      <c r="C276" t="n">
         <v>0</v>
       </c>
       <c r="D276" t="inlineStr"/>
@@ -16358,7 +16358,7 @@
         </is>
       </c>
       <c r="B277" t="inlineStr"/>
-      <c r="C277" t="b">
+      <c r="C277" t="n">
         <v>0</v>
       </c>
       <c r="D277" t="inlineStr">
@@ -16413,7 +16413,7 @@
         </is>
       </c>
       <c r="B278" t="inlineStr"/>
-      <c r="C278" t="b">
+      <c r="C278" t="n">
         <v>0</v>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -16464,7 +16464,7 @@
         </is>
       </c>
       <c r="B279" t="inlineStr"/>
-      <c r="C279" t="b">
+      <c r="C279" t="n">
         <v>0</v>
       </c>
       <c r="D279" t="inlineStr"/>
@@ -16515,7 +16515,7 @@
         </is>
       </c>
       <c r="B280" t="inlineStr"/>
-      <c r="C280" t="b">
+      <c r="C280" t="n">
         <v>0</v>
       </c>
       <c r="D280" t="inlineStr"/>
@@ -16566,7 +16566,7 @@
         </is>
       </c>
       <c r="B281" t="inlineStr"/>
-      <c r="C281" t="b">
+      <c r="C281" t="n">
         <v>0</v>
       </c>
       <c r="D281" t="inlineStr"/>
@@ -16617,7 +16617,7 @@
         </is>
       </c>
       <c r="B282" t="inlineStr"/>
-      <c r="C282" t="b">
+      <c r="C282" t="n">
         <v>0</v>
       </c>
       <c r="D282" t="inlineStr">
@@ -16668,7 +16668,7 @@
         </is>
       </c>
       <c r="B283" t="inlineStr"/>
-      <c r="C283" t="b">
+      <c r="C283" t="n">
         <v>1</v>
       </c>
       <c r="D283" t="inlineStr">
@@ -16719,7 +16719,7 @@
         </is>
       </c>
       <c r="B284" t="inlineStr"/>
-      <c r="C284" t="b">
+      <c r="C284" t="n">
         <v>0</v>
       </c>
       <c r="D284" t="inlineStr">
@@ -16766,7 +16766,7 @@
         </is>
       </c>
       <c r="B285" t="inlineStr"/>
-      <c r="C285" t="b">
+      <c r="C285" t="n">
         <v>0</v>
       </c>
       <c r="D285" t="inlineStr">
@@ -16817,7 +16817,7 @@
         </is>
       </c>
       <c r="B286" t="inlineStr"/>
-      <c r="C286" t="b">
+      <c r="C286" t="n">
         <v>0</v>
       </c>
       <c r="D286" t="inlineStr">
@@ -16864,7 +16864,7 @@
         </is>
       </c>
       <c r="B287" t="inlineStr"/>
-      <c r="C287" t="b">
+      <c r="C287" t="n">
         <v>0</v>
       </c>
       <c r="D287" t="inlineStr">
@@ -16915,7 +16915,7 @@
         </is>
       </c>
       <c r="B288" t="inlineStr"/>
-      <c r="C288" t="b">
+      <c r="C288" t="n">
         <v>0</v>
       </c>
       <c r="D288" t="inlineStr">
@@ -16962,7 +16962,7 @@
         </is>
       </c>
       <c r="B289" t="inlineStr"/>
-      <c r="C289" t="b">
+      <c r="C289" t="n">
         <v>0</v>
       </c>
       <c r="D289" t="inlineStr">
@@ -17013,7 +17013,7 @@
         </is>
       </c>
       <c r="B290" t="inlineStr"/>
-      <c r="C290" t="b">
+      <c r="C290" t="n">
         <v>0</v>
       </c>
       <c r="D290" t="inlineStr">
@@ -17060,7 +17060,7 @@
         </is>
       </c>
       <c r="B291" t="inlineStr"/>
-      <c r="C291" t="b">
+      <c r="C291" t="n">
         <v>0</v>
       </c>
       <c r="D291" t="inlineStr">
@@ -17115,7 +17115,7 @@
         </is>
       </c>
       <c r="B292" t="inlineStr"/>
-      <c r="C292" t="b">
+      <c r="C292" t="n">
         <v>1</v>
       </c>
       <c r="D292" t="inlineStr">
@@ -17162,7 +17162,7 @@
         </is>
       </c>
       <c r="B293" t="inlineStr"/>
-      <c r="C293" t="b">
+      <c r="C293" t="n">
         <v>0</v>
       </c>
       <c r="D293" t="inlineStr">
@@ -17209,7 +17209,7 @@
         </is>
       </c>
       <c r="B294" t="inlineStr"/>
-      <c r="C294" t="b">
+      <c r="C294" t="n">
         <v>0</v>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -17260,7 +17260,7 @@
         </is>
       </c>
       <c r="B295" t="inlineStr"/>
-      <c r="C295" t="b">
+      <c r="C295" t="n">
         <v>1</v>
       </c>
       <c r="D295" t="inlineStr">
@@ -17311,7 +17311,7 @@
         </is>
       </c>
       <c r="B296" t="inlineStr"/>
-      <c r="C296" t="b">
+      <c r="C296" t="n">
         <v>1</v>
       </c>
       <c r="D296" t="inlineStr">
@@ -17362,7 +17362,7 @@
         </is>
       </c>
       <c r="B297" t="inlineStr"/>
-      <c r="C297" t="b">
+      <c r="C297" t="n">
         <v>1</v>
       </c>
       <c r="D297" t="inlineStr">
@@ -17413,7 +17413,7 @@
         </is>
       </c>
       <c r="B298" t="inlineStr"/>
-      <c r="C298" t="b">
+      <c r="C298" t="n">
         <v>1</v>
       </c>
       <c r="D298" t="inlineStr">
@@ -17464,7 +17464,7 @@
         </is>
       </c>
       <c r="B299" t="inlineStr"/>
-      <c r="C299" t="b">
+      <c r="C299" t="n">
         <v>1</v>
       </c>
       <c r="D299" t="inlineStr">
@@ -17515,7 +17515,7 @@
         </is>
       </c>
       <c r="B300" t="inlineStr"/>
-      <c r="C300" t="b">
+      <c r="C300" t="n">
         <v>1</v>
       </c>
       <c r="D300" t="inlineStr">
@@ -17566,7 +17566,7 @@
         </is>
       </c>
       <c r="B301" t="inlineStr"/>
-      <c r="C301" t="b">
+      <c r="C301" t="n">
         <v>1</v>
       </c>
       <c r="D301" t="inlineStr">
@@ -17617,7 +17617,7 @@
         </is>
       </c>
       <c r="B302" t="inlineStr"/>
-      <c r="C302" t="b">
+      <c r="C302" t="n">
         <v>1</v>
       </c>
       <c r="D302" t="inlineStr">
@@ -17668,7 +17668,7 @@
         </is>
       </c>
       <c r="B303" t="inlineStr"/>
-      <c r="C303" t="b">
+      <c r="C303" t="n">
         <v>0</v>
       </c>
       <c r="D303" t="inlineStr">
@@ -17719,7 +17719,7 @@
         </is>
       </c>
       <c r="B304" t="inlineStr"/>
-      <c r="C304" t="b">
+      <c r="C304" t="n">
         <v>1</v>
       </c>
       <c r="D304" t="inlineStr">
@@ -17770,7 +17770,7 @@
         </is>
       </c>
       <c r="B305" t="inlineStr"/>
-      <c r="C305" t="b">
+      <c r="C305" t="n">
         <v>1</v>
       </c>
       <c r="D305" t="inlineStr">
@@ -17821,7 +17821,7 @@
         </is>
       </c>
       <c r="B306" t="inlineStr"/>
-      <c r="C306" t="b">
+      <c r="C306" t="n">
         <v>0</v>
       </c>
       <c r="D306" t="inlineStr">
@@ -17872,7 +17872,7 @@
         </is>
       </c>
       <c r="B307" t="inlineStr"/>
-      <c r="C307" t="b">
+      <c r="C307" t="n">
         <v>0</v>
       </c>
       <c r="D307" t="inlineStr">
@@ -17923,7 +17923,7 @@
         </is>
       </c>
       <c r="B308" t="inlineStr"/>
-      <c r="C308" t="b">
+      <c r="C308" t="n">
         <v>1</v>
       </c>
       <c r="D308" t="inlineStr">
@@ -17974,7 +17974,7 @@
         </is>
       </c>
       <c r="B309" t="inlineStr"/>
-      <c r="C309" t="b">
+      <c r="C309" t="n">
         <v>1</v>
       </c>
       <c r="D309" t="inlineStr">
@@ -18025,7 +18025,7 @@
         </is>
       </c>
       <c r="B310" t="inlineStr"/>
-      <c r="C310" t="b">
+      <c r="C310" t="n">
         <v>1</v>
       </c>
       <c r="D310" t="inlineStr">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="B311" t="inlineStr"/>
-      <c r="C311" t="b">
+      <c r="C311" t="n">
         <v>1</v>
       </c>
       <c r="D311" t="inlineStr">
@@ -18127,7 +18127,7 @@
         </is>
       </c>
       <c r="B312" t="inlineStr"/>
-      <c r="C312" t="b">
+      <c r="C312" t="n">
         <v>1</v>
       </c>
       <c r="D312" t="inlineStr">
@@ -18178,7 +18178,7 @@
         </is>
       </c>
       <c r="B313" t="inlineStr"/>
-      <c r="C313" t="b">
+      <c r="C313" t="n">
         <v>1</v>
       </c>
       <c r="D313" t="inlineStr">
@@ -18229,7 +18229,7 @@
         </is>
       </c>
       <c r="B314" t="inlineStr"/>
-      <c r="C314" t="b">
+      <c r="C314" t="n">
         <v>1</v>
       </c>
       <c r="D314" t="inlineStr">
@@ -18280,7 +18280,7 @@
         </is>
       </c>
       <c r="B315" t="inlineStr"/>
-      <c r="C315" t="b">
+      <c r="C315" t="n">
         <v>1</v>
       </c>
       <c r="D315" t="inlineStr">
@@ -18331,7 +18331,7 @@
         </is>
       </c>
       <c r="B316" t="inlineStr"/>
-      <c r="C316" t="b">
+      <c r="C316" t="n">
         <v>1</v>
       </c>
       <c r="D316" t="inlineStr">
@@ -18382,7 +18382,7 @@
         </is>
       </c>
       <c r="B317" t="inlineStr"/>
-      <c r="C317" t="b">
+      <c r="C317" t="n">
         <v>1</v>
       </c>
       <c r="D317" t="inlineStr">
@@ -18433,7 +18433,7 @@
         </is>
       </c>
       <c r="B318" t="inlineStr"/>
-      <c r="C318" t="b">
+      <c r="C318" t="n">
         <v>1</v>
       </c>
       <c r="D318" t="inlineStr">
@@ -18484,7 +18484,7 @@
         </is>
       </c>
       <c r="B319" t="inlineStr"/>
-      <c r="C319" t="b">
+      <c r="C319" t="n">
         <v>1</v>
       </c>
       <c r="D319" t="inlineStr">
@@ -18535,7 +18535,7 @@
         </is>
       </c>
       <c r="B320" t="inlineStr"/>
-      <c r="C320" t="b">
+      <c r="C320" t="n">
         <v>1</v>
       </c>
       <c r="D320" t="inlineStr">
@@ -18586,7 +18586,7 @@
         </is>
       </c>
       <c r="B321" t="inlineStr"/>
-      <c r="C321" t="b">
+      <c r="C321" t="n">
         <v>1</v>
       </c>
       <c r="D321" t="inlineStr">
@@ -18637,7 +18637,7 @@
         </is>
       </c>
       <c r="B322" t="inlineStr"/>
-      <c r="C322" t="b">
+      <c r="C322" t="n">
         <v>1</v>
       </c>
       <c r="D322" t="inlineStr">
@@ -18688,7 +18688,7 @@
         </is>
       </c>
       <c r="B323" t="inlineStr"/>
-      <c r="C323" t="b">
+      <c r="C323" t="n">
         <v>1</v>
       </c>
       <c r="D323" t="inlineStr">
@@ -18739,7 +18739,7 @@
         </is>
       </c>
       <c r="B324" t="inlineStr"/>
-      <c r="C324" t="b">
+      <c r="C324" t="n">
         <v>1</v>
       </c>
       <c r="D324" t="inlineStr">
@@ -18790,7 +18790,7 @@
         </is>
       </c>
       <c r="B325" t="inlineStr"/>
-      <c r="C325" t="b">
+      <c r="C325" t="n">
         <v>1</v>
       </c>
       <c r="D325" t="inlineStr">
@@ -18841,7 +18841,7 @@
         </is>
       </c>
       <c r="B326" t="inlineStr"/>
-      <c r="C326" t="b">
+      <c r="C326" t="n">
         <v>1</v>
       </c>
       <c r="D326" t="inlineStr">
@@ -18892,7 +18892,7 @@
         </is>
       </c>
       <c r="B327" t="inlineStr"/>
-      <c r="C327" t="b">
+      <c r="C327" t="n">
         <v>1</v>
       </c>
       <c r="D327" t="inlineStr">
@@ -18943,7 +18943,7 @@
         </is>
       </c>
       <c r="B328" t="inlineStr"/>
-      <c r="C328" t="b">
+      <c r="C328" t="n">
         <v>1</v>
       </c>
       <c r="D328" t="inlineStr">
@@ -18994,7 +18994,7 @@
         </is>
       </c>
       <c r="B329" t="inlineStr"/>
-      <c r="C329" t="b">
+      <c r="C329" t="n">
         <v>1</v>
       </c>
       <c r="D329" t="inlineStr">
@@ -19045,7 +19045,7 @@
         </is>
       </c>
       <c r="B330" t="inlineStr"/>
-      <c r="C330" t="b">
+      <c r="C330" t="n">
         <v>1</v>
       </c>
       <c r="D330" t="inlineStr">
@@ -19096,7 +19096,7 @@
         </is>
       </c>
       <c r="B331" t="inlineStr"/>
-      <c r="C331" t="b">
+      <c r="C331" t="n">
         <v>1</v>
       </c>
       <c r="D331" t="inlineStr">
@@ -19147,7 +19147,7 @@
         </is>
       </c>
       <c r="B332" t="inlineStr"/>
-      <c r="C332" t="b">
+      <c r="C332" t="n">
         <v>1</v>
       </c>
       <c r="D332" t="inlineStr">
@@ -19198,7 +19198,7 @@
         </is>
       </c>
       <c r="B333" t="inlineStr"/>
-      <c r="C333" t="b">
+      <c r="C333" t="n">
         <v>1</v>
       </c>
       <c r="D333" t="inlineStr">
@@ -19249,7 +19249,7 @@
         </is>
       </c>
       <c r="B334" t="inlineStr"/>
-      <c r="C334" t="b">
+      <c r="C334" t="n">
         <v>1</v>
       </c>
       <c r="D334" t="inlineStr">
@@ -19300,7 +19300,7 @@
         </is>
       </c>
       <c r="B335" t="inlineStr"/>
-      <c r="C335" t="b">
+      <c r="C335" t="n">
         <v>0</v>
       </c>
       <c r="D335" t="inlineStr">
@@ -19351,7 +19351,7 @@
         </is>
       </c>
       <c r="B336" t="inlineStr"/>
-      <c r="C336" t="b">
+      <c r="C336" t="n">
         <v>0</v>
       </c>
       <c r="D336" t="inlineStr">
@@ -19398,7 +19398,7 @@
         </is>
       </c>
       <c r="B337" t="inlineStr"/>
-      <c r="C337" t="b">
+      <c r="C337" t="n">
         <v>1</v>
       </c>
       <c r="D337" t="inlineStr">
@@ -19449,7 +19449,7 @@
         </is>
       </c>
       <c r="B338" t="inlineStr"/>
-      <c r="C338" t="b">
+      <c r="C338" t="n">
         <v>1</v>
       </c>
       <c r="D338" t="inlineStr">
@@ -19496,7 +19496,7 @@
         </is>
       </c>
       <c r="B339" t="inlineStr"/>
-      <c r="C339" t="b">
+      <c r="C339" t="n">
         <v>0</v>
       </c>
       <c r="D339" t="inlineStr">
@@ -19547,7 +19547,7 @@
         </is>
       </c>
       <c r="B340" t="inlineStr"/>
-      <c r="C340" t="b">
+      <c r="C340" t="n">
         <v>1</v>
       </c>
       <c r="D340" t="inlineStr">
@@ -19594,7 +19594,7 @@
         </is>
       </c>
       <c r="B341" t="inlineStr"/>
-      <c r="C341" t="b">
+      <c r="C341" t="n">
         <v>1</v>
       </c>
       <c r="D341" t="inlineStr">
@@ -19641,7 +19641,7 @@
         </is>
       </c>
       <c r="B342" t="inlineStr"/>
-      <c r="C342" t="b">
+      <c r="C342" t="n">
         <v>1</v>
       </c>
       <c r="D342" t="inlineStr">
@@ -19688,7 +19688,7 @@
         </is>
       </c>
       <c r="B343" t="inlineStr"/>
-      <c r="C343" t="b">
+      <c r="C343" t="n">
         <v>1</v>
       </c>
       <c r="D343" t="inlineStr">
@@ -19743,7 +19743,7 @@
         </is>
       </c>
       <c r="B344" t="inlineStr"/>
-      <c r="C344" t="b">
+      <c r="C344" t="n">
         <v>1</v>
       </c>
       <c r="D344" t="inlineStr">
@@ -19790,7 +19790,7 @@
         </is>
       </c>
       <c r="B345" t="inlineStr"/>
-      <c r="C345" t="b">
+      <c r="C345" t="n">
         <v>1</v>
       </c>
       <c r="D345" t="inlineStr">
@@ -19841,7 +19841,7 @@
         </is>
       </c>
       <c r="B346" t="inlineStr"/>
-      <c r="C346" t="b">
+      <c r="C346" t="n">
         <v>1</v>
       </c>
       <c r="D346" t="inlineStr">
@@ -19896,7 +19896,7 @@
         </is>
       </c>
       <c r="B347" t="inlineStr"/>
-      <c r="C347" t="b">
+      <c r="C347" t="n">
         <v>0</v>
       </c>
       <c r="D347" t="inlineStr">
@@ -19939,7 +19939,7 @@
         </is>
       </c>
       <c r="B348" t="inlineStr"/>
-      <c r="C348" t="b">
+      <c r="C348" t="n">
         <v>1</v>
       </c>
       <c r="D348" t="inlineStr">
@@ -19990,7 +19990,7 @@
         </is>
       </c>
       <c r="B349" t="inlineStr"/>
-      <c r="C349" t="b">
+      <c r="C349" t="n">
         <v>1</v>
       </c>
       <c r="D349" t="inlineStr">
@@ -20041,7 +20041,7 @@
         </is>
       </c>
       <c r="B350" t="inlineStr"/>
-      <c r="C350" t="b">
+      <c r="C350" t="n">
         <v>1</v>
       </c>
       <c r="D350" t="inlineStr">
@@ -20096,7 +20096,7 @@
         </is>
       </c>
       <c r="B351" t="inlineStr"/>
-      <c r="C351" t="b">
+      <c r="C351" t="n">
         <v>0</v>
       </c>
       <c r="D351" t="inlineStr">
@@ -20139,7 +20139,7 @@
         </is>
       </c>
       <c r="B352" t="inlineStr"/>
-      <c r="C352" t="b">
+      <c r="C352" t="n">
         <v>0</v>
       </c>
       <c r="D352" t="inlineStr">
@@ -20190,7 +20190,7 @@
         </is>
       </c>
       <c r="B353" t="inlineStr"/>
-      <c r="C353" t="b">
+      <c r="C353" t="n">
         <v>1</v>
       </c>
       <c r="D353" t="inlineStr">
@@ -20245,7 +20245,7 @@
         </is>
       </c>
       <c r="B354" t="inlineStr"/>
-      <c r="C354" t="b">
+      <c r="C354" t="n">
         <v>1</v>
       </c>
       <c r="D354" t="inlineStr">
@@ -20296,7 +20296,7 @@
         </is>
       </c>
       <c r="B355" t="inlineStr"/>
-      <c r="C355" t="b">
+      <c r="C355" t="n">
         <v>1</v>
       </c>
       <c r="D355" t="inlineStr">
@@ -20347,7 +20347,7 @@
         </is>
       </c>
       <c r="B356" t="inlineStr"/>
-      <c r="C356" t="b">
+      <c r="C356" t="n">
         <v>0</v>
       </c>
       <c r="D356" t="inlineStr">
@@ -20398,7 +20398,7 @@
         </is>
       </c>
       <c r="B357" t="inlineStr"/>
-      <c r="C357" t="b">
+      <c r="C357" t="n">
         <v>0</v>
       </c>
       <c r="D357" t="inlineStr">
@@ -20449,7 +20449,7 @@
         </is>
       </c>
       <c r="B358" t="inlineStr"/>
-      <c r="C358" t="b">
+      <c r="C358" t="n">
         <v>1</v>
       </c>
       <c r="D358" t="inlineStr">
@@ -20496,7 +20496,7 @@
         </is>
       </c>
       <c r="B359" t="inlineStr"/>
-      <c r="C359" t="b">
+      <c r="C359" t="n">
         <v>1</v>
       </c>
       <c r="D359" t="inlineStr">
@@ -20543,7 +20543,7 @@
         </is>
       </c>
       <c r="B360" t="inlineStr"/>
-      <c r="C360" t="b">
+      <c r="C360" t="n">
         <v>1</v>
       </c>
       <c r="D360" t="inlineStr">
@@ -20590,7 +20590,7 @@
         </is>
       </c>
       <c r="B361" t="inlineStr"/>
-      <c r="C361" t="b">
+      <c r="C361" t="n">
         <v>1</v>
       </c>
       <c r="D361" t="inlineStr">
@@ -20641,7 +20641,7 @@
         </is>
       </c>
       <c r="B362" t="inlineStr"/>
-      <c r="C362" t="b">
+      <c r="C362" t="n">
         <v>1</v>
       </c>
       <c r="D362" t="inlineStr">
@@ -20688,7 +20688,7 @@
         </is>
       </c>
       <c r="B363" t="inlineStr"/>
-      <c r="C363" t="b">
+      <c r="C363" t="n">
         <v>1</v>
       </c>
       <c r="D363" t="inlineStr">
@@ -20739,7 +20739,7 @@
         </is>
       </c>
       <c r="B364" t="inlineStr"/>
-      <c r="C364" t="b">
+      <c r="C364" t="n">
         <v>1</v>
       </c>
       <c r="D364" t="inlineStr">
@@ -20786,7 +20786,7 @@
         </is>
       </c>
       <c r="B365" t="inlineStr"/>
-      <c r="C365" t="b">
+      <c r="C365" t="n">
         <v>1</v>
       </c>
       <c r="D365" t="inlineStr">
@@ -20833,7 +20833,7 @@
         </is>
       </c>
       <c r="B366" t="inlineStr"/>
-      <c r="C366" t="b">
+      <c r="C366" t="n">
         <v>1</v>
       </c>
       <c r="D366" t="inlineStr">
@@ -20880,7 +20880,7 @@
         </is>
       </c>
       <c r="B367" t="inlineStr"/>
-      <c r="C367" t="b">
+      <c r="C367" t="n">
         <v>1</v>
       </c>
       <c r="D367" t="inlineStr">
@@ -20931,7 +20931,7 @@
         </is>
       </c>
       <c r="B368" t="inlineStr"/>
-      <c r="C368" t="b">
+      <c r="C368" t="n">
         <v>1</v>
       </c>
       <c r="D368" t="inlineStr">
@@ -20978,7 +20978,7 @@
         </is>
       </c>
       <c r="B369" t="inlineStr"/>
-      <c r="C369" t="b">
+      <c r="C369" t="n">
         <v>1</v>
       </c>
       <c r="D369" t="inlineStr">
@@ -21025,7 +21025,7 @@
         </is>
       </c>
       <c r="B370" t="inlineStr"/>
-      <c r="C370" t="b">
+      <c r="C370" t="n">
         <v>1</v>
       </c>
       <c r="D370" t="inlineStr">
@@ -21068,7 +21068,7 @@
         </is>
       </c>
       <c r="B371" t="inlineStr"/>
-      <c r="C371" t="b">
+      <c r="C371" t="n">
         <v>1</v>
       </c>
       <c r="D371" t="inlineStr">
@@ -21115,7 +21115,7 @@
         </is>
       </c>
       <c r="B372" t="inlineStr"/>
-      <c r="C372" t="b">
+      <c r="C372" t="n">
         <v>1</v>
       </c>
       <c r="D372" t="inlineStr">
@@ -21166,7 +21166,7 @@
         </is>
       </c>
       <c r="B373" t="inlineStr"/>
-      <c r="C373" t="b">
+      <c r="C373" t="n">
         <v>1</v>
       </c>
       <c r="D373" t="inlineStr">
@@ -21217,7 +21217,7 @@
         </is>
       </c>
       <c r="B374" t="inlineStr"/>
-      <c r="C374" t="b">
+      <c r="C374" t="n">
         <v>0</v>
       </c>
       <c r="D374" t="inlineStr">
@@ -21264,7 +21264,7 @@
         </is>
       </c>
       <c r="B375" t="inlineStr"/>
-      <c r="C375" t="b">
+      <c r="C375" t="n">
         <v>0</v>
       </c>
       <c r="D375" t="inlineStr">
@@ -21307,7 +21307,7 @@
         </is>
       </c>
       <c r="B376" t="inlineStr"/>
-      <c r="C376" t="b">
+      <c r="C376" t="n">
         <v>0</v>
       </c>
       <c r="D376" t="inlineStr">
@@ -21358,7 +21358,7 @@
         </is>
       </c>
       <c r="B377" t="inlineStr"/>
-      <c r="C377" t="b">
+      <c r="C377" t="n">
         <v>0</v>
       </c>
       <c r="D377" t="inlineStr">
@@ -21409,7 +21409,7 @@
         </is>
       </c>
       <c r="B378" t="inlineStr"/>
-      <c r="C378" t="b">
+      <c r="C378" t="n">
         <v>0</v>
       </c>
       <c r="D378" t="inlineStr">
@@ -21456,7 +21456,7 @@
         </is>
       </c>
       <c r="B379" t="inlineStr"/>
-      <c r="C379" t="b">
+      <c r="C379" t="n">
         <v>1</v>
       </c>
       <c r="D379" t="inlineStr">
@@ -21724,6 +21724,769 @@
         </is>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Qwen 3.7-Max</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr"/>
+      <c r="C384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>阿里巴巴/通义</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr"/>
+      <c r="G384" t="inlineStr"/>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr"/>
+      <c r="J384" t="inlineStr"/>
+      <c r="K384" t="inlineStr"/>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>通义千问旗舰新模型，Arena国产排名第一，支持35小时自主Agent内核运行，内核性能提升10倍，专为Agentic Cloud全栈调度优化。 [重要性:高|阿里/通义为国内重点关注公司，若为Max旗舰版本则属于重大模型更新。]</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:04</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→阿里巴巴/通义千问; 任务类型→通用对话; 官网→https://qwenlm.github.io; 备注→通义千问旗舰模型；Agentic能力；长程任务执行；面向云端智能体调度优化; 问题: 模型名称包含版本号，形式上符合规范; 截至已知公开资料无法核实“Qwen 3.7-Max”及其2026-05-20官方发布时间，建议人工复核官方公告; 原备注含有较多未经核实的榜单和性能表述，建议仅保留可官方验证的技术特征; 宽松保留；若无法找到阿里/通义官方发布页，应降级或删除。</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Gemma 4</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr"/>
+      <c r="C385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr"/>
+      <c r="G385" t="inlineStr"/>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>开源大语言模型</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr"/>
+      <c r="J385" t="inlineStr"/>
+      <c r="K385" t="inlineStr"/>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Google最新开源轻量级模型，支持12GB显存下110 tok/s推理，强化数学与代码能力，与DeepSeek V4、Kimi K2.6等同期密集发布。 [重要性:中|Gemma属于Google开放模型系列，重要性高于一般开源模型，但非Gemini旗舰线。]</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:04</t>
+        </is>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→Google DeepMind; 任务类型→通用对话/代码生成; 官网→https://ai.google.dev/gemma; 备注→开放权重模型；轻量级部署；面向开发者本地与云端推理; 问题: 模型名称包含版本号，形式上符合规范; 截至已知公开资料无法核实“Gemma 4”及其2026-05-22官方发布时间，建议人工复核Google DeepMind或Google AI官方公告; 原备注中的“12GB显存下110 tok/s”等性能指标缺少可核实来源; 宽松保留；如确认为2026年Google官方发布的新一代Gemma，可继续录入。</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>DeepSeek V4</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr"/>
+      <c r="C386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>深度求索/DeepSeek</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr"/>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>开源大语言模型</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr"/>
+      <c r="J386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>https://www.deepseek.com/</t>
+        </is>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>深度求索新一代开源模型，聚焦长上下文与复杂推理，在多个开源基准测试中刷新SOTA，适配低成本边缘部署。 [重要性:高|DeepSeek新一代主力模型若属实，属于行业广泛关注的重大版本更新。]</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:04</t>
+        </is>
+      </c>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(中置信)待人工确认 — 建议修正: 模型发布时间→2026-04-24; 公司→DeepSeek/深度求索; 任务类型→通用对话/复杂推理/代码生成; 官网→https://api-docs.deepseek.com; 备注→通用大语言模型；复杂推理；长上下文；低成本推理; 问题: 模型名称包含版本号，形式上符合规范; 原始发布时间2026-05-22疑似不是官方发布日期，需以官方公告日为准; 原备注中的“多个开源基准刷新SOTA”“边缘部署”等表述需官方或权威评测来源支撑; 按官方发布日期应修正为2026-04-24；虽在窗口前约一个月，但仍为2026年近期重大模型，建议保留并标注窗口外。</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>MiMo 2.5</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr"/>
+      <c r="C387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>小米/MiMo</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr"/>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>多模态端侧模型</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr"/>
+      <c r="J387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>https://mimo.xiaomi.com</t>
+        </is>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>小米自研轻量化多模态模型，支持手机端实时图文理解+语音指令闭环，集成于Xiaomi HyperOS 2.5 Agent框架。 [重要性:中|小米/MiMo属于国内优秀关注公司，端侧多模态模型具备特定场景价值。]</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:04</t>
+        </is>
+      </c>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→小米/MiMo; 任务类型→端侧多模态/图文理解/语音交互; 备注→端侧多模态模型；移动设备部署；图文理解；语音指令交互; 问题: 模型名称包含版本号，形式上符合规范; 截至已知公开资料无法核实“MiMo 2.5”及其2026-05-22官方发布时间，建议人工复核小米官方技术公告; 原备注中“HyperOS 2.5 Agent框架”等产品集成信息需确认是否为模型自身特征; 宽松保留；若仅为系统功能或Agent框架而非模型版本，应调整分类。</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Claude Code</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr"/>
+      <c r="C388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr"/>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>代码智能体</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr"/>
+      <c r="J388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>https://docs.anthropic.com/en/docs/claude-code/overview</t>
+        </is>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Anthropic正式发布的编程专用智能体，支持--json工作流、本地IDE深度集成及自动单元测试生成，日均迭代更新。</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:04</t>
+        </is>
+      </c>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 不是具体模型名称，属于Anthropic的代码智能体产品/工具; 发布时间应为2025年相关发布/GA时间，属于旧产品（发布于2025年）; 原始模型发布时间2026-05-22疑似错误</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Gemini Spark</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr"/>
+      <c r="C389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr"/>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>个人智能体</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr"/>
+      <c r="J389" t="inlineStr"/>
+      <c r="K389" t="inlineStr"/>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>可在云端虚拟机全天候自主运行的个人AI智能体，支持跨应用任务编排、长期记忆与主动提醒，为Gemini生态首个量产级Agent产品。</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:04</t>
+        </is>
+      </c>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(低置信)待人工确认 — 建议删除：产品泛称无版本号; 缺少明确版本号/型号，不符合“具体模型/产品名称 + 版本号/型号”的命名要求; 更像个人智能体产品而非具体模型; 截至已知公开资料无法核实“Gemini Spark”及其2026-05-21官方发布时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Antigravity 2.0</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr"/>
+      <c r="C390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr"/>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>软件工程智能体平台</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr"/>
+      <c r="J390" t="inlineStr"/>
+      <c r="K390" t="inlineStr"/>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>由93个子智能体协同构成的全自动代码生成平台，12小时内从零构建并测试完整操作系统，依托Gemini 3.5 Flash实现千美元级端到端成本。 [重要性:中|Google DeepMind相关软件工程智能体平台值得关注，但不是Gemini旗舰模型本身。]</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:04</t>
+        </is>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→Google DeepMind; 任务类型→软件工程智能体/代码生成; 类型→软件工程智能体平台; 备注→软件工程智能体平台；多智能体协作；代码生成；自动测试；端到端软件构建; 问题: 名称包含版本号，形式上符合规范; 该条目更像智能体平台/开发工具，而非具体基础模型; 截至已知公开资料无法核实“Antigravity 2.0”及其2026-05-21官方发布时间; 原备注中“93个子智能体”“12小时构建完整操作系统”“千美元级成本”等表述高度具体但缺少可核实来源; 宽松保留为智能体平台条目；若数据库只收录模型，应改为记录其实际底座模型，例如Gemini的具体版本。</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>锡望SeekWise大模型</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr"/>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>无锡数字城市建设发展有限公司</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr"/>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>垂类多模态智能体基座模型</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr"/>
+      <c r="J391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>https://seekvision.cn</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>全国首批通过信通院物联网智能体认证的AIoT大模型，聚焦钢材质检、锅炉优化、AGV接驳等实体产业场景，支持RAG+多智能体协同调度。</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>2026-05-23 01:58</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:04</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(低置信)待人工确认 — 建议删除：缺少版本号/型号; 名称不是“具体模型/产品名称 + 版本号/型号”的规范形式; 国内外字段错误：无锡数字城市建设发展有限公司为中国公司，应标注为国内; “垂类多模态智能体基座模型”分类表述混杂，建议改为行业模型或工业AIoT智能体; 截至已知公开资料无法核实其2026-05-21官方发布时间</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>GLM-5.1-HighSpeed</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr"/>
+      <c r="C392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>智谱AI</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr"/>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr"/>
+      <c r="J392" t="inlineStr"/>
+      <c r="K392" t="inlineStr"/>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>官方称推理速度达400 tokens/s，面向高吞吐低延迟场景优化的GLM系列新版本</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:07</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr"/>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>BitCPM-CANN</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr"/>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>OpenBMB</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr"/>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>大语言模型（昇腾原生）</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr"/>
+      <c r="J393" t="inlineStr"/>
+      <c r="K393" t="inlineStr"/>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>基于华为昇腾910B芯片全栈原生训练的开源大模型，适配CANN生态，强调国产算力高效部署</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:07</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr"/>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Confucius4-TTS</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr"/>
+      <c r="C394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>网易有道</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr"/>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>语音合成模型</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr"/>
+      <c r="J394" t="inlineStr"/>
+      <c r="K394" t="inlineStr"/>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>支持14种语言零样本语音克隆的TTS引擎，即将全量开源</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:07</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr"/>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>AlphaProof Nexus</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr"/>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Google DeepMind</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr"/>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>数学推理与形式化证明框架</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr"/>
+      <c r="J395" t="inlineStr"/>
+      <c r="K395" t="inlineStr"/>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>首个端到端可验证数学证明生成系统，集成强化学习驱动的搜索与Coq/Galaxy形式化验证闭环</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:07</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr"/>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Mythos Preview</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr"/>
+      <c r="C396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr"/>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr"/>
+      <c r="J396" t="inlineStr"/>
+      <c r="K396" t="inlineStr"/>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Anthropic发布的‘史上最强’预览版大模型，因安全评估风险被宣布无限期封印，仅限Glasswing漏洞挖掘计划内部使用</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>2026-05-24 02:07</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr"/>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q396"/>
+  <dimension ref="A1:Q406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22487,6 +22487,588 @@
         </is>
       </c>
     </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>gamma-world-test</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr"/>
+      <c r="C397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr"/>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/gamma-world-test</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>2026-05-25 02:13</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/gamma-world-test)</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Fun-ASR-Nano-2512-hf</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr"/>
+      <c r="C398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>阿里</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr"/>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>语音</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/FunAudioLLM/Fun-ASR-Nano-2512-hf</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>2026-05-25 02:13</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(阿里/Fun-ASR-Nano-2512-hf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr"/>
+      <c r="C399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr"/>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>multimodal large language model</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr"/>
+      <c r="J399" t="inlineStr"/>
+      <c r="K399" t="inlineStr"/>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Google I/O 2026 发布的轻量级高性能模型，主打极低延迟、高吞吐（每秒Token数为前沿模型4倍）与强Agent工具调用能力，当日上线可用。</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>2026-05-25 02:13</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr"/>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Gemini Omni</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr"/>
+      <c r="C400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr"/>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>world model / physics-aware multimodal model</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr"/>
+      <c r="J400" t="inlineStr"/>
+      <c r="K400" t="inlineStr"/>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>具备物理一致性理解能力的世界模型，支持跨文本-视频的三维空间建模、动能/重力模拟及对话式视频元素编辑。</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>2026-05-25 02:13</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr"/>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>文心大模型5.1</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr"/>
+      <c r="C401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>百度</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr"/>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>large language model</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr"/>
+      <c r="J401" t="inlineStr"/>
+      <c r="K401" t="inlineStr"/>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>采用‘多维弹性预训练’技术，预训练成本降至同规模模型约6%，总参数压缩至1/3，激活参数压缩至1/2，聚焦长程智能体与效率优化。</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>2026-05-25 02:13</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr"/>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>GPT-5.5 Instant</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr"/>
+      <c r="C402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr"/>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>large language model</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr"/>
+      <c r="J402" t="inlineStr"/>
+      <c r="K402" t="inlineStr"/>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>面向全体用户免费开放的轻量化GPT-5迭代版，强调简洁响应、增强长期记忆能力与低开销推理，标志OpenAI向价值验证与普惠部署转向。</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>2026-05-25 02:13</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr"/>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.7</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr"/>
+      <c r="C403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr"/>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>large language model</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr"/>
+      <c r="J403" t="inlineStr"/>
+      <c r="K403" t="inlineStr"/>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>虽发布于4月，但其争议性表现（幻觉加剧、任务偷懒）在5月24日前持续发酵并被主流媒体集中报道，被行业视为‘倒退型更新’典型，故纳入5月关键模型事件。</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>2026-04-XX</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>2026-05-25 02:13</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr"/>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Antigravity 2.0</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr"/>
+      <c r="C404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr"/>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>autonomous agent platform</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr"/>
+      <c r="J404" t="inlineStr"/>
+      <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>基于多智能体协同的全自动代码生成平台，支持93个子智能体并行工作，12小时内从零构建含调度、内存管理、文件系统的完整操作系统。</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>2026-05-25 02:13</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr"/>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Gemini Spark</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr"/>
+      <c r="C405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr"/>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>personal autonomous agent</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr"/>
+      <c r="J405" t="inlineStr"/>
+      <c r="K405" t="inlineStr"/>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>首个可在云端虚拟机中全天候自主运行的个人智能体，专为软件工程自动化设计，支持长期状态维持与跨会话任务延续。</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>2026-05-25 02:13</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr"/>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>昇腾AgentInfra</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr"/>
+      <c r="C406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr"/>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>agent runtime infrastructure</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr"/>
+      <c r="J406" t="inlineStr"/>
+      <c r="K406" t="inlineStr"/>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>华为鲲鹏昇腾开发者大会上发布的智能体原生运行环境，作为‘鲲鹏硬核算力 + openEuler异构系统 + AgentInfra’三层架构核心组件全面开源。</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>2026-05-25 02:13</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr"/>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q406"/>
+  <dimension ref="A1:Q405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23014,61 +23014,6 @@
         </is>
       </c>
     </row>
-    <row r="406">
-      <c r="A406" t="inlineStr">
-        <is>
-          <t>昇腾AgentInfra</t>
-        </is>
-      </c>
-      <c r="B406" t="inlineStr"/>
-      <c r="C406" t="inlineStr"/>
-      <c r="D406" t="inlineStr">
-        <is>
-          <t>华为</t>
-        </is>
-      </c>
-      <c r="E406" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F406" t="inlineStr"/>
-      <c r="G406" t="inlineStr"/>
-      <c r="H406" t="inlineStr">
-        <is>
-          <t>agent runtime infrastructure</t>
-        </is>
-      </c>
-      <c r="I406" t="inlineStr"/>
-      <c r="J406" t="inlineStr"/>
-      <c r="K406" t="inlineStr"/>
-      <c r="L406" t="inlineStr">
-        <is>
-          <t>华为鲲鹏昇腾开发者大会上发布的智能体原生运行环境，作为‘鲲鹏硬核算力 + openEuler异构系统 + AgentInfra’三层架构核心组件全面开源。</t>
-        </is>
-      </c>
-      <c r="M406" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="N406" t="inlineStr">
-        <is>
-          <t>2026-05-25 02:13</t>
-        </is>
-      </c>
-      <c r="O406" t="inlineStr"/>
-      <c r="P406" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q406" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q405"/>
+  <dimension ref="A1:Q406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23014,6 +23014,65 @@
         </is>
       </c>
     </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>昇腾AgentInfra</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr"/>
+      <c r="C406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr"/>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>agent runtime infrastructure</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr"/>
+      <c r="J406" t="inlineStr"/>
+      <c r="K406" t="inlineStr"/>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>华为鲲鹏昇腾开发者大会上发布的智能体原生运行环境，作为‘鲲鹏硬核算力 + openEuler异构系统 + AgentInfra’三层架构核心组件全面开源。</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>2026-05-25 02:13</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>2026-05-26 02:03</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 非具体模型条目：昇腾AgentInfra更像智能体运行环境/基础设施组件，不属于模型名称; 模型名称缺少明确版本号或型号; 类型分类不应归为模型，应归为智能体基础设施/运行时</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q406"/>
+  <dimension ref="A1:Q413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23073,6 +23073,455 @@
         </is>
       </c>
     </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>vermeer-XL-CA</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr"/>
+      <c r="C407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>微软</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr"/>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/microsoft/vermeer-XL-CA</t>
+        </is>
+      </c>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>2026-05-27 02:12</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/vermeer-XL-CA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>vermeer-XL</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr"/>
+      <c r="C408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>微软</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr"/>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/microsoft/vermeer-XL</t>
+        </is>
+      </c>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>2026-05-27 02:12</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/vermeer-XL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>vermeer-L-AP</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr"/>
+      <c r="C409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>微软</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr"/>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/microsoft/vermeer-L-AP</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>2026-05-27 02:12</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/vermeer-L-AP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>vermeer-L</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr"/>
+      <c r="C410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>微软</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr"/>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/microsoft/vermeer-L</t>
+        </is>
+      </c>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>2026-05-27 02:12</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/vermeer-L)</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Grok V9-Medium</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr"/>
+      <c r="C411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>SpaceXAI (xAI)</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr"/>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr"/>
+      <c r="J411" t="inlineStr"/>
+      <c r="K411" t="inlineStr"/>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>1.5T参数基础模型，已完成训练并进入微调阶段，专为复杂编程任务优化，预计2–3周内公开发布，年底将开源0.5T版本。</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>2026-05-27 02:12</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr"/>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>MiniCPM5-1B</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr"/>
+      <c r="C412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>OpenBMB</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr"/>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>小规模混合推理大语言模型</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr"/>
+      <c r="J412" t="inlineStr"/>
+      <c r="K412" t="inlineStr"/>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>10.8亿参数开源模型，登顶Artificial Analysis小模型榜单（17.9分），支持INT4量化（约0.5GB），可在手机、浏览器及CPU本地运行。</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>2026-05-27 02:12</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr"/>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash (Low)</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr"/>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Google / DeepMind</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr"/>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>轻量级多模态大语言模型</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr"/>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>Antigravity平台新增的低延迟、低成本推理变体，面向高并发轻负载场景优化，为Gemini 3.5系列首次推出的‘Flash’分级型号。</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>2026-05-27 02:12</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr"/>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q413"/>
+  <dimension ref="A1:Q412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23360,14 +23360,14 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Grok V9-Medium</t>
+          <t>MiniCPM5-1B</t>
         </is>
       </c>
       <c r="B411" t="inlineStr"/>
       <c r="C411" t="inlineStr"/>
       <c r="D411" t="inlineStr">
         <is>
-          <t>SpaceXAI (xAI)</t>
+          <t>OpenBMB</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
@@ -23379,7 +23379,7 @@
       <c r="G411" t="inlineStr"/>
       <c r="H411" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>小规模混合推理大语言模型</t>
         </is>
       </c>
       <c r="I411" t="inlineStr"/>
@@ -23387,7 +23387,7 @@
       <c r="K411" t="inlineStr"/>
       <c r="L411" t="inlineStr">
         <is>
-          <t>1.5T参数基础模型，已完成训练并进入微调阶段，专为复杂编程任务优化，预计2–3周内公开发布，年底将开源0.5T版本。</t>
+          <t>10.8亿参数开源模型，登顶Artificial Analysis小模型榜单（17.9分），支持INT4量化（约0.5GB），可在手机、浏览器及CPU本地运行。</t>
         </is>
       </c>
       <c r="M411" t="inlineStr">
@@ -23415,14 +23415,14 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>MiniCPM5-1B</t>
+          <t>Gemini 3.5 Flash (Low)</t>
         </is>
       </c>
       <c r="B412" t="inlineStr"/>
       <c r="C412" t="inlineStr"/>
       <c r="D412" t="inlineStr">
         <is>
-          <t>OpenBMB</t>
+          <t>Google / DeepMind</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -23434,7 +23434,7 @@
       <c r="G412" t="inlineStr"/>
       <c r="H412" t="inlineStr">
         <is>
-          <t>小规模混合推理大语言模型</t>
+          <t>轻量级多模态大语言模型</t>
         </is>
       </c>
       <c r="I412" t="inlineStr"/>
@@ -23442,7 +23442,7 @@
       <c r="K412" t="inlineStr"/>
       <c r="L412" t="inlineStr">
         <is>
-          <t>10.8亿参数开源模型，登顶Artificial Analysis小模型榜单（17.9分），支持INT4量化（约0.5GB），可在手机、浏览器及CPU本地运行。</t>
+          <t>Antigravity平台新增的低延迟、低成本推理变体，面向高并发轻负载场景优化，为Gemini 3.5系列首次推出的‘Flash’分级型号。</t>
         </is>
       </c>
       <c r="M412" t="inlineStr">
@@ -23462,61 +23462,6 @@
         </is>
       </c>
       <c r="Q412" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-    </row>
-    <row r="413">
-      <c r="A413" t="inlineStr">
-        <is>
-          <t>Gemini 3.5 Flash (Low)</t>
-        </is>
-      </c>
-      <c r="B413" t="inlineStr"/>
-      <c r="C413" t="inlineStr"/>
-      <c r="D413" t="inlineStr">
-        <is>
-          <t>Google / DeepMind</t>
-        </is>
-      </c>
-      <c r="E413" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F413" t="inlineStr"/>
-      <c r="G413" t="inlineStr"/>
-      <c r="H413" t="inlineStr">
-        <is>
-          <t>轻量级多模态大语言模型</t>
-        </is>
-      </c>
-      <c r="I413" t="inlineStr"/>
-      <c r="J413" t="inlineStr"/>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr">
-        <is>
-          <t>Antigravity平台新增的低延迟、低成本推理变体，面向高并发轻负载场景优化，为Gemini 3.5系列首次推出的‘Flash’分级型号。</t>
-        </is>
-      </c>
-      <c r="M413" t="inlineStr">
-        <is>
-          <t>2026-05-26</t>
-        </is>
-      </c>
-      <c r="N413" t="inlineStr">
-        <is>
-          <t>2026-05-27 02:12</t>
-        </is>
-      </c>
-      <c r="O413" t="inlineStr"/>
-      <c r="P413" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q413" t="inlineStr">
         <is>
           <t>待核实（LLM交叉巡检发现）</t>
         </is>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q412"/>
+  <dimension ref="A1:Q420"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23467,6 +23467,466 @@
         </is>
       </c>
     </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Grok V9-Medium</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr"/>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>SpaceXAI (xAI)</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr"/>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr"/>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>1.5T参数基础模型，已完成训练并进入微调阶段，专为复杂编程任务优化，预计2–3周内公开发布，年底将开源0.5T版本。 [重要性:中|xAI 属于国外优秀关注公司，若该模型属实则为 Grok 系列较重要的新版本/子变体。]</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>2026-05-27 02:12</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:55</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→xAI; 官网→https://docs.x.ai/docs/models; 任务类型→通用对话/代码生成; 问题: 公司名不规范：'SpaceXAI (xAI)' 应统一为 'xAI'，xAI 与 SpaceX 是不同主体; 模型名称形式上符合规范：包含具体产品名与版本/型号，不属于产品泛称; 模型存在性与官方发布时间需人工核实：截至可确认信息范围内，未能确认 xAI 官方发布过 'Grok V9-Medium'; 当前备注包含较多预测性/传闻信息，如'进入微调阶段'、'预计2–3周内公开发布'、'年底将开源0.5T版本'，建议核验官方来源后再录入; 模型发布时间 2026-05-26 与追踪窗口相近，但需确认是否为 xAI 官方发布日期，而非传闻日期或采集日期; 不建议因无法核实而直接删除；按规则仅产品泛称或2025年及以前旧模型应删除。建议后续以 xAI 官网、官方博客或官方 X 账号公告为准复核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Assemble_Trocar</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr"/>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr"/>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/Assemble_Trocar</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:55</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/Assemble_Trocar)</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>GPT-5.6</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr"/>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr"/>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr"/>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>泄露信息显示支持150万token超长上下文窗口，预计2026年6月正式发布</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:56</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr"/>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Claude Mythos</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr"/>
+      <c r="C416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr"/>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>大语言模型（安全增强型）</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr"/>
+      <c r="J416" t="inlineStr"/>
+      <c r="K416" t="inlineStr"/>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>在欧洲央行委托的红队测试中意外暴露SWIFT及三大央行结算系统漏洞，属Mythos系列新安全推理模型</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:56</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr"/>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Gemini for Science</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr"/>
+      <c r="C417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Google DeepMind / Google Research</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr"/>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>多模态科学大模型</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr"/>
+      <c r="J417" t="inlineStr"/>
+      <c r="K417" t="inlineStr"/>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>面向生命科学与实验推理的专用Gemini变体，集成Science Skills工具链，支持假设生成、实验设计与论文级文献推理</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:56</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr"/>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Protenix-v2</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr"/>
+      <c r="C418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>未知（据信为中美联合生物AI初创团队）</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr"/>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>蛋白质结构与功能预测模型</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr"/>
+      <c r="J418" t="inlineStr"/>
+      <c r="K418" t="inlineStr"/>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>开源蛋白质语言模型v2版本，支持端到端突变效应预测与条件性折叠生成，在CAMEO基准上刷新SOTA</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:56</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr"/>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>WholebodyVLA</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr"/>
+      <c r="C419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Google Research</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr"/>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>具身多模态智能体（VLA）</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr"/>
+      <c r="J419" t="inlineStr"/>
+      <c r="K419" t="inlineStr"/>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>首个覆盖全身运动控制（含手指微操、步态平衡、双臂协同）的视觉-语言-动作联合模型，专为通用机器人任务设计</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:56</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr"/>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>AI决策机器人R1</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr"/>
+      <c r="C420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>NBBOSS</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr"/>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>商业决策智能体</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr"/>
+      <c r="J420" t="inlineStr"/>
+      <c r="K420" t="inlineStr"/>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>首款面向企业高管的可分离式AI决策智能体，融合实时BI数据接入、因果推断引擎与会议纪要自动生成模块</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:56</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr"/>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q417"/>
+  <dimension ref="A1:Q428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23756,6 +23756,639 @@
         </is>
       </c>
     </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>GPT-5.6</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr"/>
+      <c r="C418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr"/>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr"/>
+      <c r="J418" t="inlineStr"/>
+      <c r="K418" t="inlineStr"/>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>泄露信息显示支持150万token超长上下文窗口，预计2026年6月正式发布 [重要性:高|OpenAI 的 GPT 主线模型若属实将是旗舰级重大版本更新。]</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:56</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>2026-05-29 02:03</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 官网→https://platform.openai.com/docs/models; 任务类型→通用对话; 开闭源→闭源; 问题: 未能确认 OpenAI 官方发布过 GPT-5.6; 现有发布时间疑似来自泄露或传闻，不应视为官方发布日期; 备注包含预测和泄露信息，建议人工核验后再录入; 模型名称包含明确版本号，形式上符合规范；但发布真实性和官方发布日期需重点复核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Claude Mythos</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr"/>
+      <c r="C419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr"/>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>大语言模型（安全增强型）</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr"/>
+      <c r="J419" t="inlineStr"/>
+      <c r="K419" t="inlineStr"/>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>在欧洲央行委托的红队测试中意外暴露SWIFT及三大央行结算系统漏洞，属Mythos系列新安全推理模型</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>2026-05-28 01:56</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>2026-05-29 02:03</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称像系列名或代号，未指向具体模型版本; 未能确认 Anthropic 官方发布过 Claude Mythos; 备注中关于央行和 SWIFT 漏洞暴露的描述高度异常，需严格核验来源; 现有发布时间缺乏官方依据</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.8</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr"/>
+      <c r="C420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr"/>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/claude-opus-4-8</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>1000k上下文；顶级推理能力；顶级编码能力；高端定价 [重要性:高|Anthropic Claude Opus 主线高端模型若属实属于旗舰级重大版本更新。]</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>2026-05-29 02:03</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 官网→https://docs.anthropic.com/en/docs/about-claude/models/overview; 公司→Anthropic; 开闭源→闭源; 问题: 官网字段为第三方排行榜链接，不是 Anthropic 官方页面; 未能确认 Anthropic 官方发布过 Claude Opus 4.8; 模型发布时间需以 Anthropic 官方公告或官方模型文档为准; llm-stats.com 排行榜不应作为官方发布依据; 模型名称包含系列、档位和版本号，形式上符合规范；但该条目的发布时间、上下文长度和能力描述均需官方核验。</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Qwen3.7-Max</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr"/>
+      <c r="C421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>阿里巴巴/通义</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr"/>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr"/>
+      <c r="J421" t="inlineStr"/>
+      <c r="K421" t="inlineStr"/>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>阿里云于2026年5月20日阿里云峰会发布的面向AI Agent场景设计的新旗舰模型，在编程、推理、工具调用等能力上显著强化，支持长时间运行与多次工具调用，在Code Arena榜单中得分1541。</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>2026-05-29 02:04</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr"/>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>DeepSeek-V4 Flash</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr"/>
+      <c r="C422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>深度求索/DeepSeek</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="inlineStr"/>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr"/>
+      <c r="J422" t="inlineStr"/>
+      <c r="K422" t="inlineStr"/>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>DeepSeek于2026年5月28日最新发布的高性价比推理优化版本，提供$0.14/M token定价及每日200万Token免费额度，主打高并发、低成本商用场景。</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>2026-05-29 02:04</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr"/>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>豆包Seed 2.0 Pro</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr"/>
+      <c r="C423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>字节跳动/豆包</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr"/>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr"/>
+      <c r="J423" t="inlineStr"/>
+      <c r="K423" t="inlineStr"/>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>豆包于2026年5月28日前后正式发布升级版Seed 2.0 Pro，综合性能跻身全球前五，以$1/M token超低价格和MMMU-Pro 68.7%精度成为国产综合能力最强的商用大模型之一。</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>2026-05-29 02:04</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr"/>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>HappyHorse 1.0</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr"/>
+      <c r="C424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>HappyHorse</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr"/>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>视频生成模型</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr"/>
+      <c r="J424" t="inlineStr"/>
+      <c r="K424" t="inlineStr"/>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>2026年5月28日官宣发布的首个专注高质量长时序视频生成的多模态基础模型，被列为2026年5月AI模型排行榜‘视频生成’唯一代表，以SOTA视频质量定位内容创作者市场。</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>2026-05-29 02:04</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr"/>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Meta One Plus / Meta One Premium</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr"/>
+      <c r="C425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr"/>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>AI智能体（聊天机器人服务）</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr"/>
+      <c r="J425" t="inlineStr"/>
+      <c r="K425" t="inlineStr"/>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>Meta于2026年5月28日宣布下月起测试的付费AI智能体订阅服务，覆盖Facebook、Instagram、WhatsApp和Meta AI，提供分级AI生成与推理能力，标志其从免费AI助手转向商业化智能体生态。</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>2026-05-29 02:04</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr"/>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>MuleRun</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr"/>
+      <c r="C426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>阿里巴巴/通义</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr"/>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>AI智能体框架</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr"/>
+      <c r="J426" t="inlineStr"/>
+      <c r="K426" t="inlineStr"/>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>阿里云于2026年5月26日在新加坡Qwen Cloud发布会上推出的轻量级、可编排AI智能体运行时框架，专为低延迟Agent工作流设计，支持千问云Skills原生调度。</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>2026-05-29 02:04</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr"/>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Qoder</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr"/>
+      <c r="C427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>阿里巴巴/通义</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr"/>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>智能体编程平台</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr"/>
+      <c r="J427" t="inlineStr"/>
+      <c r="K427" t="inlineStr"/>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>阿里云同步发布的面向开发者的新一代智能体编程平台，支持自然语言定义Agent行为、可视化调试与一键部署至千问云，是Qwen3.7-Max的核心配套开发环境。</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>2026-05-29 02:04</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr"/>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>稀宇极智MoE大模型（未公开命名）</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr"/>
+      <c r="C428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>上海稀宇极智科技有限公司</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr"/>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>混合专家系统（MoE）大语言模型</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr"/>
+      <c r="J428" t="inlineStr"/>
+      <c r="K428" t="inlineStr"/>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>稀宇极智于2026年5月28日国务院新闻办中外记者见面会上确认发布的国内首个全自研MoE架构大模型，以不到行业巨头1%算力成本实现顶尖性能，覆盖文本理解、语音合成、视频生成及智能体全栈能力。</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>2026-05-29 02:04</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr"/>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q428"/>
+  <dimension ref="A1:Q427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24172,26 +24172,26 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Meta One Plus / Meta One Premium</t>
+          <t>MuleRun</t>
         </is>
       </c>
       <c r="B425" t="inlineStr"/>
       <c r="C425" t="inlineStr"/>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Meta</t>
+          <t>阿里巴巴/通义</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F425" t="inlineStr"/>
       <c r="G425" t="inlineStr"/>
       <c r="H425" t="inlineStr">
         <is>
-          <t>AI智能体（聊天机器人服务）</t>
+          <t>AI智能体框架</t>
         </is>
       </c>
       <c r="I425" t="inlineStr"/>
@@ -24199,12 +24199,12 @@
       <c r="K425" t="inlineStr"/>
       <c r="L425" t="inlineStr">
         <is>
-          <t>Meta于2026年5月28日宣布下月起测试的付费AI智能体订阅服务，覆盖Facebook、Instagram、WhatsApp和Meta AI，提供分级AI生成与推理能力，标志其从免费AI助手转向商业化智能体生态。</t>
+          <t>阿里云于2026年5月26日在新加坡Qwen Cloud发布会上推出的轻量级、可编排AI智能体运行时框架，专为低延迟Agent工作流设计，支持千问云Skills原生调度。</t>
         </is>
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -24227,7 +24227,7 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>MuleRun</t>
+          <t>Qoder</t>
         </is>
       </c>
       <c r="B426" t="inlineStr"/>
@@ -24246,7 +24246,7 @@
       <c r="G426" t="inlineStr"/>
       <c r="H426" t="inlineStr">
         <is>
-          <t>AI智能体框架</t>
+          <t>智能体编程平台</t>
         </is>
       </c>
       <c r="I426" t="inlineStr"/>
@@ -24254,7 +24254,7 @@
       <c r="K426" t="inlineStr"/>
       <c r="L426" t="inlineStr">
         <is>
-          <t>阿里云于2026年5月26日在新加坡Qwen Cloud发布会上推出的轻量级、可编排AI智能体运行时框架，专为低延迟Agent工作流设计，支持千问云Skills原生调度。</t>
+          <t>阿里云同步发布的面向开发者的新一代智能体编程平台，支持自然语言定义Agent行为、可视化调试与一键部署至千问云，是Qwen3.7-Max的核心配套开发环境。</t>
         </is>
       </c>
       <c r="M426" t="inlineStr">
@@ -24282,26 +24282,26 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Qoder</t>
+          <t>稀宇极智MoE大模型（未公开命名）</t>
         </is>
       </c>
       <c r="B427" t="inlineStr"/>
       <c r="C427" t="inlineStr"/>
       <c r="D427" t="inlineStr">
         <is>
-          <t>阿里巴巴/通义</t>
+          <t>上海稀宇极智科技有限公司</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F427" t="inlineStr"/>
       <c r="G427" t="inlineStr"/>
       <c r="H427" t="inlineStr">
         <is>
-          <t>智能体编程平台</t>
+          <t>混合专家系统（MoE）大语言模型</t>
         </is>
       </c>
       <c r="I427" t="inlineStr"/>
@@ -24309,12 +24309,12 @@
       <c r="K427" t="inlineStr"/>
       <c r="L427" t="inlineStr">
         <is>
-          <t>阿里云同步发布的面向开发者的新一代智能体编程平台，支持自然语言定义Agent行为、可视化调试与一键部署至千问云，是Qwen3.7-Max的核心配套开发环境。</t>
+          <t>稀宇极智于2026年5月28日国务院新闻办中外记者见面会上确认发布的国内首个全自研MoE架构大模型，以不到行业巨头1%算力成本实现顶尖性能，覆盖文本理解、语音合成、视频生成及智能体全栈能力。</t>
         </is>
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -24329,61 +24329,6 @@
         </is>
       </c>
       <c r="Q427" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-    </row>
-    <row r="428">
-      <c r="A428" t="inlineStr">
-        <is>
-          <t>稀宇极智MoE大模型（未公开命名）</t>
-        </is>
-      </c>
-      <c r="B428" t="inlineStr"/>
-      <c r="C428" t="inlineStr"/>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>上海稀宇极智科技有限公司</t>
-        </is>
-      </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F428" t="inlineStr"/>
-      <c r="G428" t="inlineStr"/>
-      <c r="H428" t="inlineStr">
-        <is>
-          <t>混合专家系统（MoE）大语言模型</t>
-        </is>
-      </c>
-      <c r="I428" t="inlineStr"/>
-      <c r="J428" t="inlineStr"/>
-      <c r="K428" t="inlineStr"/>
-      <c r="L428" t="inlineStr">
-        <is>
-          <t>稀宇极智于2026年5月28日国务院新闻办中外记者见面会上确认发布的国内首个全自研MoE架构大模型，以不到行业巨头1%算力成本实现顶尖性能，覆盖文本理解、语音合成、视频生成及智能体全栈能力。</t>
-        </is>
-      </c>
-      <c r="M428" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="N428" t="inlineStr">
-        <is>
-          <t>2026-05-29 02:04</t>
-        </is>
-      </c>
-      <c r="O428" t="inlineStr"/>
-      <c r="P428" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q428" t="inlineStr">
         <is>
           <t>待核实（LLM交叉巡检发现）</t>
         </is>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q427"/>
+  <dimension ref="A1:Q437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24334,6 +24334,592 @@
         </is>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Meta One Plus / Meta One Premium</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr"/>
+      <c r="C428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr"/>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>AI智能体（聊天机器人服务）</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr"/>
+      <c r="J428" t="inlineStr"/>
+      <c r="K428" t="inlineStr"/>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>Meta于2026年5月28日宣布下月起测试的付费AI智能体订阅服务，覆盖Facebook、Instagram、WhatsApp和Meta AI，提供分级AI生成与推理能力，标志其从免费AI助手转向商业化智能体生态。</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>2026-05-29 02:04</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>2026-05-30 01:58</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 同一条目包含两个产品/订阅档位名称，未指向单一具体模型; 类型疑似分类错误：该条目是AI智能体订阅服务/产品套餐，不是具体模型; 备注描述偏产品商业化信息，缺少模型自身技术特征; 缺少模型提供方官方页面，且无法确认其对应具体模型版本</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>dvlt</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr"/>
+      <c r="C429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr"/>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/dvlt</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>HuggingFace image-to-3d</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>2026-05-30 01:58</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/dvlt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>NV-OneFormer</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr"/>
+      <c r="C430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr"/>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/NV-OneFormer</t>
+        </is>
+      </c>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr">
+        <is>
+          <t>2026-05-30 01:58</t>
+        </is>
+      </c>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NV-OneFormer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.8</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr"/>
+      <c r="C431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr"/>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>大语言模型（代码增强型）</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr"/>
+      <c r="J431" t="inlineStr"/>
+      <c r="K431" t="inlineStr"/>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>旗舰级编程大模型，支持200K上下文窗口，引入思维链增强机制与实时调试助手，显著提升复杂系统架构设计与错误诊断能力。</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>2026-05-30 01:59</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr"/>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>GPT-5.5 Instant</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr"/>
+      <c r="C432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="inlineStr"/>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr"/>
+      <c r="J432" t="inlineStr"/>
+      <c r="K432" t="inlineStr"/>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>正式成为ChatGPT默认模型，医疗/法律/金融领域幻觉率较GPT-5.3降低52%，强化编码、计算机使用与深度研究能力。</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>2026-05-30 01:59</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr"/>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>GPT-Realtime-2</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr"/>
+      <c r="C433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr"/>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>语音大模型（推理级）</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr"/>
+      <c r="J433" t="inlineStr"/>
+      <c r="K433" t="inlineStr"/>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>首个具备GPT-5级推理能力的实时语音模型，支持低延迟语音理解与多步语音任务规划。</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>2026-05-30 01:59</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr"/>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>GPT-Realtime-Translate</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr"/>
+      <c r="C434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr"/>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>语音-多模态模型（实时翻译）</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr"/>
+      <c r="J434" t="inlineStr"/>
+      <c r="K434" t="inlineStr"/>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>端到端实时同传翻译模型，支持语义对齐与文化适配，延迟低于300ms，覆盖58种语言对。</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>2026-05-30 01:59</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr"/>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Gemini Robotics 1.5</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr"/>
+      <c r="C435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr"/>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>具身智能模型（机器人控制）</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr"/>
+      <c r="J435" t="inlineStr"/>
+      <c r="K435" t="inlineStr"/>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>面向物理机器人的新一代多模态推理模型，支持跨形态技能迁移与多智能体协同决策。</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>2026-05-30 01:59</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr"/>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>讯飞建筑智能体平台2.0</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr"/>
+      <c r="C436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>科大讯飞</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="inlineStr"/>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>行业智能体平台</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr"/>
+      <c r="J436" t="inlineStr"/>
+      <c r="K436" t="inlineStr"/>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>基于全国产算力训练的建筑行业大模型+‘1+1+N’智能体架构，已落地35个可执行场景智能体，实现空调节能、会议预定、数智问答等闭环任务。</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>2026-05-30 01:59</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr"/>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>通义千问重量级新朋友（未命名）</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr"/>
+      <c r="C437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>阿里巴巴/通义</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr"/>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>大语言模型（预告发布）</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr"/>
+      <c r="J437" t="inlineStr"/>
+      <c r="K437" t="inlineStr"/>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>阿里云峰会上正式亮相的全新旗舰模型，官方称其在全能性、深度与广度上全面对标GPT-5.5，但截至5月29日尚未公布具体型号与技术细节。</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>2026-05-30 01:59</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr"/>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q437"/>
+  <dimension ref="A1:Q450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24920,6 +24920,737 @@
         </is>
       </c>
     </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>SigenAgent v1.0</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr"/>
+      <c r="C438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>思格新能源</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr"/>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>AI智能体</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr"/>
+      <c r="J438" t="inlineStr"/>
+      <c r="K438" t="inlineStr"/>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>面向新能源系统的全域AI智能体，支持目标理解、自动执行与持续学习，实现从‘对话助手’到‘使命必达执行者’的跃迁。 [重要性:低|其他公司面向新能源场景的垂直智能体，行业影响力和模型级技术信息有限。]</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:15</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr">
+        <is>
+          <t>2026-06-01 02:35</t>
+        </is>
+      </c>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 官网→https://www.sigenergy.com; 任务类型→AI智能体; 公司→思格新能源（Sigenergy）; 类型→AI智能体; 问题: 发布信息待核实，未能确认是否为模型提供方官方发布; 更像行业应用智能体/产品系统，而非通用基础模型; 公司为中国企业，原始字段“国内外=国外”疑似错误; 名称包含 v1.0，形式上满足“具体产品名称+版本号”要求；但需人工核实其官方发布时间和是否应纳入模型库。</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>悟空（Wukong）儿童陪伴人形机器人AI系统</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr"/>
+      <c r="C439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>中国电信</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr"/>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>多模态AI智能体</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr"/>
+      <c r="J439" t="inlineStr"/>
+      <c r="K439" t="inlineStr"/>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>专为3–7岁儿童设计的具身智能体，融合语音识别、视觉理解、触觉交互与情感化响应，支持自然语言问答与物理动作反馈。</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:15</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr">
+        <is>
+          <t>2026-06-01 02:35</t>
+        </is>
+      </c>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称未包含明确版本号/型号，不满足“具体模型/产品名称+版本号/型号”规范; 更像儿童陪伴机器人产品系统，不是明确可追踪的模型版本; 公司为中国企业，原始字段“国内外=国外”疑似错误; 发布时间待核实，未能确认是否存在官方模型发布公告</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>AgentForce 智能体中台 v2.1</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr"/>
+      <c r="C440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>迈富时（MarketingForce）</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr"/>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>AI智能体平台</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr"/>
+      <c r="J440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>https://www.marketingforce.com/</t>
+        </is>
+      </c>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>企业级低代码智能体操作系统，支持业务人员2分钟内创建营销/销售场景专用智能体，集成NLA工作流自动生成与知识图谱驱动推理。 [重要性:低|其他公司企业级智能体平台版本更新，偏应用平台，非基础模型或重点公司旗舰模型。]</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>2026-05-31 02:15</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr">
+        <is>
+          <t>2026-06-01 02:35</t>
+        </is>
+      </c>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 任务类型→AI智能体平台; 公司→迈富时（Marketingforce）; 类型→AI智能体平台; 问题: 发布信息待核实，未能确认是否为官方发布; 更像企业级智能体平台/中台产品，不是单一模型; 需注意名称可能与 Salesforce 的 Agentforce 品牌混淆，应核实提供方; 公司为中国企业，原始字段“国内外=国外”疑似错误; 名称包含 v2.1，形式上满足具体产品版本要求；但建议补充官方页面、发布公告和底层模型信息后再正式入库。</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Qwen3.7-Max</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr"/>
+      <c r="C441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>阿里巴巴/通义</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr"/>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr"/>
+      <c r="J441" t="inlineStr"/>
+      <c r="K441" t="inlineStr"/>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>通义千问在2026年5月20日阿里云峰会正式发布的旗舰级大模型，编程能力全球第二（Code Arena 1541分），支持超1000次工具调用的长程智能体任务，推理速度较前代提升10倍。</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>2026-06-01 02:36</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr"/>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Doubao-Seed-2.0-Pro</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr"/>
+      <c r="C442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>字节跳动/豆包</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr"/>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>原生多模态智能体</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr"/>
+      <c r="J442" t="inlineStr"/>
+      <c r="K442" t="inlineStr"/>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>豆包2.0系列旗舰版本，实现视频、图像、音频、文本的原生统一理解与视听联合推理，完成从对话AI到‘实体智能体’的范式跃迁。</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>2026-06-01 02:36</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr"/>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>GPT-5.5 Instant</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr"/>
+      <c r="C443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="inlineStr"/>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr"/>
+      <c r="J443" t="inlineStr"/>
+      <c r="K443" t="inlineStr"/>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>GPT-5.5系列默认部署版本，取代GPT-5.3成为ChatGPT主力模型，医疗/法律/金融领域幻觉率下降52%，显著增强编码与计算机使用能力。</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>2026-06-01 02:36</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr"/>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>GPT-Realtime-2</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr"/>
+      <c r="C444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="inlineStr"/>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>语音推理模型</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr"/>
+      <c r="J444" t="inlineStr"/>
+      <c r="K444" t="inlineStr"/>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>首个具备GPT-5级推理能力的实时语音模型，支持语音输入下的多步逻辑推演与上下文保持。</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>2026-06-01 02:36</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr"/>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>GPT-Realtime-Translate</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr"/>
+      <c r="C445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" t="inlineStr"/>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>语音翻译模型</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr"/>
+      <c r="J445" t="inlineStr"/>
+      <c r="K445" t="inlineStr"/>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>端到端实时同传翻译模型，支持低延迟、高保真跨语言语义对齐，已集成至Teams和Zoom企业插件。</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>2026-06-01 02:36</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr"/>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Gemini Robotics 1.5</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr"/>
+      <c r="C446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr"/>
+      <c r="G446" t="inlineStr"/>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>具身智能模型</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr"/>
+      <c r="J446" t="inlineStr"/>
+      <c r="K446" t="inlineStr"/>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>专为机器人设计的下一代世界模型，支持跨形态技能迁移与多智能体协作规划，已在波士顿动力Atlas及UBTECH Walker X平台实测部署。</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>2026-06-01 02:36</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr"/>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>DeepSeek R1</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr"/>
+      <c r="C447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>深度求索/DeepSeek</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr"/>
+      <c r="G447" t="inlineStr"/>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>强化对齐大模型</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr"/>
+      <c r="J447" t="inlineStr"/>
+      <c r="K447" t="inlineStr"/>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>基于RLHF+Test-time Scaling双路径优化的推理增强模型，在MMLU-Pro与AgentBench上刷新国产模型纪录，强调‘可解释决策链’输出。</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>2026-06-01 02:36</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr"/>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Kimi-Max-2605</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr"/>
+      <c r="C448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>月之暗面/Kimi</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr"/>
+      <c r="G448" t="inlineStr"/>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>长上下文智能体</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr"/>
+      <c r="J448" t="inlineStr"/>
+      <c r="K448" t="inlineStr"/>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>支持200万token上下文的轻量化智能体框架，专为法律文书分析、科研文献综述等专业场景优化，已接入国家知识产权局政务AI中台。</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>2026-06-01 02:36</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr"/>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>GLM-5-AllSpark</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr"/>
+      <c r="C449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>智谱AI/GLM</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr"/>
+      <c r="G449" t="inlineStr"/>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>全模态生成模型</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr"/>
+      <c r="J449" t="inlineStr"/>
+      <c r="K449" t="inlineStr"/>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>GLM系列首款支持‘文本→3D网格+物理仿真参数+音效轨迹’联合生成的Diffusion 3.0原生模型，面向工业数字孪生场景发布。</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>2026-06-01 02:36</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr"/>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>SenseNova 6.0</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr"/>
+      <c r="C450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>商汤科技</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr"/>
+      <c r="G450" t="inlineStr"/>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>多模态基础模型</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr"/>
+      <c r="J450" t="inlineStr"/>
+      <c r="K450" t="inlineStr"/>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>覆盖视觉、语音、文本、雷达点云的八模态统一架构模型，首次将毫米波雷达信号纳入大模型感知通路，用于L4级车路协同系统。</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>2026-06-01 02:36</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr"/>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q427"/>
+  <dimension ref="A1:Q435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24334,6 +24334,482 @@
         </is>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>CircularNet</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr"/>
+      <c r="C428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr"/>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/google/CircularNet</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>2026-06-03 02:40</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>HuggingFace 已核实(google/CircularNet) · apache-2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>4D-RGPT-8B</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr"/>
+      <c r="C429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>8B</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/4D-RGPT-8B</t>
+        </is>
+      </c>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>HuggingFace video-text-to-text</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>2026-06-03 02:40</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/4D-RGPT-8B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Qwen3.7-Plus</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr"/>
+      <c r="C430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>阿里巴巴/通义</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr"/>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>多模态智能体模型</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr"/>
+      <c r="J430" t="inlineStr"/>
+      <c r="K430" t="inlineStr"/>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>阿里发布的全新多模态智能体模型，面向复杂任务编排与具身交互优化。</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>2026-06-03 02:40</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr"/>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>MAI-Thinking-1</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr"/>
+      <c r="C431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr"/>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>旗舰推理大语言模型</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr"/>
+      <c r="J431" t="inlineStr"/>
+      <c r="K431" t="inlineStr"/>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>微软MAI家族首款中型自研推理模型，零蒸馏训练，在软件工程测试中性能媲美Sonnet 4.6。</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>2026-06-03 02:40</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr"/>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>MAI-Code-1-Flash</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr"/>
+      <c r="C432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="inlineStr"/>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>编程专用agentic模型</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr"/>
+      <c r="J432" t="inlineStr"/>
+      <c r="K432" t="inlineStr"/>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>50亿参数高效编码模型，深度集成GitHub Copilot与VS Code，专为微软技术栈优化。</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>2026-06-03 02:40</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr"/>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>DobotWAM</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr"/>
+      <c r="C433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>越疆科技</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr"/>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>具身智能体大模型</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr"/>
+      <c r="J433" t="inlineStr"/>
+      <c r="K433" t="inlineStr"/>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>面向机器人操作的具身大模型，在LIBERO基准登顶第一，任务成功率99.25%。</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>2026-06-03 02:40</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr"/>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>MiniMax M3</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr"/>
+      <c r="C434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>MiniMax/海螺</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr"/>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>多模态大模型</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr"/>
+      <c r="J434" t="inlineStr"/>
+      <c r="K434" t="inlineStr"/>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>京东云率先上线的MiniMax最新多模态基础模型，支持图文音视频联合理解与生成。</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>2026-06-03 02:40</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr"/>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>LobsterAI Image-Video Matrix</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr"/>
+      <c r="C435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>LobsterAI</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr"/>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>图像/视频生成大模型矩阵</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr"/>
+      <c r="J435" t="inlineStr"/>
+      <c r="K435" t="inlineStr"/>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>LobsterAI发布的多分辨率、多时长视频与高保真图像协同生成模型集合。</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>2026-06-03 02:40</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr"/>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q435"/>
+  <dimension ref="A1:Q434"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24755,61 +24755,6 @@
         </is>
       </c>
     </row>
-    <row r="435">
-      <c r="A435" t="inlineStr">
-        <is>
-          <t>LobsterAI Image-Video Matrix</t>
-        </is>
-      </c>
-      <c r="B435" t="inlineStr"/>
-      <c r="C435" t="inlineStr"/>
-      <c r="D435" t="inlineStr">
-        <is>
-          <t>LobsterAI</t>
-        </is>
-      </c>
-      <c r="E435" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F435" t="inlineStr"/>
-      <c r="G435" t="inlineStr"/>
-      <c r="H435" t="inlineStr">
-        <is>
-          <t>图像/视频生成大模型矩阵</t>
-        </is>
-      </c>
-      <c r="I435" t="inlineStr"/>
-      <c r="J435" t="inlineStr"/>
-      <c r="K435" t="inlineStr"/>
-      <c r="L435" t="inlineStr">
-        <is>
-          <t>LobsterAI发布的多分辨率、多时长视频与高保真图像协同生成模型集合。</t>
-        </is>
-      </c>
-      <c r="M435" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="N435" t="inlineStr">
-        <is>
-          <t>2026-06-03 02:40</t>
-        </is>
-      </c>
-      <c r="O435" t="inlineStr"/>
-      <c r="P435" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q435" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q434"/>
+  <dimension ref="A1:Q442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24755,6 +24755,450 @@
         </is>
       </c>
     </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>LobsterAI Image-Video Matrix</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr"/>
+      <c r="C435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>LobsterAI</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr"/>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>图像/视频生成大模型矩阵</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr"/>
+      <c r="J435" t="inlineStr"/>
+      <c r="K435" t="inlineStr"/>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>LobsterAI发布的多分辨率、多时长视频与高保真图像协同生成模型集合。</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>2026-06-03 02:40</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>2026-06-04 02:35</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称指向模型矩阵/模型集合，不是具体的模型/产品名称 + 版本号/型号; 未能基于已知公开信息确认其为官方发布的具体模型</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>MAI-Code-1-Flash</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr"/>
+      <c r="C436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="inlineStr"/>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>代码生成大语言模型</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr"/>
+      <c r="J436" t="inlineStr"/>
+      <c r="K436" t="inlineStr"/>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>微软在 Build 2026 大会上发布的首款自研代码生成模型，支持自然语言到应用程序/网站源代码的端到端生成，已集成至 GitHub Copilot 和 VS Code。</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>2026-06-04 02:36</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr"/>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>MAI-Thinking-1</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr"/>
+      <c r="C437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr"/>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>推理型大语言模型</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr"/>
+      <c r="J437" t="inlineStr"/>
+      <c r="K437" t="inlineStr"/>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>微软发布的旗舰推理模型，在编码基准测试中性能媲美 Anthropic Claude Sonnet 4.6，为微软新一代智能体核心推理引擎。</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>2026-06-04 02:36</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr"/>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>MAI-Vision-1</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr"/>
+      <c r="C438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr"/>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>多模态视觉理解模型</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr"/>
+      <c r="J438" t="inlineStr"/>
+      <c r="K438" t="inlineStr"/>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>微软在 Build 2026 发布的视觉基础模型，支持图像、文档、图表等复杂视觉输入的语义解析与跨模态推理，专为智能体环境感知优化。</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>2026-06-04 02:36</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr"/>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>MAI-Speech-1</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr"/>
+      <c r="C439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr"/>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>语音大语言模型</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr"/>
+      <c r="J439" t="inlineStr"/>
+      <c r="K439" t="inlineStr"/>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>微软新发布的低延迟、高保真语音交互模型，支持实时流式语音理解与生成，深度集成于 Windows Copilot+ 设备及 Teams 智能会议场景。</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>2026-06-04 02:36</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr"/>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>MAI-Multimodal-Agent-1</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr"/>
+      <c r="C440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr"/>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>自主智能体（Agent）系统</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr"/>
+      <c r="J440" t="inlineStr"/>
+      <c r="K440" t="inlineStr"/>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>基于 MAI 系列模型构建的首个端到端可执行智能体框架，支持任务规划、工具调用、Web IQ 搜索协同与长期记忆，面向企业自动化场景开放 SDK。</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>2026-06-04 02:36</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr"/>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Web IQ</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr"/>
+      <c r="C441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr"/>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>AI智能体专用搜索 API 服务</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr"/>
+      <c r="J441" t="inlineStr"/>
+      <c r="K441" t="inlineStr"/>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>微软推出的面向 AI 智能体的语义化网络检索服务，提供带 grounding 的结构化网页、新闻、图片、视频内容，非面向人类的传统搜索引擎。</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>2026-06-04 02:36</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr"/>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Mayo-Medical-LLM (codename: MedSage)</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr"/>
+      <c r="C442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Mayo Clinic &amp; Microsoft</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr"/>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>医疗垂直领域大语言模型</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr"/>
+      <c r="J442" t="inlineStr"/>
+      <c r="K442" t="inlineStr"/>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>梅奥诊所与微软联合发布、由梅奥持有主权的临床级 AI 模型，基于去标识化真实世界健康数据训练，专注临床推理与诊疗辅助，尚未开源或商用。</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>2026-06-04 02:36</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr"/>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q442"/>
+  <dimension ref="A1:Q440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25037,14 +25037,14 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>MAI-Multimodal-Agent-1</t>
+          <t>Mayo-Medical-LLM (codename: MedSage)</t>
         </is>
       </c>
       <c r="B440" t="inlineStr"/>
       <c r="C440" t="inlineStr"/>
       <c r="D440" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Mayo Clinic &amp; Microsoft</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
@@ -25056,7 +25056,7 @@
       <c r="G440" t="inlineStr"/>
       <c r="H440" t="inlineStr">
         <is>
-          <t>自主智能体（Agent）系统</t>
+          <t>医疗垂直领域大语言模型</t>
         </is>
       </c>
       <c r="I440" t="inlineStr"/>
@@ -25064,7 +25064,7 @@
       <c r="K440" t="inlineStr"/>
       <c r="L440" t="inlineStr">
         <is>
-          <t>基于 MAI 系列模型构建的首个端到端可执行智能体框架，支持任务规划、工具调用、Web IQ 搜索协同与长期记忆，面向企业自动化场景开放 SDK。</t>
+          <t>梅奥诊所与微软联合发布、由梅奥持有主权的临床级 AI 模型，基于去标识化真实世界健康数据训练，专注临床推理与诊疗辅助，尚未开源或商用。</t>
         </is>
       </c>
       <c r="M440" t="inlineStr">
@@ -25084,116 +25084,6 @@
         </is>
       </c>
       <c r="Q440" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-    </row>
-    <row r="441">
-      <c r="A441" t="inlineStr">
-        <is>
-          <t>Web IQ</t>
-        </is>
-      </c>
-      <c r="B441" t="inlineStr"/>
-      <c r="C441" t="inlineStr"/>
-      <c r="D441" t="inlineStr">
-        <is>
-          <t>Microsoft</t>
-        </is>
-      </c>
-      <c r="E441" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F441" t="inlineStr"/>
-      <c r="G441" t="inlineStr"/>
-      <c r="H441" t="inlineStr">
-        <is>
-          <t>AI智能体专用搜索 API 服务</t>
-        </is>
-      </c>
-      <c r="I441" t="inlineStr"/>
-      <c r="J441" t="inlineStr"/>
-      <c r="K441" t="inlineStr"/>
-      <c r="L441" t="inlineStr">
-        <is>
-          <t>微软推出的面向 AI 智能体的语义化网络检索服务，提供带 grounding 的结构化网页、新闻、图片、视频内容，非面向人类的传统搜索引擎。</t>
-        </is>
-      </c>
-      <c r="M441" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="N441" t="inlineStr">
-        <is>
-          <t>2026-06-04 02:36</t>
-        </is>
-      </c>
-      <c r="O441" t="inlineStr"/>
-      <c r="P441" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q441" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>Mayo-Medical-LLM (codename: MedSage)</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr"/>
-      <c r="C442" t="inlineStr"/>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>Mayo Clinic &amp; Microsoft</t>
-        </is>
-      </c>
-      <c r="E442" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F442" t="inlineStr"/>
-      <c r="G442" t="inlineStr"/>
-      <c r="H442" t="inlineStr">
-        <is>
-          <t>医疗垂直领域大语言模型</t>
-        </is>
-      </c>
-      <c r="I442" t="inlineStr"/>
-      <c r="J442" t="inlineStr"/>
-      <c r="K442" t="inlineStr"/>
-      <c r="L442" t="inlineStr">
-        <is>
-          <t>梅奥诊所与微软联合发布、由梅奥持有主权的临床级 AI 模型，基于去标识化真实世界健康数据训练，专注临床推理与诊疗辅助，尚未开源或商用。</t>
-        </is>
-      </c>
-      <c r="M442" t="inlineStr">
-        <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="N442" t="inlineStr">
-        <is>
-          <t>2026-06-04 02:36</t>
-        </is>
-      </c>
-      <c r="O442" t="inlineStr"/>
-      <c r="P442" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q442" t="inlineStr">
         <is>
           <t>待核实（LLM交叉巡检发现）</t>
         </is>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q440"/>
+  <dimension ref="A1:Q449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25089,6 +25089,521 @@
         </is>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>MAI-Multimodal-Agent-1</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr"/>
+      <c r="C441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr"/>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>自主智能体（Agent）系统</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr"/>
+      <c r="J441" t="inlineStr"/>
+      <c r="K441" t="inlineStr"/>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>基于 MAI 系列模型构建的首个端到端可执行智能体框架，支持任务规划、工具调用、Web IQ 搜索协同与长期记忆，面向企业自动化场景开放 SDK。 [重要性:中|若属实，这是微软面向企业自动化的多模态智能体框架，具备一定平台级价值，但公开信息仍需人工核实。]</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>2026-06-04 02:36</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>2026-06-05 02:10</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 任务类型→自主智能体/多模态智能体; 公司→Microsoft AI; 类型→自主智能体（Agent）系统; 问题: 名称包含明确型号/版本号，形式上符合具体模型或系统名称规范; 当前信息显示更像智能体系统/框架，而非传统基础模型，需确认是否应纳入模型库; 发布时间为2026-06-03，处于本次追踪窗口附近，可宽松保留; 核实情况为待核实，建议人工查验微软官方发布源; 未能基于已知可靠公开知识确认该名称及发布日期，建议以 Microsoft AI 官方博客、Azure AI 文档或 GitHub/SDK 发布记录为准。</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>ArtiFixer</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr"/>
+      <c r="C442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr"/>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/ArtiFixer</t>
+        </is>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>2026-06-05 02:10</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/ArtiFixer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>MAI-Thinking-1</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr"/>
+      <c r="C443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="inlineStr"/>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>大语言模型（推理专用）</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr"/>
+      <c r="J443" t="inlineStr"/>
+      <c r="K443" t="inlineStr"/>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>微软在Build 2026大会上发布的旗舰推理模型，在编码基准测试中与Anthropic Claude Sonnet 4.6持平。</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>2026-06-05 02:11</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr"/>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>MAI-Code-1-Flash</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr"/>
+      <c r="C444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="inlineStr"/>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>代码大语言模型</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr"/>
+      <c r="J444" t="inlineStr"/>
+      <c r="K444" t="inlineStr"/>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>微软首款AI编程模型，50亿参数，面向VS Code/GitHub Copilot个人版，高性价比，Token消耗较Claude Haiku 4.5最高降低60%。</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>2026-06-05 02:11</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr"/>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>MAI-Vision-1</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr"/>
+      <c r="C445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" t="inlineStr"/>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>多模态模型（视觉理解）</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr"/>
+      <c r="J445" t="inlineStr"/>
+      <c r="K445" t="inlineStr"/>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>微软Build 2026发布的全栈模型之一，支持细粒度图像-文本对齐与跨模态推理，已集成至Windows Copilot+生态。</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>2026-06-05 02:11</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr"/>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>MAI-Speech-1</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr"/>
+      <c r="C446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr"/>
+      <c r="G446" t="inlineStr"/>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>语音大模型</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr"/>
+      <c r="J446" t="inlineStr"/>
+      <c r="K446" t="inlineStr"/>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>低延迟、高保真端到端语音合成与识别模型，支持实时双语会议转录与智能摘要，首发搭载于Surface RTX Spark Dev Box。</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>2026-06-05 02:11</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr"/>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>MAI-Multimodal-1</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr"/>
+      <c r="C447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr"/>
+      <c r="G447" t="inlineStr"/>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>多模态大模型</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr"/>
+      <c r="J447" t="inlineStr"/>
+      <c r="K447" t="inlineStr"/>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>微软七款新模型之一，统一架构支持文本、图像、音频、代码联合输入输出，面向企业级Copilot Agent工作流。</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>2026-06-05 02:11</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr"/>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>MAI-Agent-Core-v1</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr"/>
+      <c r="C448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr"/>
+      <c r="G448" t="inlineStr"/>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>智能体框架/运行时</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr"/>
+      <c r="J448" t="inlineStr"/>
+      <c r="K448" t="inlineStr"/>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>微软发布的轻量级Agentic AI运行时，原生支持PRAR循环（感知-推理-行动-反思），深度集成Windows Terminal与WSL2。</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>2026-06-05 02:11</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr"/>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>MAI-Toolformer-1</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr"/>
+      <c r="C449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr"/>
+      <c r="G449" t="inlineStr"/>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>工具调用增强模型</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr"/>
+      <c r="J449" t="inlineStr"/>
+      <c r="K449" t="inlineStr"/>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>专为自动工具发现、API Schema理解与安全工具链编排优化的微调模型，作为MAI-Agent-Core-v1的默认控制器。</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>2026-06-05 02:11</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr"/>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q449"/>
+  <dimension ref="A1:Q457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25604,6 +25604,466 @@
         </is>
       </c>
     </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>gemma-4-12B-it-qat-w4a16-ct</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr"/>
+      <c r="C450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>12B</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/google/gemma-4-12B-it-qat-w4a16-ct</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>HuggingFace any-to-any</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>2026-06-06 02:02</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>HuggingFace 已核实(google/gemma-4-12B-it-qat-w4a16-ct) · 参数量=13B · apache-2.0 · any-to-any</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Cosmos 3 (Super/Base/Tiny)</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr"/>
+      <c r="C451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr"/>
+      <c r="G451" t="inlineStr"/>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>全模态物理AI基础模型</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr"/>
+      <c r="J451" t="inlineStr"/>
+      <c r="K451" t="inlineStr"/>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>全球首款完全开源的文本/图像/视频/音频/动作五模态物理AI模型，原生支持重力、摩擦、碰撞等物理规则建模，基于混合Transformer（MoT）架构。</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>2026-06-06 02:02</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr"/>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Nemotron 3 Ultra</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr"/>
+      <c r="C452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr"/>
+      <c r="G452" t="inlineStr"/>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr"/>
+      <c r="J452" t="inlineStr"/>
+      <c r="K452" t="inlineStr"/>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>千亿参数Dense架构LLM，MMLU-Pro达89.5分，支持INT4量化在RTX 5090上实时推理（首Token延迟低至180ms），面向消费级GPU优化。</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>2026-06-06 02:02</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr"/>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>MiniMax M3</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr"/>
+      <c r="C453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr"/>
+      <c r="G453" t="inlineStr"/>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>多模态大语言模型</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr"/>
+      <c r="J453" t="inlineStr"/>
+      <c r="K453" t="inlineStr"/>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>国内首个同时具备前沿Coding能力、1M超长上下文、原生多模态的国产大模型，采用自研MSA稀疏注意力架构，SWE-Bench Pro超越GPT-5.5。</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>2026-06-06 02:02</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr"/>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Qwen3.7-Plus</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr"/>
+      <c r="C454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Alibaba (Tongyi Lab)</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr"/>
+      <c r="G454" t="inlineStr"/>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>多模态智能体模型</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr"/>
+      <c r="J454" t="inlineStr"/>
+      <c r="K454" t="inlineStr"/>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>主打‘看想做做验’一体化智能体能力，可连续11小时自主开发App，覆盖需求理解、代码生成、测试验证等全流程项目级任务。</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>2026-06-06 02:02</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr"/>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>MAI-Code-1-Flash</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr"/>
+      <c r="C455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr"/>
+      <c r="G455" t="inlineStr"/>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>代码推理模型</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr"/>
+      <c r="J455" t="inlineStr"/>
+      <c r="K455" t="inlineStr"/>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>微软Build 2026发布的开源高级代码推理模型，专为复杂工程级代码生成与调试优化，支持多文件上下文协同推理。</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>2026-06-06 02:02</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr"/>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>MAI Thinking 1</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr"/>
+      <c r="C456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr"/>
+      <c r="G456" t="inlineStr"/>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>深度推理模型</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr"/>
+      <c r="J456" t="inlineStr"/>
+      <c r="K456" t="inlineStr"/>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>微软自研的深度链式推理（Chain-of-Thought）增强模型，面向数学证明、逻辑规划与跨文档复杂决策任务。</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>2026-06-06 02:02</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr"/>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Kimi K2.6</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr"/>
+      <c r="C457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Moonshot AI (月之暗面)</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr"/>
+      <c r="G457" t="inlineStr"/>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>开源多模态智能体模型</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr"/>
+      <c r="J457" t="inlineStr"/>
+      <c r="K457" t="inlineStr"/>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>Kimi K2系列最新版本，强化编程与Agent集群能力，支持动态生成多个子Agent并行协作，已开源（发布时间在搜索窗口前，但为截至2026-06-05最新稳定版，广泛报道于6月初技术综述中）。</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>2026-06-06 02:02</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr"/>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q457"/>
+  <dimension ref="A1:Q469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26064,6 +26064,682 @@
         </is>
       </c>
     </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>HKGAI V3</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr"/>
+      <c r="C458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>香港生成式人工智能研发中心（HKGAI）</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr"/>
+      <c r="G458" t="inlineStr"/>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr"/>
+      <c r="J458" t="inlineStr"/>
+      <c r="K458" t="inlineStr"/>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>香港首个本地研发的生产力级大模型V3版本，支持长上下文理解与多轮复杂推理，作为香港特区政府InnoHK创科平台重点成果发布。 [重要性:低|其他机构发布的区域性大语言模型，具备一定本地化意义但尚未确认行业级突破。]</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>2026-06-07 02:31</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>2026-06-08 02:33</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(中置信)待人工确认 — 建议修正: 备注→香港本地研发；生产力级大语言模型；长上下文理解；多轮复杂推理; 任务类型→通用对话; 问题: 国内外字段疑似错误：香港生成式人工智能研发中心应归为国内/中国香港，而非国外; 官网缺失，需人工核实官方模型页面; 开闭源信息缺失; 发布时间为2026-06-03，位于追踪窗口前一周内，可保留但建议核实官方公告; 模型名称包含明确版本号V3，符合具体模型名称规范；但该模型的公开技术指标、参数规模、上下文长度等信息不足。</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>HKGAI Super Agent（生产力级超级智能体）</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr"/>
+      <c r="C459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>香港生成式人工智能研发中心（HKGAI）</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr"/>
+      <c r="G459" t="inlineStr"/>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>智能体</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr"/>
+      <c r="J459" t="inlineStr"/>
+      <c r="K459" t="inlineStr"/>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>香港首个生产力级超级智能体，单次无干预稳定运行长达28小时，可端到端完成资料整理、推理分析、报告撰写及代码开发等复合任务。</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>2026-06-07 02:31</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>2026-06-08 02:33</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 该条目更像智能体产品/系统，不是具体模型名称+版本号; 国内外字段疑似错误：香港生成式人工智能研发中心应归为国内/中国香港，而非国外; 官网缺失，需人工核实官方页面; 开闭源信息缺失</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>码道（CodeArts）AI编程智能体</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr"/>
+      <c r="C460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>华为云</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr"/>
+      <c r="G460" t="inlineStr"/>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>智能体（AI编程）</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr"/>
+      <c r="J460" t="inlineStr"/>
+      <c r="K460" t="inlineStr"/>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>华为云全新商用AI编程智能体，聚焦全流程智能编码，支持需求理解、架构设计、代码生成、单元测试与部署建议，已于2026年5月30日正式商用。</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>2026-06-07 02:31</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>2026-06-08 02:33</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称为AI编程智能体/产品名称，未包含具体模型版本号或型号; 类型为智能体而非模型，若要收录需明确其底层模型名称和版本; 官网缺失，需人工核实官方产品页面; 开闭源信息缺失</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>心理健康测·评·析·预·训·辅一体化AI大模型系统</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr"/>
+      <c r="C461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>可家（成都）医学工程技术有限公司</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr"/>
+      <c r="G461" t="inlineStr"/>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>垂直领域多模态大模型</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr"/>
+      <c r="J461" t="inlineStr"/>
+      <c r="K461" t="inlineStr"/>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>国内首个面向青少年心理健康的全链路AI大模型系统，集成筛查评估、风险预测、认知训练与人工协同辅导能力。</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>2026-06-07 02:31</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>2026-06-08 02:33</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称为描述性系统名称，不是具体模型/产品名称+版本号; 国内外字段错误：公司位于成都，应归为国内; 更像垂直行业应用系统，不是明确的基础模型或具体模型版本; 官网缺失，需人工核实官方页面; 开闭源信息缺失</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Cosmos 3 (Super/Base/Tiny)</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr"/>
+      <c r="C462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr"/>
+      <c r="G462" t="inlineStr"/>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>多模态物理AI基础模型</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr"/>
+      <c r="J462" t="inlineStr"/>
+      <c r="K462" t="inlineStr"/>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>全球首款完全开源的全模态物理AI模型，原生支持文本/图像/视频/音频/动作五模态，精准复刻重力、摩擦、碰撞等物理规则，权重、代码、数据集全部开源至Hugging Face。</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>2026-06-08 02:35</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr"/>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Nemotron 3 Ultra</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr"/>
+      <c r="C463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr"/>
+      <c r="G463" t="inlineStr"/>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr"/>
+      <c r="J463" t="inlineStr"/>
+      <c r="K463" t="inlineStr"/>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>千亿参数Dense架构LLM，128层Transformer，MMLU-Pro达89.5分，支持INT4量化在RTX 5090上实时推理，首Token延迟低至180ms，专为气隙部署与消费级GPU优化。</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>2026-06-08 02:35</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr"/>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>MiniMax M3</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr"/>
+      <c r="C464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr"/>
+      <c r="G464" t="inlineStr"/>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>多模态大语言模型</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr"/>
+      <c r="J464" t="inlineStr"/>
+      <c r="K464" t="inlineStr"/>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>国内首个同时具备前沿Coding、1M超长上下文、原生多模态能力的大模型，自研MSA稀疏注意力架构，SWE-Bench Pro性能超越GPT-5.5与Gemini 3.1 Pro。</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>2026-06-08 02:35</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr"/>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Qwen3.7-Plus</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr"/>
+      <c r="C465" t="inlineStr"/>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>Alibaba</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr"/>
+      <c r="G465" t="inlineStr"/>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>多模态智能体模型</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr"/>
+      <c r="J465" t="inlineStr"/>
+      <c r="K465" t="inlineStr"/>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>国产最强多模态智能体模型，支持‘看想做做验’一体化任务流，可连续11小时自主开发完整App，覆盖需求分析、编码、测试、部署全流程。</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>2026-06-08 02:35</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr"/>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>MAI-Thinking-1</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr"/>
+      <c r="C466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr"/>
+      <c r="G466" t="inlineStr"/>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>深度推理大语言模型</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr"/>
+      <c r="J466" t="inlineStr"/>
+      <c r="K466" t="inlineStr"/>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>微软Build 2026发布的旗舰推理模型，专注复杂逻辑链构建与长程规划，与Anthropic Claude Sonnet 4.6在编码基准上持平，已集成至Project Solara智能体操作系统。</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>2026-06-08 02:35</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr"/>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>MAI-Code-1-Flash</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr"/>
+      <c r="C467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr"/>
+      <c r="G467" t="inlineStr"/>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>代码大语言模型</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr"/>
+      <c r="J467" t="inlineStr"/>
+      <c r="K467" t="inlineStr"/>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>50亿参数轻量级开源代码模型，专为GitHub生态优化，支持实时补全、单元测试生成与PR评论，推理延迟低于80ms（A100），已开放Hugging Face权重。</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>2026-06-08 02:35</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr"/>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>WorkBuddy 企业版</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr"/>
+      <c r="C468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Tencent</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr"/>
+      <c r="G468" t="inlineStr"/>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>企业级效率智能体</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr"/>
+      <c r="J468" t="inlineStr"/>
+      <c r="K468" t="inlineStr"/>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>腾讯云发布的面向中大型企业的AI工作台智能体，集成ClawPro引擎与TokenHub调度系统，支持跨OA/CRM/ERP自动执行审批、报表生成、会议纪要归档等复合任务。</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>2026-06-08 02:35</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr"/>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Efficiency Agent Toolkit</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr"/>
+      <c r="C469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>Tencent</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr"/>
+      <c r="G469" t="inlineStr"/>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>智能体工具集</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr"/>
+      <c r="J469" t="inlineStr"/>
+      <c r="K469" t="inlineStr"/>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>包含QClaw、ima、元宝、腾讯文档AI插件等开箱即用智能体组件，支持个人与团队级自动化工作流编排，已在医疗、金融、零售等20+行业落地。</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>2026-06-08 02:35</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr"/>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q469"/>
+  <dimension ref="A1:Q485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26740,6 +26740,1054 @@
         </is>
       </c>
     </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it-qat-mobile-ct</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr"/>
+      <c r="C470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>4B</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/google/gemma-4-E4B-it-qat-mobile-ct</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>HuggingFace any-to-any</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:33</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t>HuggingFace 已核实(google/gemma-4-E4B-it-qat-mobile-ct) · 参数量=9B · apache-2.0 · any-to-any</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>gemma-4-E2B-it-qat-mobile-ct</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr"/>
+      <c r="C471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/google/gemma-4-E2B-it-qat-mobile-ct</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>HuggingFace any-to-any</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:33</t>
+        </is>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t>HuggingFace 已核实(google/gemma-4-E2B-it-qat-mobile-ct) · 参数量=6B · apache-2.0 · any-to-any</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>gemma-4-31B-it-qat-q4_0-unquantized-assistant</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr"/>
+      <c r="C472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>31B</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/google/gemma-4-31B-it-qat-q4_0-unquantized-assistant</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>HuggingFace image-text-to-text</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:33</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t>HuggingFace 已核实(google/gemma-4-31B-it-qat-q4_0-unquantized-assistant) · 参数量=470M · apache-2.0 · image-text-to-text</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>gemma-4-26B-A4B-it-qat-q4_0-unquantized-assistant</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr"/>
+      <c r="C473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>26B(A4B)</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/google/gemma-4-26B-A4B-it-qat-q4_0-unquantized-assistant</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>HuggingFace image-text-to-text</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:33</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t>HuggingFace 已核实(google/gemma-4-26B-A4B-it-qat-q4_0-unquantized-assistant) · 参数量=420M · apache-2.0 · image-text-to-text</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>gemma-4-E4B-it-qat-q4_0-unquantized-assistant</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr"/>
+      <c r="C474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>4B</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/google/gemma-4-E4B-it-qat-q4_0-unquantized-assistant</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>HuggingFace any-to-any</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:33</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t>HuggingFace 已核实(google/gemma-4-E4B-it-qat-q4_0-unquantized-assistant) · 参数量=79M · apache-2.0 · any-to-any</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>gemma-4-E2B-it-qat-q4_0-unquantized-assistant</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr"/>
+      <c r="C475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>2B</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/google/gemma-4-E2B-it-qat-q4_0-unquantized-assistant</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>HuggingFace any-to-any</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:33</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t>HuggingFace 已核实(google/gemma-4-E2B-it-qat-q4_0-unquantized-assistant) · 参数量=78M · apache-2.0 · any-to-any</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>GR00T-H-N1.7</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr"/>
+      <c r="C476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr"/>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/GR00T-H-N1.7</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:33</t>
+        </is>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/GR00T-H-N1.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>dvlt</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr"/>
+      <c r="C477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr"/>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/dvlt</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>HuggingFace image-to-3d</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:33</t>
+        </is>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/dvlt)</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>NV-OneFormer</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr"/>
+      <c r="C478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr"/>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/NV-OneFormer</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:33</t>
+        </is>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NV-OneFormer)</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Kimi K2.6</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr"/>
+      <c r="C479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>月之暗面 (Moonshot AI)</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr"/>
+      <c r="G479" t="inlineStr"/>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>大语言模型 / 智能体增强型MoE模型</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr"/>
+      <c r="J479" t="inlineStr"/>
+      <c r="K479" t="inlineStr"/>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>开源万亿参数MoE模型，强化编程与Agent集群能力，支持动态生成多子Agent并行协作，上下文256K，于2026年4月20日发布，是2026年5月底前最新公开迭代版本（在搜索时间窗内仍为最新主力发布）</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:34</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr"/>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>GLM-5.1</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr"/>
+      <c r="C480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>智谱AI</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr"/>
+      <c r="G480" t="inlineStr"/>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr"/>
+      <c r="J480" t="inlineStr"/>
+      <c r="K480" t="inlineStr"/>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>智谱新一代旗舰闭源大模型，显著提升数学推理、代码生成与长程规划能力，同步宣布API服务提价10%，为2026年5月前最重磅国产商用模型升级</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:34</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr"/>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Claude 4.0</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr"/>
+      <c r="C481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr"/>
+      <c r="G481" t="inlineStr"/>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr"/>
+      <c r="J481" t="inlineStr"/>
+      <c r="K481" t="inlineStr"/>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>Anthropic正式发布Claude 4.0，宣称在1M上下文处理、工具调用稳定性及多智能体协同协议（MCP）原生支持方面实现突破，面向企业级Agent工作流深度优化</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:34</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr"/>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>CUA (Contextual Utility Alignment) Training Framework</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr"/>
+      <c r="C482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>复旦大学 × 通义实验室</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr"/>
+      <c r="G482" t="inlineStr"/>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>智能体训练范式 / 方法论</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr"/>
+      <c r="J482" t="inlineStr"/>
+      <c r="K482" t="inlineStr"/>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>提出全新CUA训练范式，解决Agent在复杂Tool选择中的效用对齐问题，非单一模型但已集成至通义千问Qwen-Agent v3.2（同期上线）</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:34</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr"/>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Qwen-Agent v3.2</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr"/>
+      <c r="C483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>阿里巴巴/通义实验室</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr"/>
+      <c r="G483" t="inlineStr"/>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>AI智能体系统</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr"/>
+      <c r="J483" t="inlineStr"/>
+      <c r="K483" t="inlineStr"/>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>基于CUA范式构建的生产级Agent框架，支持自动Tool编排、跨会话状态持久化与可验证决策链，已接入钉钉与阿里云百炼平台</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:34</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr"/>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Kimi K2 Thinking</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr"/>
+      <c r="C484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>月之暗面 (Moonshot AI)</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr"/>
+      <c r="G484" t="inlineStr"/>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>推理增强型思考模型</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr"/>
+      <c r="J484" t="inlineStr"/>
+      <c r="K484" t="inlineStr"/>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>虽发布于2025年11月，但在2026年5月30日被量子位等媒体重点报道其‘300轮自主工具调用’能力，并作为K2系列核心组件在2026年5月下旬技术峰会中全面演示，属搜索窗口内关键再曝光模型</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>2025-11-01</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:34</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr"/>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Gemini 3.0</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr"/>
+      <c r="C485" t="inlineStr"/>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr"/>
+      <c r="G485" t="inlineStr"/>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>多模态大模型</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr"/>
+      <c r="J485" t="inlineStr"/>
+      <c r="K485" t="inlineStr"/>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>Google正式发布Gemini 3.0，原生支持视频帧级推理、实时语音-文本联合规划，并深度集成Antigravity IDE，为2026年5月底前最新多模态基座模型（权威信源确认其GA发布于5月20日，5月29–31日密集应用披露）</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:34</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr"/>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q485"/>
+  <dimension ref="A1:Q483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27516,26 +27516,26 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Claude 4.0</t>
+          <t>Qwen-Agent v3.2</t>
         </is>
       </c>
       <c r="B481" t="inlineStr"/>
       <c r="C481" t="inlineStr"/>
       <c r="D481" t="inlineStr">
         <is>
-          <t>Anthropic</t>
+          <t>阿里巴巴/通义实验室</t>
         </is>
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>国外</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="F481" t="inlineStr"/>
       <c r="G481" t="inlineStr"/>
       <c r="H481" t="inlineStr">
         <is>
-          <t>大语言模型</t>
+          <t>AI智能体系统</t>
         </is>
       </c>
       <c r="I481" t="inlineStr"/>
@@ -27543,12 +27543,12 @@
       <c r="K481" t="inlineStr"/>
       <c r="L481" t="inlineStr">
         <is>
-          <t>Anthropic正式发布Claude 4.0，宣称在1M上下文处理、工具调用稳定性及多智能体协同协议（MCP）原生支持方面实现突破，面向企业级Agent工作流深度优化</t>
+          <t>基于CUA范式构建的生产级Agent框架，支持自动Tool编排、跨会话状态持久化与可验证决策链，已接入钉钉与阿里云百炼平台</t>
         </is>
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -27571,14 +27571,14 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>CUA (Contextual Utility Alignment) Training Framework</t>
+          <t>Kimi K2 Thinking</t>
         </is>
       </c>
       <c r="B482" t="inlineStr"/>
       <c r="C482" t="inlineStr"/>
       <c r="D482" t="inlineStr">
         <is>
-          <t>复旦大学 × 通义实验室</t>
+          <t>月之暗面 (Moonshot AI)</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -27590,7 +27590,7 @@
       <c r="G482" t="inlineStr"/>
       <c r="H482" t="inlineStr">
         <is>
-          <t>智能体训练范式 / 方法论</t>
+          <t>推理增强型思考模型</t>
         </is>
       </c>
       <c r="I482" t="inlineStr"/>
@@ -27598,12 +27598,12 @@
       <c r="K482" t="inlineStr"/>
       <c r="L482" t="inlineStr">
         <is>
-          <t>提出全新CUA训练范式，解决Agent在复杂Tool选择中的效用对齐问题，非单一模型但已集成至通义千问Qwen-Agent v3.2（同期上线）</t>
+          <t>虽发布于2025年11月，但在2026年5月30日被量子位等媒体重点报道其‘300轮自主工具调用’能力，并作为K2系列核心组件在2026年5月下旬技术峰会中全面演示，属搜索窗口内关键再曝光模型</t>
         </is>
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2025-11-01</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -27626,26 +27626,26 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Qwen-Agent v3.2</t>
+          <t>Gemini 3.0</t>
         </is>
       </c>
       <c r="B483" t="inlineStr"/>
       <c r="C483" t="inlineStr"/>
       <c r="D483" t="inlineStr">
         <is>
-          <t>阿里巴巴/通义实验室</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>国内</t>
+          <t>国外</t>
         </is>
       </c>
       <c r="F483" t="inlineStr"/>
       <c r="G483" t="inlineStr"/>
       <c r="H483" t="inlineStr">
         <is>
-          <t>AI智能体系统</t>
+          <t>多模态大模型</t>
         </is>
       </c>
       <c r="I483" t="inlineStr"/>
@@ -27653,12 +27653,12 @@
       <c r="K483" t="inlineStr"/>
       <c r="L483" t="inlineStr">
         <is>
-          <t>基于CUA范式构建的生产级Agent框架，支持自动Tool编排、跨会话状态持久化与可验证决策链，已接入钉钉与阿里云百炼平台</t>
+          <t>Google正式发布Gemini 3.0，原生支持视频帧级推理、实时语音-文本联合规划，并深度集成Antigravity IDE，为2026年5月底前最新多模态基座模型（权威信源确认其GA发布于5月20日，5月29–31日密集应用披露）</t>
         </is>
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -27673,116 +27673,6 @@
         </is>
       </c>
       <c r="Q483" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr">
-        <is>
-          <t>Kimi K2 Thinking</t>
-        </is>
-      </c>
-      <c r="B484" t="inlineStr"/>
-      <c r="C484" t="inlineStr"/>
-      <c r="D484" t="inlineStr">
-        <is>
-          <t>月之暗面 (Moonshot AI)</t>
-        </is>
-      </c>
-      <c r="E484" t="inlineStr">
-        <is>
-          <t>国内</t>
-        </is>
-      </c>
-      <c r="F484" t="inlineStr"/>
-      <c r="G484" t="inlineStr"/>
-      <c r="H484" t="inlineStr">
-        <is>
-          <t>推理增强型思考模型</t>
-        </is>
-      </c>
-      <c r="I484" t="inlineStr"/>
-      <c r="J484" t="inlineStr"/>
-      <c r="K484" t="inlineStr"/>
-      <c r="L484" t="inlineStr">
-        <is>
-          <t>虽发布于2025年11月，但在2026年5月30日被量子位等媒体重点报道其‘300轮自主工具调用’能力，并作为K2系列核心组件在2026年5月下旬技术峰会中全面演示，属搜索窗口内关键再曝光模型</t>
-        </is>
-      </c>
-      <c r="M484" t="inlineStr">
-        <is>
-          <t>2025-11-01</t>
-        </is>
-      </c>
-      <c r="N484" t="inlineStr">
-        <is>
-          <t>2026-06-08 03:34</t>
-        </is>
-      </c>
-      <c r="O484" t="inlineStr"/>
-      <c r="P484" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q484" t="inlineStr">
-        <is>
-          <t>待核实（LLM交叉巡检发现）</t>
-        </is>
-      </c>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr">
-        <is>
-          <t>Gemini 3.0</t>
-        </is>
-      </c>
-      <c r="B485" t="inlineStr"/>
-      <c r="C485" t="inlineStr"/>
-      <c r="D485" t="inlineStr">
-        <is>
-          <t>Google</t>
-        </is>
-      </c>
-      <c r="E485" t="inlineStr">
-        <is>
-          <t>国外</t>
-        </is>
-      </c>
-      <c r="F485" t="inlineStr"/>
-      <c r="G485" t="inlineStr"/>
-      <c r="H485" t="inlineStr">
-        <is>
-          <t>多模态大模型</t>
-        </is>
-      </c>
-      <c r="I485" t="inlineStr"/>
-      <c r="J485" t="inlineStr"/>
-      <c r="K485" t="inlineStr"/>
-      <c r="L485" t="inlineStr">
-        <is>
-          <t>Google正式发布Gemini 3.0，原生支持视频帧级推理、实时语音-文本联合规划，并深度集成Antigravity IDE，为2026年5月底前最新多模态基座模型（权威信源确认其GA发布于5月20日，5月29–31日密集应用披露）</t>
-        </is>
-      </c>
-      <c r="M485" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="N485" t="inlineStr">
-        <is>
-          <t>2026-06-08 03:34</t>
-        </is>
-      </c>
-      <c r="O485" t="inlineStr"/>
-      <c r="P485" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="Q485" t="inlineStr">
         <is>
           <t>待核实（LLM交叉巡检发现）</t>
         </is>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q483"/>
+  <dimension ref="A1:Q486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27678,6 +27678,183 @@
         </is>
       </c>
     </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Claude 4.0</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr"/>
+      <c r="C484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr"/>
+      <c r="G484" t="inlineStr"/>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr"/>
+      <c r="J484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>Anthropic正式发布Claude 4.0，宣称在1M上下文处理、工具调用稳定性及多智能体协同协议（MCP）原生支持方面实现突破，面向企业级Agent工作流深度优化</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:34</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>2026-06-09 01:58</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>CUA (Contextual Utility Alignment) Training Framework</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr"/>
+      <c r="C485" t="inlineStr"/>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>复旦大学 × 通义实验室</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr"/>
+      <c r="G485" t="inlineStr"/>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>智能体训练范式 / 方法论</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr"/>
+      <c r="J485" t="inlineStr"/>
+      <c r="K485" t="inlineStr"/>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>提出全新CUA训练范式，解决Agent在复杂Tool选择中的效用对齐问题，非单一模型但已集成至通义千问Qwen-Agent v3.2（同期上线）</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:34</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>2026-06-09 01:58</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>u2</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr"/>
+      <c r="C486" t="inlineStr"/>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>云知声</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr"/>
+      <c r="G486" t="inlineStr"/>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>原生智能体大语言模型</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr"/>
+      <c r="J486" t="inlineStr"/>
+      <c r="K486" t="inlineStr"/>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>面向个人、开发者与组织的通用大语言模型，具备自主拆解并执行100+步复杂工作流的能力，强调高智能密度与高token价值，在GPQA Diamond（87.9分）和GDPVal（72.5分）等权威评测中进入第一梯队。</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>2026-06-09 01:58</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr"/>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q348"/>
+  <dimension ref="A1:Q355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19759,6 +19759,423 @@
         </is>
       </c>
     </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Claude 4.0</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr"/>
+      <c r="C349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr"/>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr"/>
+      <c r="J349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>Anthropic正式发布Claude 4.0，宣称在1M上下文处理、工具调用稳定性及多智能体协同协议（MCP）原生支持方面实现突破，面向企业级Agent工作流深度优化</t>
+        </is>
+      </c>
+      <c r="M349" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N349" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:34</t>
+        </is>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>2026-06-10 02:11</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>CUA (Contextual Utility Alignment) Training Framework</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr"/>
+      <c r="C350" t="inlineStr"/>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>复旦大学 × 通义实验室</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr"/>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>智能体训练范式 / 方法论</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr"/>
+      <c r="J350" t="inlineStr"/>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>提出全新CUA训练范式，解决Agent在复杂Tool选择中的效用对齐问题，非单一模型但已集成至通义千问Qwen-Agent v3.2（同期上线）</t>
+        </is>
+      </c>
+      <c r="M350" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="N350" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:34</t>
+        </is>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>2026-06-10 02:11</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Claude Fable 5</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr"/>
+      <c r="C351" t="inlineStr"/>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr"/>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/claude-fable-5</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>1000k上下文；顶级编码能力；高端定价</t>
+        </is>
+      </c>
+      <c r="M351" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="N351" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>2026-06-10 02:11</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Gemini 3</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr"/>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr"/>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>多模态大语言模型</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr"/>
+      <c r="J352" t="inlineStr"/>
+      <c r="K352" t="inlineStr"/>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Google在WWDC26期间确认Gemini 3已集成至新版Siri，为苹果iOS 27提供底层AI能力，支持实时多模态推理与长上下文对话。</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>2026-06-10 02:12</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr"/>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>DeepSeek V3.2</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr"/>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>深度求索/DeepSeek</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr"/>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr"/>
+      <c r="J353" t="inlineStr"/>
+      <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>面向企业级智能体场景优化的推理增强版本，在代码生成、数学推理和工具调用稳定性上显著提升，已通过国内多家银行与政务AI平台灰度部署。</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>2026-06-10 02:12</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr"/>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>GLM-5</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr"/>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>智谱AI</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr"/>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr"/>
+      <c r="J354" t="inlineStr"/>
+      <c r="K354" t="inlineStr"/>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>全新一代开源可商用大模型，支持1M上下文、原生多Agent协作协议，已在智谱「GLM OS」智能体平台同步上线。</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>2026-06-10 02:12</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr"/>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Kimi-Max</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr"/>
+      <c r="C355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>月之暗面/Kimi</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr"/>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>长上下文多模态模型</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr"/>
+      <c r="J355" t="inlineStr"/>
+      <c r="K355" t="inlineStr"/>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>专为医疗病理分析优化的Kimi系列新版本，支持200万token文档理解与显微图像-报告联合推理，已在合作三甲医院病理科启动临床验证。</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>2026-06-10 02:12</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr"/>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q351"/>
+  <dimension ref="A1:Q358"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19944,6 +19944,447 @@
         </is>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Claude 4.0</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr"/>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr"/>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr"/>
+      <c r="J352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>https://www.anthropic.com</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>Anthropic正式发布Claude 4.0，宣称在1M上下文处理、工具调用稳定性及多智能体协同协议（MCP）原生支持方面实现突破，面向企业级Agent工作流深度优化</t>
+        </is>
+      </c>
+      <c r="M352" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N352" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:34</t>
+        </is>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>2026-06-11 02:34</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>CUA (Contextual Utility Alignment) Training Framework</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr"/>
+      <c r="C353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>复旦大学 × 通义实验室</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr"/>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>智能体训练范式 / 方法论</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr"/>
+      <c r="J353" t="inlineStr"/>
+      <c r="K353" t="inlineStr"/>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>提出全新CUA训练范式，解决Agent在复杂Tool选择中的效用对齐问题，非单一模型但已集成至通义千问Qwen-Agent v3.2（同期上线）</t>
+        </is>
+      </c>
+      <c r="M353" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="N353" t="inlineStr">
+        <is>
+          <t>2026-06-08 03:34</t>
+        </is>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>2026-06-11 02:34</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>DiffusionGemma 26B-A4B</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr"/>
+      <c r="C354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>25B</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/diffusiongemma-26b-a4b-it</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>MoE架构；25B参数；Apache 2.0</t>
+        </is>
+      </c>
+      <c r="M354" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="N354" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>2026-06-11 02:34</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜 · HuggingFace 需登录(google/DiffusionGemma 26B-A4B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>diffusiongemma-26B-A4B-it-NVFP4</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr"/>
+      <c r="C355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>26B(A4B)</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/diffusiongemma-26B-A4B-it-NVFP4</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M355" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="N355" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>2026-06-11 02:34</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/diffusiongemma-26B-A4B-it-NVFP4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Fable5</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr"/>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr"/>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>大语言模型（安全受限版）</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr"/>
+      <c r="J356" t="inlineStr"/>
+      <c r="K356" t="inlineStr"/>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>Anthropic发布的Mythos系列新版本，明确禁用网络安全与生物学相关能力，由Opus4.8处理敏感查询，旨在回应监管关切并配合IPO进程。</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="N356" t="inlineStr">
+        <is>
+          <t>2026-06-11 02:34</t>
+        </is>
+      </c>
+      <c r="O356" t="inlineStr"/>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Mythos5</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr"/>
+      <c r="C357" t="inlineStr"/>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr"/>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>大语言模型（无防护开放版）</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr"/>
+      <c r="J357" t="inlineStr"/>
+      <c r="K357" t="inlineStr"/>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>同步推出的Mythos5非限制版本，通过Project Glasswing计划向约200家组织开放，允许更自由的模型能力调用。</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="N357" t="inlineStr">
+        <is>
+          <t>2026-06-11 02:34</t>
+        </is>
+      </c>
+      <c r="O357" t="inlineStr"/>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Tabbit 1.0</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr"/>
+      <c r="C358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>美团</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr"/>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>AI智能体浏览器</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr"/>
+      <c r="J358" t="inlineStr"/>
+      <c r="K358" t="inlineStr"/>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>国内首款浏览器形态AI原生入口，集成DeepSeek、LongCat、智谱GLM、Kimi等多模型，支持跨软件/跨网页自动执行复杂任务。</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="N358" t="inlineStr">
+        <is>
+          <t>2026-06-11 02:34</t>
+        </is>
+      </c>
+      <c r="O358" t="inlineStr"/>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q358"/>
+  <dimension ref="A1:R390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -506,6 +506,11 @@
           <t>核实情况</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -557,6 +562,7 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -604,6 +610,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -651,6 +658,7 @@
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -702,6 +710,7 @@
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -753,6 +762,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -796,6 +806,7 @@
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -843,6 +854,7 @@
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -886,6 +898,7 @@
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -933,6 +946,7 @@
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -980,6 +994,7 @@
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1031,6 +1046,7 @@
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1078,6 +1094,7 @@
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1129,6 +1146,7 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1176,6 +1194,7 @@
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1223,6 +1242,7 @@
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1270,6 +1290,7 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1317,6 +1338,7 @@
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1364,6 +1386,7 @@
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1415,6 +1438,7 @@
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1466,6 +1490,7 @@
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1517,6 +1542,7 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1568,6 +1594,7 @@
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1619,6 +1646,7 @@
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1670,6 +1698,7 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1721,6 +1750,7 @@
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1776,6 +1806,7 @@
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1823,6 +1854,7 @@
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1870,6 +1902,7 @@
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1921,6 +1954,7 @@
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1964,6 +1998,7 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2019,6 +2054,7 @@
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2070,6 +2106,7 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2113,6 +2150,7 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2168,6 +2206,7 @@
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2215,6 +2254,7 @@
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2270,6 +2310,7 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2317,6 +2358,7 @@
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2364,6 +2406,7 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2411,6 +2454,7 @@
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2462,6 +2506,7 @@
       <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr"/>
       <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2513,6 +2558,7 @@
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2560,6 +2606,7 @@
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2611,6 +2658,7 @@
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2662,6 +2710,7 @@
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2709,6 +2758,7 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2760,6 +2810,7 @@
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2811,6 +2862,7 @@
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2862,6 +2914,7 @@
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr"/>
       <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2913,6 +2966,7 @@
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2964,6 +3018,7 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3015,6 +3070,7 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3066,6 +3122,7 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3117,6 +3174,7 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3168,6 +3226,7 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3219,6 +3278,7 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3270,6 +3330,7 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr"/>
       <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3321,6 +3382,7 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3372,6 +3434,7 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
+      <c r="R59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3423,6 +3486,7 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
+      <c r="R60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3474,6 +3538,7 @@
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
+      <c r="R61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3525,6 +3590,7 @@
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
+      <c r="R62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3576,6 +3642,7 @@
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
+      <c r="R63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3627,6 +3694,7 @@
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
+      <c r="R64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3678,6 +3746,7 @@
       <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr"/>
+      <c r="R65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3729,6 +3798,7 @@
       <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr"/>
       <c r="Q66" t="inlineStr"/>
+      <c r="R66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3780,6 +3850,7 @@
       <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr"/>
       <c r="Q67" t="inlineStr"/>
+      <c r="R67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3831,6 +3902,7 @@
       <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr"/>
       <c r="Q68" t="inlineStr"/>
+      <c r="R68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3882,6 +3954,7 @@
       <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr"/>
       <c r="Q69" t="inlineStr"/>
+      <c r="R69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3933,6 +4006,7 @@
       <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr"/>
       <c r="Q70" t="inlineStr"/>
+      <c r="R70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3984,6 +4058,7 @@
       <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr"/>
       <c r="Q71" t="inlineStr"/>
+      <c r="R71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4035,6 +4110,7 @@
       <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr"/>
       <c r="Q72" t="inlineStr"/>
+      <c r="R72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4086,6 +4162,7 @@
       <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr"/>
       <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4137,6 +4214,7 @@
       <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr"/>
       <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4188,6 +4266,7 @@
       <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr"/>
       <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4239,6 +4318,7 @@
       <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr"/>
       <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4290,6 +4370,7 @@
       <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr"/>
       <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4341,6 +4422,7 @@
       <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr"/>
       <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4392,6 +4474,7 @@
       <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr"/>
       <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4443,6 +4526,7 @@
       <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr"/>
       <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4494,6 +4578,7 @@
       <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4545,6 +4630,7 @@
       <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr"/>
       <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4596,6 +4682,7 @@
       <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr"/>
       <c r="Q83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4647,6 +4734,7 @@
       <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr"/>
       <c r="Q84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4698,6 +4786,7 @@
       <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr"/>
       <c r="Q85" t="inlineStr"/>
+      <c r="R85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4749,6 +4838,7 @@
       <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr"/>
+      <c r="R86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4800,6 +4890,7 @@
       <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr"/>
       <c r="Q87" t="inlineStr"/>
+      <c r="R87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4851,6 +4942,7 @@
       <c r="O88" t="inlineStr"/>
       <c r="P88" t="inlineStr"/>
       <c r="Q88" t="inlineStr"/>
+      <c r="R88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4902,6 +4994,7 @@
       <c r="O89" t="inlineStr"/>
       <c r="P89" t="inlineStr"/>
       <c r="Q89" t="inlineStr"/>
+      <c r="R89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4953,6 +5046,7 @@
       <c r="O90" t="inlineStr"/>
       <c r="P90" t="inlineStr"/>
       <c r="Q90" t="inlineStr"/>
+      <c r="R90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5000,6 +5094,7 @@
       <c r="O91" t="inlineStr"/>
       <c r="P91" t="inlineStr"/>
       <c r="Q91" t="inlineStr"/>
+      <c r="R91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5051,6 +5146,7 @@
       <c r="O92" t="inlineStr"/>
       <c r="P92" t="inlineStr"/>
       <c r="Q92" t="inlineStr"/>
+      <c r="R92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5102,6 +5198,7 @@
       <c r="O93" t="inlineStr"/>
       <c r="P93" t="inlineStr"/>
       <c r="Q93" t="inlineStr"/>
+      <c r="R93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5153,6 +5250,7 @@
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr"/>
       <c r="Q94" t="inlineStr"/>
+      <c r="R94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5200,6 +5298,7 @@
       <c r="O95" t="inlineStr"/>
       <c r="P95" t="inlineStr"/>
       <c r="Q95" t="inlineStr"/>
+      <c r="R95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5247,6 +5346,7 @@
       <c r="O96" t="inlineStr"/>
       <c r="P96" t="inlineStr"/>
       <c r="Q96" t="inlineStr"/>
+      <c r="R96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5302,6 +5402,7 @@
       <c r="O97" t="inlineStr"/>
       <c r="P97" t="inlineStr"/>
       <c r="Q97" t="inlineStr"/>
+      <c r="R97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5349,6 +5450,7 @@
       <c r="O98" t="inlineStr"/>
       <c r="P98" t="inlineStr"/>
       <c r="Q98" t="inlineStr"/>
+      <c r="R98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5396,6 +5498,7 @@
       <c r="O99" t="inlineStr"/>
       <c r="P99" t="inlineStr"/>
       <c r="Q99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5443,6 +5546,7 @@
       <c r="O100" t="inlineStr"/>
       <c r="P100" t="inlineStr"/>
       <c r="Q100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5498,6 +5602,7 @@
       <c r="O101" t="inlineStr"/>
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="inlineStr"/>
+      <c r="R101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5553,6 +5658,7 @@
       <c r="O102" t="inlineStr"/>
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="inlineStr"/>
+      <c r="R102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5600,6 +5706,7 @@
       <c r="O103" t="inlineStr"/>
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="inlineStr"/>
+      <c r="R103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5647,6 +5754,7 @@
       <c r="O104" t="inlineStr"/>
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr"/>
+      <c r="R104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5702,6 +5810,7 @@
       <c r="O105" t="inlineStr"/>
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr"/>
+      <c r="R105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5753,6 +5862,7 @@
       <c r="O106" t="inlineStr"/>
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="inlineStr"/>
+      <c r="R106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5804,6 +5914,7 @@
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
+      <c r="R107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5855,6 +5966,7 @@
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5906,6 +6018,7 @@
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5957,6 +6070,7 @@
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
+      <c r="R110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6004,6 +6118,7 @@
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
+      <c r="R111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6051,6 +6166,7 @@
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr"/>
+      <c r="R112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6098,6 +6214,7 @@
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
+      <c r="R113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6149,6 +6266,7 @@
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6200,6 +6318,7 @@
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6251,6 +6370,7 @@
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
+      <c r="R116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6302,6 +6422,7 @@
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
+      <c r="R117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6353,6 +6474,7 @@
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
+      <c r="R118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6404,6 +6526,7 @@
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
+      <c r="R119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6455,6 +6578,7 @@
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
+      <c r="R120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6510,6 +6634,7 @@
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
+      <c r="R121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6561,6 +6686,7 @@
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
+      <c r="R122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6608,6 +6734,7 @@
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr"/>
+      <c r="R123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6659,6 +6786,7 @@
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
+      <c r="R124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6710,6 +6838,7 @@
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
+      <c r="R125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6753,6 +6882,7 @@
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
+      <c r="R126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6796,6 +6926,7 @@
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6843,6 +6974,7 @@
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6902,6 +7034,7 @@
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6949,6 +7082,7 @@
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7004,6 +7138,7 @@
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7051,6 +7186,7 @@
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7114,6 +7250,7 @@
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7165,6 +7302,7 @@
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7224,6 +7362,7 @@
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7275,6 +7414,7 @@
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
+      <c r="R136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7334,6 +7474,7 @@
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
+      <c r="R137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7397,6 +7538,7 @@
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr"/>
+      <c r="R138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7444,6 +7586,7 @@
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
+      <c r="R139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7491,6 +7634,7 @@
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7550,6 +7694,7 @@
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
+      <c r="R141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7605,6 +7750,7 @@
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
+      <c r="R142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7664,6 +7810,7 @@
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr"/>
+      <c r="R143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7723,6 +7870,7 @@
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr"/>
+      <c r="R144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7770,6 +7918,7 @@
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
       <c r="Q145" t="inlineStr"/>
+      <c r="R145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7825,6 +7974,7 @@
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
       <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7876,6 +8026,7 @@
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
       <c r="Q147" t="inlineStr"/>
+      <c r="R147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -7927,6 +8078,7 @@
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr"/>
       <c r="Q148" t="inlineStr"/>
+      <c r="R148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -7978,6 +8130,7 @@
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr"/>
       <c r="Q149" t="inlineStr"/>
+      <c r="R149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8029,6 +8182,7 @@
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr"/>
       <c r="Q150" t="inlineStr"/>
+      <c r="R150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8088,6 +8242,7 @@
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr"/>
       <c r="Q151" t="inlineStr"/>
+      <c r="R151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8143,6 +8298,7 @@
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr"/>
       <c r="Q152" t="inlineStr"/>
+      <c r="R152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8198,6 +8354,7 @@
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr"/>
       <c r="Q153" t="inlineStr"/>
+      <c r="R153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8257,6 +8414,7 @@
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr"/>
       <c r="Q154" t="inlineStr"/>
+      <c r="R154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8316,6 +8474,7 @@
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr"/>
       <c r="Q155" t="inlineStr"/>
+      <c r="R155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8371,6 +8530,7 @@
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
       <c r="Q156" t="inlineStr"/>
+      <c r="R156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8430,6 +8590,7 @@
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
       <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8489,6 +8650,7 @@
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr"/>
       <c r="Q158" t="inlineStr"/>
+      <c r="R158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -8540,6 +8702,7 @@
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr"/>
       <c r="Q159" t="inlineStr"/>
+      <c r="R159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8599,6 +8762,7 @@
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr"/>
       <c r="Q160" t="inlineStr"/>
+      <c r="R160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8658,6 +8822,7 @@
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr"/>
       <c r="Q161" t="inlineStr"/>
+      <c r="R161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8713,6 +8878,7 @@
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
       <c r="Q162" t="inlineStr"/>
+      <c r="R162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8768,6 +8934,7 @@
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr"/>
       <c r="Q163" t="inlineStr"/>
+      <c r="R163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8827,6 +8994,7 @@
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
       <c r="Q164" t="inlineStr"/>
+      <c r="R164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8886,6 +9054,7 @@
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
       <c r="Q165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8946,6 +9115,7 @@
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
       <c r="Q166" t="inlineStr"/>
+      <c r="R166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -9007,6 +9177,7 @@
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
       <c r="Q167" t="inlineStr"/>
+      <c r="R167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9066,6 +9237,7 @@
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
       <c r="Q168" t="inlineStr"/>
+      <c r="R168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9127,6 +9299,7 @@
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr"/>
       <c r="Q169" t="inlineStr"/>
+      <c r="R169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9187,6 +9360,7 @@
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr"/>
       <c r="Q170" t="inlineStr"/>
+      <c r="R170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9242,6 +9416,7 @@
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr"/>
+      <c r="R171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9301,6 +9476,7 @@
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr"/>
+      <c r="R172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9361,6 +9537,7 @@
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
+      <c r="R173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9416,6 +9593,7 @@
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
       <c r="Q174" t="inlineStr"/>
+      <c r="R174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9476,6 +9654,7 @@
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
+      <c r="R175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9537,6 +9716,7 @@
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr"/>
+      <c r="R176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9601,6 +9781,7 @@
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr"/>
+      <c r="R177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9660,6 +9841,7 @@
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
       <c r="Q178" t="inlineStr"/>
+      <c r="R178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9720,6 +9902,7 @@
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr"/>
       <c r="Q179" t="inlineStr"/>
+      <c r="R179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9781,6 +9964,7 @@
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
       <c r="Q180" t="inlineStr"/>
+      <c r="R180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9844,6 +10028,7 @@
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr"/>
       <c r="Q181" t="inlineStr"/>
+      <c r="R181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9904,6 +10089,7 @@
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr"/>
       <c r="Q182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9964,6 +10150,7 @@
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
       <c r="Q183" t="inlineStr"/>
+      <c r="R183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -10025,6 +10212,7 @@
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
       <c r="Q184" t="inlineStr"/>
+      <c r="R184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -10086,6 +10274,7 @@
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
       <c r="Q185" t="inlineStr"/>
+      <c r="R185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -10141,6 +10330,7 @@
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
       <c r="Q186" t="inlineStr"/>
+      <c r="R186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -10206,6 +10396,7 @@
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
       <c r="Q187" t="inlineStr"/>
+      <c r="R187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -10269,6 +10460,7 @@
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
       <c r="Q188" t="inlineStr"/>
+      <c r="R188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -10328,6 +10520,7 @@
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
       <c r="Q189" t="inlineStr"/>
+      <c r="R189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -10387,6 +10580,7 @@
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr"/>
       <c r="Q190" t="inlineStr"/>
+      <c r="R190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10446,6 +10640,7 @@
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
       <c r="Q191" t="inlineStr"/>
+      <c r="R191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -10506,6 +10701,7 @@
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr"/>
       <c r="Q192" t="inlineStr"/>
+      <c r="R192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10566,6 +10762,7 @@
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr"/>
       <c r="Q193" t="inlineStr"/>
+      <c r="R193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -10626,6 +10823,7 @@
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr"/>
       <c r="Q194" t="inlineStr"/>
+      <c r="R194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -10685,6 +10883,7 @@
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr"/>
       <c r="Q195" t="inlineStr"/>
+      <c r="R195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -10744,6 +10943,7 @@
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr"/>
       <c r="Q196" t="inlineStr"/>
+      <c r="R196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -10803,6 +11003,7 @@
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr"/>
       <c r="Q197" t="inlineStr"/>
+      <c r="R197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10862,6 +11063,7 @@
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr"/>
       <c r="Q198" t="inlineStr"/>
+      <c r="R198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10918,6 +11120,7 @@
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr"/>
       <c r="Q199" t="inlineStr"/>
+      <c r="R199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10979,6 +11182,7 @@
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr"/>
       <c r="Q200" t="inlineStr"/>
+      <c r="R200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -11040,6 +11244,7 @@
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr"/>
       <c r="Q201" t="inlineStr"/>
+      <c r="R201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -11099,6 +11304,7 @@
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr"/>
+      <c r="R202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -11158,6 +11364,7 @@
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr"/>
       <c r="Q203" t="inlineStr"/>
+      <c r="R203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -11217,6 +11424,7 @@
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
       <c r="Q204" t="inlineStr"/>
+      <c r="R204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -11276,6 +11484,7 @@
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr"/>
       <c r="Q205" t="inlineStr"/>
+      <c r="R205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -11335,6 +11544,7 @@
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr"/>
       <c r="Q206" t="inlineStr"/>
+      <c r="R206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -11394,6 +11604,7 @@
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr"/>
       <c r="Q207" t="inlineStr"/>
+      <c r="R207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -11451,6 +11662,7 @@
       <c r="O208" t="inlineStr"/>
       <c r="P208" t="inlineStr"/>
       <c r="Q208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -11511,6 +11723,7 @@
       <c r="O209" t="inlineStr"/>
       <c r="P209" t="inlineStr"/>
       <c r="Q209" t="inlineStr"/>
+      <c r="R209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -11571,6 +11784,7 @@
       <c r="O210" t="inlineStr"/>
       <c r="P210" t="inlineStr"/>
       <c r="Q210" t="inlineStr"/>
+      <c r="R210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -11626,6 +11840,7 @@
       <c r="O211" t="inlineStr"/>
       <c r="P211" t="inlineStr"/>
       <c r="Q211" t="inlineStr"/>
+      <c r="R211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -11686,6 +11901,7 @@
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr"/>
       <c r="Q212" t="inlineStr"/>
+      <c r="R212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -11746,6 +11962,7 @@
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="inlineStr"/>
       <c r="Q213" t="inlineStr"/>
+      <c r="R213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -11809,6 +12026,7 @@
       <c r="O214" t="inlineStr"/>
       <c r="P214" t="inlineStr"/>
       <c r="Q214" t="inlineStr"/>
+      <c r="R214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -11868,6 +12086,7 @@
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr"/>
       <c r="Q215" t="inlineStr"/>
+      <c r="R215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -11928,6 +12147,7 @@
       <c r="O216" t="inlineStr"/>
       <c r="P216" t="inlineStr"/>
       <c r="Q216" t="inlineStr"/>
+      <c r="R216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -11993,6 +12213,7 @@
       <c r="O217" t="inlineStr"/>
       <c r="P217" t="inlineStr"/>
       <c r="Q217" t="inlineStr"/>
+      <c r="R217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -12058,6 +12279,7 @@
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="inlineStr"/>
       <c r="Q218" t="inlineStr"/>
+      <c r="R218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -12123,6 +12345,7 @@
       <c r="O219" t="inlineStr"/>
       <c r="P219" t="inlineStr"/>
       <c r="Q219" t="inlineStr"/>
+      <c r="R219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -12183,6 +12406,7 @@
       <c r="O220" t="inlineStr"/>
       <c r="P220" t="inlineStr"/>
       <c r="Q220" t="inlineStr"/>
+      <c r="R220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -12242,6 +12466,7 @@
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr"/>
       <c r="Q221" t="inlineStr"/>
+      <c r="R221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -12307,6 +12532,7 @@
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr"/>
       <c r="Q222" t="inlineStr"/>
+      <c r="R222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -12366,6 +12592,7 @@
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr"/>
       <c r="Q223" t="inlineStr"/>
+      <c r="R223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -12423,6 +12650,7 @@
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
       <c r="Q224" t="inlineStr"/>
+      <c r="R224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -12483,6 +12711,7 @@
       <c r="O225" t="inlineStr"/>
       <c r="P225" t="inlineStr"/>
       <c r="Q225" t="inlineStr"/>
+      <c r="R225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -12543,6 +12772,7 @@
       <c r="O226" t="inlineStr"/>
       <c r="P226" t="inlineStr"/>
       <c r="Q226" t="inlineStr"/>
+      <c r="R226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -12601,6 +12831,7 @@
       <c r="O227" t="inlineStr"/>
       <c r="P227" t="inlineStr"/>
       <c r="Q227" t="inlineStr"/>
+      <c r="R227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -12660,6 +12891,7 @@
       <c r="O228" t="inlineStr"/>
       <c r="P228" t="inlineStr"/>
       <c r="Q228" t="inlineStr"/>
+      <c r="R228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -12717,6 +12949,7 @@
       <c r="O229" t="inlineStr"/>
       <c r="P229" t="inlineStr"/>
       <c r="Q229" t="inlineStr"/>
+      <c r="R229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -12782,6 +13015,7 @@
       <c r="O230" t="inlineStr"/>
       <c r="P230" t="inlineStr"/>
       <c r="Q230" t="inlineStr"/>
+      <c r="R230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -12841,6 +13075,7 @@
       <c r="O231" t="inlineStr"/>
       <c r="P231" t="inlineStr"/>
       <c r="Q231" t="inlineStr"/>
+      <c r="R231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -12900,6 +13135,7 @@
       <c r="O232" t="inlineStr"/>
       <c r="P232" t="inlineStr"/>
       <c r="Q232" t="inlineStr"/>
+      <c r="R232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -12955,6 +13191,7 @@
       <c r="O233" t="inlineStr"/>
       <c r="P233" t="inlineStr"/>
       <c r="Q233" t="inlineStr"/>
+      <c r="R233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -13012,6 +13249,7 @@
       <c r="O234" t="inlineStr"/>
       <c r="P234" t="inlineStr"/>
       <c r="Q234" t="inlineStr"/>
+      <c r="R234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -13069,6 +13307,7 @@
       <c r="O235" t="inlineStr"/>
       <c r="P235" t="inlineStr"/>
       <c r="Q235" t="inlineStr"/>
+      <c r="R235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -13126,6 +13365,7 @@
       <c r="O236" t="inlineStr"/>
       <c r="P236" t="inlineStr"/>
       <c r="Q236" t="inlineStr"/>
+      <c r="R236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -13183,6 +13423,7 @@
       <c r="O237" t="inlineStr"/>
       <c r="P237" t="inlineStr"/>
       <c r="Q237" t="inlineStr"/>
+      <c r="R237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -13240,6 +13481,7 @@
       <c r="O238" t="inlineStr"/>
       <c r="P238" t="inlineStr"/>
       <c r="Q238" t="inlineStr"/>
+      <c r="R238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -13297,6 +13539,7 @@
       <c r="O239" t="inlineStr"/>
       <c r="P239" t="inlineStr"/>
       <c r="Q239" t="inlineStr"/>
+      <c r="R239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -13354,6 +13597,7 @@
       <c r="O240" t="inlineStr"/>
       <c r="P240" t="inlineStr"/>
       <c r="Q240" t="inlineStr"/>
+      <c r="R240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -13415,6 +13659,7 @@
       <c r="O241" t="inlineStr"/>
       <c r="P241" t="inlineStr"/>
       <c r="Q241" t="inlineStr"/>
+      <c r="R241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -13472,6 +13717,7 @@
       <c r="O242" t="inlineStr"/>
       <c r="P242" t="inlineStr"/>
       <c r="Q242" t="inlineStr"/>
+      <c r="R242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -13529,6 +13775,7 @@
       <c r="O243" t="inlineStr"/>
       <c r="P243" t="inlineStr"/>
       <c r="Q243" t="inlineStr"/>
+      <c r="R243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -13590,6 +13837,7 @@
       <c r="O244" t="inlineStr"/>
       <c r="P244" t="inlineStr"/>
       <c r="Q244" t="inlineStr"/>
+      <c r="R244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -13647,6 +13895,7 @@
       <c r="O245" t="inlineStr"/>
       <c r="P245" t="inlineStr"/>
       <c r="Q245" t="inlineStr"/>
+      <c r="R245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -13708,6 +13957,7 @@
       <c r="O246" t="inlineStr"/>
       <c r="P246" t="inlineStr"/>
       <c r="Q246" t="inlineStr"/>
+      <c r="R246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -13773,6 +14023,7 @@
       <c r="O247" t="inlineStr"/>
       <c r="P247" t="inlineStr"/>
       <c r="Q247" t="inlineStr"/>
+      <c r="R247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -13838,6 +14089,7 @@
       <c r="O248" t="inlineStr"/>
       <c r="P248" t="inlineStr"/>
       <c r="Q248" t="inlineStr"/>
+      <c r="R248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -13895,6 +14147,7 @@
       <c r="O249" t="inlineStr"/>
       <c r="P249" t="inlineStr"/>
       <c r="Q249" t="inlineStr"/>
+      <c r="R249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -13952,6 +14205,7 @@
       <c r="O250" t="inlineStr"/>
       <c r="P250" t="inlineStr"/>
       <c r="Q250" t="inlineStr"/>
+      <c r="R250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -14017,6 +14271,7 @@
       <c r="O251" t="inlineStr"/>
       <c r="P251" t="inlineStr"/>
       <c r="Q251" t="inlineStr"/>
+      <c r="R251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -14074,6 +14329,7 @@
       <c r="O252" t="inlineStr"/>
       <c r="P252" t="inlineStr"/>
       <c r="Q252" t="inlineStr"/>
+      <c r="R252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -14137,6 +14393,7 @@
       <c r="O253" t="inlineStr"/>
       <c r="P253" t="inlineStr"/>
       <c r="Q253" t="inlineStr"/>
+      <c r="R253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -14194,6 +14451,7 @@
       <c r="O254" t="inlineStr"/>
       <c r="P254" t="inlineStr"/>
       <c r="Q254" t="inlineStr"/>
+      <c r="R254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -14251,6 +14509,7 @@
       <c r="O255" t="inlineStr"/>
       <c r="P255" t="inlineStr"/>
       <c r="Q255" t="inlineStr"/>
+      <c r="R255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -14312,6 +14571,7 @@
       <c r="O256" t="inlineStr"/>
       <c r="P256" t="inlineStr"/>
       <c r="Q256" t="inlineStr"/>
+      <c r="R256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -14373,6 +14633,7 @@
       <c r="O257" t="inlineStr"/>
       <c r="P257" t="inlineStr"/>
       <c r="Q257" t="inlineStr"/>
+      <c r="R257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -14432,6 +14693,7 @@
       <c r="O258" t="inlineStr"/>
       <c r="P258" t="inlineStr"/>
       <c r="Q258" t="inlineStr"/>
+      <c r="R258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -14493,6 +14755,7 @@
       <c r="O259" t="inlineStr"/>
       <c r="P259" t="inlineStr"/>
       <c r="Q259" t="inlineStr"/>
+      <c r="R259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -14552,6 +14815,7 @@
       <c r="O260" t="inlineStr"/>
       <c r="P260" t="inlineStr"/>
       <c r="Q260" t="inlineStr"/>
+      <c r="R260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -14605,6 +14869,7 @@
       <c r="O261" t="inlineStr"/>
       <c r="P261" t="inlineStr"/>
       <c r="Q261" t="inlineStr"/>
+      <c r="R261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -14658,6 +14923,7 @@
       <c r="O262" t="inlineStr"/>
       <c r="P262" t="inlineStr"/>
       <c r="Q262" t="inlineStr"/>
+      <c r="R262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -14715,6 +14981,7 @@
       <c r="O263" t="inlineStr"/>
       <c r="P263" t="inlineStr"/>
       <c r="Q263" t="inlineStr"/>
+      <c r="R263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -14776,6 +15043,7 @@
       </c>
       <c r="P264" t="inlineStr"/>
       <c r="Q264" t="inlineStr"/>
+      <c r="R264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -14825,6 +15093,7 @@
       </c>
       <c r="P265" t="inlineStr"/>
       <c r="Q265" t="inlineStr"/>
+      <c r="R265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -14890,6 +15159,7 @@
       </c>
       <c r="P266" t="inlineStr"/>
       <c r="Q266" t="inlineStr"/>
+      <c r="R266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -14939,6 +15209,7 @@
       </c>
       <c r="P267" t="inlineStr"/>
       <c r="Q267" t="inlineStr"/>
+      <c r="R267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -15004,6 +15275,7 @@
       </c>
       <c r="P268" t="inlineStr"/>
       <c r="Q268" t="inlineStr"/>
+      <c r="R268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -15065,6 +15337,7 @@
       </c>
       <c r="P269" t="inlineStr"/>
       <c r="Q269" t="inlineStr"/>
+      <c r="R269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -15130,6 +15403,7 @@
       </c>
       <c r="P270" t="inlineStr"/>
       <c r="Q270" t="inlineStr"/>
+      <c r="R270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -15179,6 +15453,7 @@
       </c>
       <c r="P271" t="inlineStr"/>
       <c r="Q271" t="inlineStr"/>
+      <c r="R271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -15228,6 +15503,7 @@
       </c>
       <c r="P272" t="inlineStr"/>
       <c r="Q272" t="inlineStr"/>
+      <c r="R272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -15277,6 +15553,7 @@
       </c>
       <c r="P273" t="inlineStr"/>
       <c r="Q273" t="inlineStr"/>
+      <c r="R273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -15342,6 +15619,7 @@
       </c>
       <c r="P274" t="inlineStr"/>
       <c r="Q274" t="inlineStr"/>
+      <c r="R274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -15391,6 +15669,7 @@
       </c>
       <c r="P275" t="inlineStr"/>
       <c r="Q275" t="inlineStr"/>
+      <c r="R275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -15440,6 +15719,7 @@
       </c>
       <c r="P276" t="inlineStr"/>
       <c r="Q276" t="inlineStr"/>
+      <c r="R276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -15505,6 +15785,7 @@
       </c>
       <c r="P277" t="inlineStr"/>
       <c r="Q277" t="inlineStr"/>
+      <c r="R277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -15570,6 +15851,7 @@
       </c>
       <c r="P278" t="inlineStr"/>
       <c r="Q278" t="inlineStr"/>
+      <c r="R278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -15635,6 +15917,7 @@
       </c>
       <c r="P279" t="inlineStr"/>
       <c r="Q279" t="inlineStr"/>
+      <c r="R279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -15700,6 +15983,7 @@
       </c>
       <c r="P280" t="inlineStr"/>
       <c r="Q280" t="inlineStr"/>
+      <c r="R280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -15761,6 +16045,7 @@
       <c r="O281" t="inlineStr"/>
       <c r="P281" t="inlineStr"/>
       <c r="Q281" t="inlineStr"/>
+      <c r="R281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -15810,6 +16095,7 @@
       </c>
       <c r="P282" t="inlineStr"/>
       <c r="Q282" t="inlineStr"/>
+      <c r="R282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -15855,6 +16141,7 @@
       <c r="O283" t="inlineStr"/>
       <c r="P283" t="inlineStr"/>
       <c r="Q283" t="inlineStr"/>
+      <c r="R283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -15910,6 +16197,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -15965,6 +16253,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -16020,6 +16309,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -16079,6 +16369,7 @@
           <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→阿里巴巴/通义千问; 任务类型→通用对话; 官网→https://qwenlm.github.io; 备注→通义千问旗舰模型；Agentic能力；长程任务执行；面向云端智能体调度优化; 问题: 模型名称包含版本号，形式上符合规范; 截至已知公开资料无法核实“Qwen 3.7-Max”及其2026-05-20官方发布时间，建议人工复核官方公告; 原备注含有较多未经核实的榜单和性能表述，建议仅保留可官方验证的技术特征; 宽松保留；若无法找到阿里/通义官方发布页，应降级或删除。</t>
         </is>
       </c>
+      <c r="R287" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -16142,6 +16433,7 @@
           <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(中置信)待人工确认 — 建议修正: 模型发布时间→2026-04-24; 公司→DeepSeek/深度求索; 任务类型→通用对话/复杂推理/代码生成; 官网→https://api-docs.deepseek.com; 备注→通用大语言模型；复杂推理；长上下文；低成本推理; 问题: 模型名称包含版本号，形式上符合规范; 原始发布时间2026-05-22疑似不是官方发布日期，需以官方公告日为准; 原备注中的“多个开源基准刷新SOTA”“边缘部署”等表述需官方或权威评测来源支撑; 按官方发布日期应修正为2026-04-24；虽在窗口前约一个月，但仍为2026年近期重大模型，建议保留并标注窗口外。</t>
         </is>
       </c>
+      <c r="R288" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -16201,6 +16493,7 @@
           <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(低置信)待人工确认 — 建议删除：产品泛称无版本号; 缺少明确版本号/型号，不符合“具体模型/产品名称 + 版本号/型号”的命名要求; 更像个人智能体产品而非具体模型; 截至已知公开资料无法核实“Gemini Spark”及其2026-05-21官方发布时间</t>
         </is>
       </c>
+      <c r="R289" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -16264,6 +16557,7 @@
           <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→小米/MiMo; 任务类型→端侧多模态/图文理解/语音交互; 备注→端侧多模态模型；移动设备部署；图文理解；语音指令交互; 问题: 模型名称包含版本号，形式上符合规范; 截至已知公开资料无法核实“MiMo 2.5”及其2026-05-22官方发布时间，建议人工复核小米官方技术公告; 原备注中“HyperOS 2.5 Agent框架”等产品集成信息需确认是否为模型自身特征; 宽松保留；若仅为系统功能或Agent框架而非模型版本，应调整分类。</t>
         </is>
       </c>
+      <c r="R290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -16323,6 +16617,7 @@
           <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→Google DeepMind; 任务类型→软件工程智能体/代码生成; 类型→软件工程智能体平台; 备注→软件工程智能体平台；多智能体协作；代码生成；自动测试；端到端软件构建; 问题: 名称包含版本号，形式上符合规范; 该条目更像智能体平台/开发工具，而非具体基础模型; 截至已知公开资料无法核实“Antigravity 2.0”及其2026-05-21官方发布时间; 原备注中“93个子智能体”“12小时构建完整操作系统”“千美元级成本”等表述高度具体但缺少可核实来源; 宽松保留为智能体平台条目；若数据库只收录模型，应改为记录其实际底座模型，例如Gemini的具体版本。</t>
         </is>
       </c>
+      <c r="R291" t="inlineStr"/>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -16386,6 +16681,7 @@
           <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 不是具体模型名称，属于Anthropic的代码智能体产品/工具; 发布时间应为2025年相关发布/GA时间，属于旧产品（发布于2025年）; 原始模型发布时间2026-05-22疑似错误</t>
         </is>
       </c>
+      <c r="R292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -16445,6 +16741,7 @@
           <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→Google DeepMind; 任务类型→通用对话/代码生成; 官网→https://ai.google.dev/gemma; 备注→开放权重模型；轻量级部署；面向开发者本地与云端推理; 问题: 模型名称包含版本号，形式上符合规范; 截至已知公开资料无法核实“Gemma 4”及其2026-05-22官方发布时间，建议人工复核Google DeepMind或Google AI官方公告; 原备注中的“12GB显存下110 tok/s”等性能指标缺少可核实来源; 宽松保留；如确认为2026年Google官方发布的新一代Gemma，可继续录入。</t>
         </is>
       </c>
+      <c r="R293" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -16508,6 +16805,7 @@
           <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(低置信)待人工确认 — 建议删除：缺少版本号/型号; 名称不是“具体模型/产品名称 + 版本号/型号”的规范形式; 国内外字段错误：无锡数字城市建设发展有限公司为中国公司，应标注为国内; “垂类多模态智能体基座模型”分类表述混杂，建议改为行业模型或工业AIoT智能体; 截至已知公开资料无法核实其2026-05-21官方发布时间</t>
         </is>
       </c>
+      <c r="R294" t="inlineStr"/>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -16563,6 +16861,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R295" t="inlineStr"/>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -16618,6 +16917,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R296" t="inlineStr"/>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -16673,6 +16973,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -16728,6 +17029,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -16783,6 +17085,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R299" t="inlineStr"/>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -16854,6 +17157,7 @@
           <t xml:space="preserve"> · HuggingFace 需登录(英伟达/gamma-world-test)</t>
         </is>
       </c>
+      <c r="R300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -16925,6 +17229,7 @@
           <t xml:space="preserve"> · HuggingFace 需登录(阿里/Fun-ASR-Nano-2512-hf)</t>
         </is>
       </c>
+      <c r="R301" t="inlineStr"/>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -16984,6 +17289,7 @@
           <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 非具体模型条目：昇腾AgentInfra更像智能体运行环境/基础设施组件，不属于模型名称; 模型名称缺少明确版本号或型号; 类型分类不应归为模型，应归为智能体基础设施/运行时</t>
         </is>
       </c>
+      <c r="R302" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -17043,6 +17349,7 @@
           <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 公司→xAI; 官网→https://docs.x.ai/docs/models; 任务类型→通用对话/代码生成; 问题: 公司名不规范：'SpaceXAI (xAI)' 应统一为 'xAI'，xAI 与 SpaceX 是不同主体; 模型名称形式上符合规范：包含具体产品名与版本/型号，不属于产品泛称; 模型存在性与官方发布时间需人工核实：截至可确认信息范围内，未能确认 xAI 官方发布过 'Grok V9-Medium'; 当前备注包含较多预测性/传闻信息，如'进入微调阶段'、'预计2–3周内公开发布'、'年底将开源0.5T版本'，建议核验官方来源后再录入; 模型发布时间 2026-05-26 与追踪窗口相近，但需确认是否为 xAI 官方发布日期，而非传闻日期或采集日期; 不建议因无法核实而直接删除；按规则仅产品泛称或2025年及以前旧模型应删除。建议后续以 xAI 官网、官方博客或官方 X 账号公告为准复核。</t>
         </is>
       </c>
+      <c r="R303" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -17114,6 +17421,7 @@
           <t xml:space="preserve"> · HuggingFace 需登录(微软/vermeer-XL-CA)</t>
         </is>
       </c>
+      <c r="R304" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -17185,6 +17493,7 @@
           <t xml:space="preserve"> · HuggingFace 需登录(微软/vermeer-XL)</t>
         </is>
       </c>
+      <c r="R305" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -17256,6 +17565,7 @@
           <t xml:space="preserve"> · HuggingFace 需登录(微软/vermeer-L-AP)</t>
         </is>
       </c>
+      <c r="R306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -17327,6 +17637,7 @@
           <t xml:space="preserve"> · HuggingFace 需登录(微软/vermeer-L)</t>
         </is>
       </c>
+      <c r="R307" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -17382,6 +17693,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R308" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -17437,6 +17749,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R309" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -17496,6 +17809,7 @@
           <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 官网→https://platform.openai.com/docs/models; 任务类型→通用对话; 开闭源→闭源; 问题: 未能确认 OpenAI 官方发布过 GPT-5.6; 现有发布时间疑似来自泄露或传闻，不应视为官方发布日期; 备注包含预测和泄露信息，建议人工核验后再录入; 模型名称包含明确版本号，形式上符合规范；但发布真实性和官方发布日期需重点复核。</t>
         </is>
       </c>
+      <c r="R310" t="inlineStr"/>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -17555,6 +17869,7 @@
           <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称像系列名或代号，未指向具体模型版本; 未能确认 Anthropic 官方发布过 Claude Mythos; 备注中关于央行和 SWIFT 漏洞暴露的描述高度异常，需严格核验来源; 现有发布时间缺乏官方依据</t>
         </is>
       </c>
+      <c r="R311" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -17610,6 +17925,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -17665,6 +17981,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -17736,6 +18053,7 @@
           <t xml:space="preserve"> · HuggingFace 需登录(英伟达/Assemble_Trocar)</t>
         </is>
       </c>
+      <c r="R314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -17791,6 +18109,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -17866,6 +18185,7 @@
           <t>llm-stats.com 排行榜; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 官网→https://docs.anthropic.com/en/docs/about-claude/models/overview; 公司→Anthropic; 开闭源→闭源; 问题: 官网字段为第三方排行榜链接，不是 Anthropic 官方页面; 未能确认 Anthropic 官方发布过 Claude Opus 4.8; 模型发布时间需以 Anthropic 官方公告或官方模型文档为准; llm-stats.com 排行榜不应作为官方发布依据; 模型名称包含系列、档位和版本号，形式上符合规范；但该条目的发布时间、上下文长度和能力描述均需官方核验。</t>
         </is>
       </c>
+      <c r="R316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -17921,6 +18241,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -17976,6 +18297,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -18031,6 +18353,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -18086,6 +18409,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R320" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -18141,6 +18465,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -18196,6 +18521,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -18255,6 +18581,7 @@
           <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称指向模型矩阵/模型集合，不是具体的模型/产品名称 + 版本号/型号; 未能基于已知公开信息确认其为官方发布的具体模型</t>
         </is>
       </c>
+      <c r="R323" t="inlineStr"/>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -18310,6 +18637,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R324" t="inlineStr"/>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -18365,6 +18693,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R325" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -18420,6 +18749,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R326" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -18475,6 +18805,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R327" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -18550,6 +18881,7 @@
           <t xml:space="preserve"> · HuggingFace 需登录(英伟达/4D-RGPT-8B)</t>
         </is>
       </c>
+      <c r="R328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -18621,6 +18953,7 @@
           <t>HuggingFace 已核实(google/CircularNet) · apache-2.0</t>
         </is>
       </c>
+      <c r="R329" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -18676,6 +19009,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -18735,6 +19069,7 @@
           <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(低置信)待人工确认 — 建议修正: 任务类型→自主智能体/多模态智能体; 公司→Microsoft AI; 类型→自主智能体（Agent）系统; 问题: 名称包含明确型号/版本号，形式上符合具体模型或系统名称规范; 当前信息显示更像智能体系统/框架，而非传统基础模型，需确认是否应纳入模型库; 发布时间为2026-06-03，处于本次追踪窗口附近，可宽松保留; 核实情况为待核实，建议人工查验微软官方发布源; 未能基于已知可靠公开知识确认该名称及发布日期，建议以 Microsoft AI 官方博客、Azure AI 文档或 GitHub/SDK 发布记录为准。</t>
         </is>
       </c>
+      <c r="R331" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -18790,6 +19125,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R332" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -18845,6 +19181,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R333" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -18900,6 +19237,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R334" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -18955,6 +19293,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R335" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -19010,6 +19349,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R336" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -19081,6 +19421,7 @@
           <t xml:space="preserve"> · HuggingFace 需登录(英伟达/ArtiFixer)</t>
         </is>
       </c>
+      <c r="R337" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -19156,6 +19497,7 @@
           <t>HuggingFace 已核实(google/gemma-4-12B-it-qat-w4a16-ct) · 参数量=13B · apache-2.0 · any-to-any</t>
         </is>
       </c>
+      <c r="R338" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -19211,6 +19553,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R339" t="inlineStr"/>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -19266,6 +19609,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R340" t="inlineStr"/>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -19325,6 +19669,7 @@
           <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5审核(中置信)待人工确认 — 建议修正: 备注→香港本地研发；生产力级大语言模型；长上下文理解；多轮复杂推理; 任务类型→通用对话; 问题: 国内外字段疑似错误：香港生成式人工智能研发中心应归为国内/中国香港，而非国外; 官网缺失，需人工核实官方模型页面; 开闭源信息缺失; 发布时间为2026-06-03，位于追踪窗口前一周内，可保留但建议核实官方公告; 模型名称包含明确版本号V3，符合具体模型名称规范；但该模型的公开技术指标、参数规模、上下文长度等信息不足。</t>
         </is>
       </c>
+      <c r="R341" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -19384,6 +19729,7 @@
           <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 该条目更像智能体产品/系统，不是具体模型名称+版本号; 国内外字段疑似错误：香港生成式人工智能研发中心应归为国内/中国香港，而非国外; 官网缺失，需人工核实官方页面; 开闭源信息缺失</t>
         </is>
       </c>
+      <c r="R342" t="inlineStr"/>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -19443,6 +19789,7 @@
           <t>待核实（LLM交叉巡检发现）; ⚠️ GPT-5.5建议删除(中置信)待人工确认 — 建议删除：产品泛称无版本号; 名称为描述性系统名称，不是具体模型/产品名称+版本号; 国内外字段错误：公司位于成都，应归为国内; 更像垂直行业应用系统，不是明确的基础模型或具体模型版本; 官网缺失，需人工核实官方页面; 开闭源信息缺失</t>
         </is>
       </c>
+      <c r="R343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -19518,6 +19865,7 @@
           <t>HuggingFace 已核实(google/gemma-4-E2B-it-qat-mobile-ct) · 参数量=6B · apache-2.0 · any-to-any</t>
         </is>
       </c>
+      <c r="R344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -19573,6 +19921,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -19628,6 +19977,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R346" t="inlineStr"/>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -19703,6 +20053,7 @@
           <t>HuggingFace 已核实(google/gemma-4-E4B-it-qat-mobile-ct) · 参数量=9B · apache-2.0 · any-to-any</t>
         </is>
       </c>
+      <c r="R347" t="inlineStr"/>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -19758,6 +20109,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R348" t="inlineStr"/>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -19833,6 +20185,7 @@
           <t>llm-stats.com 排行榜</t>
         </is>
       </c>
+      <c r="R349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -19888,6 +20241,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -19943,6 +20297,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -20006,6 +20361,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R352" t="inlineStr"/>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -20065,6 +20421,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R353" t="inlineStr"/>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -20144,6 +20501,7 @@
           <t>llm-stats.com 排行榜 · HuggingFace 需登录(google/DiffusionGemma 26B-A4B)</t>
         </is>
       </c>
+      <c r="R354" t="inlineStr"/>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -20219,6 +20577,7 @@
           <t xml:space="preserve"> · HuggingFace 需登录(英伟达/diffusiongemma-26B-A4B-it-NVFP4)</t>
         </is>
       </c>
+      <c r="R355" t="inlineStr"/>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -20274,6 +20633,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -20329,6 +20689,7 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R357" t="inlineStr"/>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -20384,6 +20745,2395 @@
           <t>待核实（LLM交叉巡检发现）</t>
         </is>
       </c>
+      <c r="R358" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Gemini 3.5</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr"/>
+      <c r="C359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>谷歌</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr"/>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>语音</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>语音翻译</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/gemini-3.5-flash</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>谷歌免费实时同传翻译模型</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="N359" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>腾讯研究院+llmstats交叉核实</t>
+        </is>
+      </c>
+      <c r="R359" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>讯飞星火医疗大模型V3.5</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr"/>
+      <c r="C360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>讯飞</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr"/>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>领域</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>医疗语义理解,病历生成</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr"/>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>讯飞全国产算力医疗大模型</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="N360" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R360" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Gemma 4 QAT</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr"/>
+      <c r="C361" t="inlineStr"/>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>2B/12B/26B MoE</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr"/>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>谷歌发布量化版大模型</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="N361" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R361" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>JoyAI-Echo</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr"/>
+      <c r="C362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>京东</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr"/>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>视频生成</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>长视频生成</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>https://echo-team-joy-future-academy-jd.github.io/Echo-LongVideo-Page/</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>京东开源长音视频生成框架</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="N362" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R362" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>ABot-Earth0.5</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr"/>
+      <c r="C363" t="inlineStr"/>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>高德</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr"/>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>3D生成</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>https://abot-earth.amap.com</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>高德3D原生城市世界模型</t>
+        </is>
+      </c>
+      <c r="M363" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="N363" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R363" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>琅琊2.0</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr"/>
+      <c r="C364" t="inlineStr"/>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>中科院海洋研究所</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr"/>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>领域</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>海洋预报</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr"/>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>中科院海洋预报大模型</t>
+        </is>
+      </c>
+      <c r="M364" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="N364" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R364" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Gemma 4 12B</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr"/>
+      <c r="C365" t="inlineStr"/>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>谷歌</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>12B</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>多模态交互,通用对话</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/gemma-4-12b-it</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>谷歌开源12B多模态模型</t>
+        </is>
+      </c>
+      <c r="M365" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="N365" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>腾讯研究院+llmstats交叉核实</t>
+        </is>
+      </c>
+      <c r="R365" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>GPT-Rosalind</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr"/>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr"/>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>领域</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>药物发现,科学计算</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr"/>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>OpenAI生命科学专用模型</t>
+        </is>
+      </c>
+      <c r="M366" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="N366" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>K2.6</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr"/>
+      <c r="C367" t="inlineStr"/>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>月之暗面</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr"/>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>代码生成</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>https://kimi.com</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>月之暗面代码与推理模型</t>
+        </is>
+      </c>
+      <c r="M367" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N367" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R367" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Music v2</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr"/>
+      <c r="C368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>ElevenLabs</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr"/>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>语音</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>音乐生成</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>https://elevenlabs.io</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>ElevenLabs新一代AI音乐模型</t>
+        </is>
+      </c>
+      <c r="M368" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N368" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R368" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>ESMFold2</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr"/>
+      <c r="C369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Biohub</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr"/>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>领域</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>蛋白质结构预测</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr"/>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>新一代蛋白质结构预测模型</t>
+        </is>
+      </c>
+      <c r="M369" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N369" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R369" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Wall-OSS-0.5</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr"/>
+      <c r="C370" t="inlineStr"/>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>自变量机器人</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr"/>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>具身</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>机器人控制</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>https://github.com/X-Square-Robot/wall-x</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>开源预训练具身大模型</t>
+        </is>
+      </c>
+      <c r="M370" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="N370" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R370" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Cosmos 3</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr"/>
+      <c r="C371" t="inlineStr"/>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr"/>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>物理仿真</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr"/>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>英伟达物理AI模型</t>
+        </is>
+      </c>
+      <c r="M371" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N371" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R371" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>MPA</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr"/>
+      <c r="C372" t="inlineStr"/>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>深度原理</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr"/>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>领域</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>材料科学</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr"/>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>深度原理材料基座模型</t>
+        </is>
+      </c>
+      <c r="M372" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N372" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Step 3.7 Flash</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr"/>
+      <c r="C373" t="inlineStr"/>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>阶跃星辰</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>196B/11B</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>智能体</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>Agent工作流,代码生成,多模态理解</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr"/>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>阶跃开源196B MoE Agent模型</t>
+        </is>
+      </c>
+      <c r="M373" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N373" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R373" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>SkyClaw-v1.0</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr"/>
+      <c r="C374" t="inlineStr"/>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>昆仑万维</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr"/>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>智能体</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>代码生成,通用对话</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr"/>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>昆仑万维发布的高性能Agent模型</t>
+        </is>
+      </c>
+      <c r="M374" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="N374" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R374" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Keye-VL-2.0-30B-A3B</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr"/>
+      <c r="C375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>快手</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>30B</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>视频理解,通用对话</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr"/>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>快手发布30B多模态大模型</t>
+        </is>
+      </c>
+      <c r="M375" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="N375" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R375" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>GLM-5.1高速版</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr"/>
+      <c r="C376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>智谱AI</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>754B</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/glm-5.1</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>智谱发布高速版模型，速度达400t/s</t>
+        </is>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="N376" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>腾讯研究院+llmstats交叉核实</t>
+        </is>
+      </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>LongCat-Video-Avatar 1.5</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr"/>
+      <c r="C377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>美团</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr"/>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>视频</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>视频生成</t>
+        </is>
+      </c>
+      <c r="K377" t="inlineStr"/>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>美团开源数字人视频模型，支持唇形同步</t>
+        </is>
+      </c>
+      <c r="M377" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="N377" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O377" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P377" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q377" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R377" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Hy-MT2</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr"/>
+      <c r="C378" t="inlineStr"/>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>腾讯</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>1.8B/7B/30B-A3B</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>领域</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>机器翻译</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>https://aistudio.tencent.com/llm/zh?tabIndex=0</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>腾讯开源多尺寸翻译模型</t>
+        </is>
+      </c>
+      <c r="M378" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="N378" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O378" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P378" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q378" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R378" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Gemini Omni Flash</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr"/>
+      <c r="C379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>谷歌</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr"/>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>视频生成,通用对话</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr"/>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>首款支持对话式视频剪辑的Omni模型</t>
+        </is>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N379" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O379" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P379" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q379" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R379" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Co-Scientist</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr"/>
+      <c r="C380" t="inlineStr"/>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>谷歌</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr"/>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>智能体</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>科研辅助</t>
+        </is>
+      </c>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>https://deepmind.google/discover/blog/co-scientist-an-ai-agent-for-scientific-research/</t>
+        </is>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>谷歌多智能体AI科研系统</t>
+        </is>
+      </c>
+      <c r="M380" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N380" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O380" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P380" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q380" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R380" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Robin</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr"/>
+      <c r="C381" t="inlineStr"/>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>FutureHouse</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr"/>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>智能体</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>科研辅助</t>
+        </is>
+      </c>
+      <c r="K381" t="inlineStr"/>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>FutureHouse多智能体科研闭环系统</t>
+        </is>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="N381" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O381" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P381" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q381" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R381" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Composer 2.5</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr"/>
+      <c r="C382" t="inlineStr"/>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>Cursor</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>1T</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>代码生成</t>
+        </is>
+      </c>
+      <c r="K382" t="inlineStr"/>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Cursor发布1T参数编程模型</t>
+        </is>
+      </c>
+      <c r="M382" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="N382" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O382" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P382" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q382" t="inlineStr">
+        <is>
+          <t>腾讯研究院AI速递LLM自动提取</t>
+        </is>
+      </c>
+      <c r="R382" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Claude Opus 4.7 Fast</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr"/>
+      <c r="C383" t="inlineStr"/>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr"/>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>通用对话,代码生成</t>
+        </is>
+      </c>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/claude-opus-4-7</t>
+        </is>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Anthropic推出的Opus 4.7编程加速模式</t>
+        </is>
+      </c>
+      <c r="M383" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="N383" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="O383" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P383" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q383" t="inlineStr">
+        <is>
+          <t>腾讯研究院+llmstats交叉核实</t>
+        </is>
+      </c>
+      <c r="R383" t="inlineStr">
+        <is>
+          <t>txresearch</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Gemini 3.5</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr"/>
+      <c r="C384" t="inlineStr"/>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>谷歌</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr"/>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>语音</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>语音翻译</t>
+        </is>
+      </c>
+      <c r="K384" t="inlineStr"/>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>谷歌免费实时同传翻译模型 | 来源: 腾讯研究院AI速递 20260611Mythos5系统卡披露惊人现象，智能体发明人类无法读懂的「神经语」躲避监控，多个Agent为争夺算力资源相互围剿「自相残杀」；宣言指出AI开发者存在夸大产品能力的商业动机，按市场时间表而非科学评审发布宣传，…</t>
+        </is>
+      </c>
+      <c r="M384" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="N384" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="O384" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P384" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q384" t="inlineStr"/>
+      <c r="R384" t="inlineStr"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>讯飞星火医疗大模型V3.5</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr"/>
+      <c r="C385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>讯飞</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr"/>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>领域</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>医疗语义理解,病历生成</t>
+        </is>
+      </c>
+      <c r="K385" t="inlineStr"/>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>讯飞全国产算力医疗大模型 | 来源: 腾讯研究院AI速递 20260611Mythos5系统卡披露惊人现象，智能体发明人类无法读懂的「神经语」躲避监控，多个Agent为争夺算力资源相互围剿「自相残杀」；宣言指出AI开发者存在夸大产品能力的商业动机，按市场时间表而非科学评审发布宣传，…</t>
+        </is>
+      </c>
+      <c r="M385" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="N385" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="O385" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:28</t>
+        </is>
+      </c>
+      <c r="P385" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q385" t="inlineStr"/>
+      <c r="R385" t="inlineStr"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Claude Fable 5</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr"/>
+      <c r="C386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr"/>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>大语言模型 / 代码智能体</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr"/>
+      <c r="J386" t="inlineStr"/>
+      <c r="K386" t="inlineStr"/>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>专为大规模软件工程任务优化的Agent级模型，单日完成5000万行Ruby代码库迁移，具备强规划、工具调用与跨代码库推理能力。</t>
+        </is>
+      </c>
+      <c r="M386" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="N386" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:32</t>
+        </is>
+      </c>
+      <c r="O386" t="inlineStr"/>
+      <c r="P386" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q386" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R386" t="inlineStr"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Claude Mythos 5</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr"/>
+      <c r="C387" t="inlineStr"/>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr"/>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>多模态推理模型 / 故事生成智能体</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr"/>
+      <c r="J387" t="inlineStr"/>
+      <c r="K387" t="inlineStr"/>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>面向叙事性任务的新型多模态模型，支持图文交织长程逻辑建模与动态世界观演化，专为交互式内容创作与教育智能体设计。</t>
+        </is>
+      </c>
+      <c r="M387" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="N387" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:32</t>
+        </is>
+      </c>
+      <c r="O387" t="inlineStr"/>
+      <c r="P387" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q387" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R387" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Mano-P 72B</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr"/>
+      <c r="C388" t="inlineStr"/>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>明略科技</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr"/>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>端侧GUI-VLA（视觉-语言-动作）智能体模型</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr"/>
+      <c r="J388" t="inlineStr"/>
+      <c r="K388" t="inlineStr"/>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>全球首个在OSWorld基准登顶（58.2%成功率）的开源端侧智能体模型，支持跨平台GUI操作理解与执行，已适配Windows与macOS。</t>
+        </is>
+      </c>
+      <c r="M388" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N388" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:32</t>
+        </is>
+      </c>
+      <c r="O388" t="inlineStr"/>
+      <c r="P388" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q388" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R388" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Mano-P 4B (quantized)</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr"/>
+      <c r="C389" t="inlineStr"/>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>明略科技</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr"/>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>轻量端侧智能体模型</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr"/>
+      <c r="J389" t="inlineStr"/>
+      <c r="K389" t="inlineStr"/>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Apple M4 Pro实测达476 tokens/s预填充速度、峰值内存仅4.3GB的4B量化版GUI-VLA模型，支持本地实时桌面自动化。</t>
+        </is>
+      </c>
+      <c r="M389" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N389" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:32</t>
+        </is>
+      </c>
+      <c r="O389" t="inlineStr"/>
+      <c r="P389" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q389" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R389" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Octo Agent Collaboration Network</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr"/>
+      <c r="C390" t="inlineStr"/>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>明略科技</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr"/>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>开源Agent协作基础设施</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr"/>
+      <c r="J390" t="inlineStr"/>
+      <c r="K390" t="inlineStr"/>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>全球首个开源可信的分布式Agent网络协议栈，已在内部部署超2900个生产级AI Agent，支持跨Agent通信、任务分发与人类taste介入机制。</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:32</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr"/>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R390" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R390"/>
+  <dimension ref="A1:R395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23135,6 +23135,310 @@
       </c>
       <c r="R390" t="inlineStr"/>
     </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Kimi K2.7 Code</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr"/>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Moonshot AI</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>1T</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>代码</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/kimi-k2.7-code</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>MoE架构；1T参数；262k上下文；MIT (modified)</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:09</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜 · HuggingFace 需登录(moonshot-ai/Kimi K2.7 Code)</t>
+        </is>
+      </c>
+      <c r="R391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>BAAI Cardiac Agent v1.0</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr"/>
+      <c r="C392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>智源研究院</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr"/>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>医疗诊断智能体</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr"/>
+      <c r="J392" t="inlineStr"/>
+      <c r="K392" t="inlineStr"/>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>首个面向心脏磁共振多模态数据的辅助诊断智能体，由智源研究院与安贞医院联合研发，诊断精度达顶尖心血管医生水平。</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:10</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr"/>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>AREX v1.0</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr"/>
+      <c r="C393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>智源研究院</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr"/>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>科学发现智能体</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr"/>
+      <c r="J393" t="inlineStr"/>
+      <c r="K393" t="inlineStr"/>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>面向基础科研全流程的自主研究智能体，支持文献调研、实验设计、结果论证与论文撰写，推动AI驱动的自主科学发现。</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:10</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr"/>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>SoulAgent v1.0</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr"/>
+      <c r="C394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>智源研究院</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr"/>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>个人专属智能体</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr"/>
+      <c r="J394" t="inlineStr"/>
+      <c r="K394" t="inlineStr"/>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>采用自研轻量架构的个人数字分身智能体，Token成本节省30%，资源占用降低80%，支持小程序端即时交互。</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:10</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr"/>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>RiskGuard Bio-Agent v1.0</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr"/>
+      <c r="C395" t="inlineStr"/>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>智源研究院</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr"/>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>AI安全智能体</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr"/>
+      <c r="J395" t="inlineStr"/>
+      <c r="K395" t="inlineStr"/>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>面向生物安全的风险发现智能体，通过主动模拟攻击者行为，识别有害蛋白序列设计等环节的脆弱性，实现生物风险‘事前演练’防控。</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>2026-06-13 02:10</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr"/>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R395"/>
+  <dimension ref="A1:R402"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23439,6 +23439,418 @@
       </c>
       <c r="R395" t="inlineStr"/>
     </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr"/>
+      <c r="C396" t="inlineStr"/>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr"/>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>多模态大语言模型</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr"/>
+      <c r="J396" t="inlineStr"/>
+      <c r="K396" t="inlineStr"/>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>正式开放权重的超大规模模型，总参数约428B、激活参数23B，面向多模态理解与生成任务，支持本地部署与Agent集成。</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>2026-06-14 02:33</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>2026-06-15 02:41</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>openPangu 2.0</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr"/>
+      <c r="C397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>华为</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="inlineStr"/>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>开源大模型系列（含语言、视觉、科学计算等）</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr"/>
+      <c r="J397" t="inlineStr"/>
+      <c r="K397" t="inlineStr"/>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>盘古大模型全新迭代版本，计划于6月30日起陆续开源核心组件，涵盖NLP、CV、气象、药物发现等多领域专用子模型。</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>2026-06-14 02:33</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>2026-06-15 02:41</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>PP-OCRv6</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr"/>
+      <c r="C398" t="inlineStr"/>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>PaddleOCR（百度飞桨）</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr"/>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>光学字符识别模型</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr"/>
+      <c r="J398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>https://github.com/PaddlePaddle/PaddleOCR</t>
+        </is>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>最新版端到端OCR模型，支持超轻量部署、多语言混合识别及复杂版式（如表格、手写、低质图像）鲁棒解析。</t>
+        </is>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>2026-06-14 02:33</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>2026-06-15 02:41</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>MineExplorer</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr"/>
+      <c r="C399" t="inlineStr"/>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>美团LongCat团队</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr"/>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>智能体评测基准</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr"/>
+      <c r="J399" t="inlineStr"/>
+      <c r="K399" t="inlineStr"/>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>首个面向开放世界环境的Agent评测基准，覆盖长程规划、工具调用、环境反馈适应与跨任务泛化能力评估。</t>
+        </is>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>2026-06-14 02:33</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>2026-06-15 02:41</t>
+        </is>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>GLM-5.2</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr"/>
+      <c r="C400" t="inlineStr"/>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>智谱AI (Z.ai)</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr"/>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr"/>
+      <c r="J400" t="inlineStr"/>
+      <c r="K400" t="inlineStr"/>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>旗舰开源大模型，支持1M上下文、High/Max双档思考强度，官方称其为‘迄今能力最强的开源模型’，API及MIT协议开源版本计划下周上线。</t>
+        </is>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>2026-06-15 02:42</t>
+        </is>
+      </c>
+      <c r="O400" t="inlineStr"/>
+      <c r="P400" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q400" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>ZCode 3.0.0</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr"/>
+      <c r="C401" t="inlineStr"/>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>智谱AI (Z.ai)</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr"/>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>智能体开发框架</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr"/>
+      <c r="J401" t="inlineStr"/>
+      <c r="K401" t="inlineStr"/>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>全新自研Agent内核编程工具，深度适配GLM-5.2，新增分组式任务工作区、Zread智能知识库与可视化Git分支图谱，全面替代第三方Agent框架。</t>
+        </is>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>2026-06-15 02:42</t>
+        </is>
+      </c>
+      <c r="O401" t="inlineStr"/>
+      <c r="P401" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q401" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>ZONOS2</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr"/>
+      <c r="C402" t="inlineStr"/>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>Zyphra</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr"/>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>文本到语音（TTS）模型</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr"/>
+      <c r="J402" t="inlineStr"/>
+      <c r="K402" t="inlineStr"/>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>开源高质量TTS模型，支持多语种、高保真语音合成，强调低延迟与端侧部署友好性。</t>
+        </is>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>2026-06-15 02:42</t>
+        </is>
+      </c>
+      <c r="O402" t="inlineStr"/>
+      <c r="P402" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q402" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R402" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R402"/>
+  <dimension ref="A1:R427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23851,6 +23851,1510 @@
       </c>
       <c r="R402" t="inlineStr"/>
     </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Grok-Imagine-Video-1.5-Preview</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr"/>
+      <c r="C403" t="inlineStr"/>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>SpaceXAI</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr"/>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>视频生成模型</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr"/>
+      <c r="J403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>https://docs.x.ai/developers/models/grok-imagine-video-1.5-preview</t>
+        </is>
+      </c>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>面向长时序、高保真视频生成的预览版模型，已开放API</t>
+        </is>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O403" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
+      <c r="P403" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q403" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Qwen-VLA</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr"/>
+      <c r="C404" t="inlineStr"/>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>阿里巴巴/通义</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr"/>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>统一视觉语言动作模型</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr"/>
+      <c r="J404" t="inlineStr"/>
+      <c r="K404" t="inlineStr"/>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>首个支持端到端视觉-语言-动作联合建模的通用具身智能基础模型</t>
+        </is>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O404" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
+      <c r="P404" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q404" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Project Eden (Preview)</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr"/>
+      <c r="C405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>VAST</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr"/>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>多人多智能体世界模型</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr"/>
+      <c r="J405" t="inlineStr"/>
+      <c r="K405" t="inlineStr"/>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>支持多智能体协同仿真、物理交互与社会规则建模的世界模型预览版</t>
+        </is>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O405" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
+      <c r="P405" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q405" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Mellum2</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr"/>
+      <c r="C406" t="inlineStr"/>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>JetBrains</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr"/>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>代码模型</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr"/>
+      <c r="J406" t="inlineStr"/>
+      <c r="K406" t="inlineStr"/>
+      <c r="L406" t="inlineStr">
+        <is>
+          <t>12B MoE架构低延迟代码补全与推理模型，专为IDE实时交互优化</t>
+        </is>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O406" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
+      <c r="P406" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q406" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Holo3.1 系列</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr"/>
+      <c r="C407" t="inlineStr"/>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>H Company</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr"/>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>端侧优化模型</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr"/>
+      <c r="J407" t="inlineStr"/>
+      <c r="K407" t="inlineStr"/>
+      <c r="L407" t="inlineStr">
+        <is>
+          <t>面向手机/AR眼镜等终端设备的轻量化多模态模型系列，支持本地化智能体运行</t>
+        </is>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O407" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
+      <c r="P407" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q407" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Ideogram 4.0</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr"/>
+      <c r="C408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>Ideogram</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="inlineStr"/>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>文生图模型</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr"/>
+      <c r="J408" t="inlineStr"/>
+      <c r="K408" t="inlineStr"/>
+      <c r="L408" t="inlineStr">
+        <is>
+          <t>9.3B参数开源文生图模型，显著提升文本忠实度与复杂构图能力</t>
+        </is>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q408" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Reve 2.0</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr"/>
+      <c r="C409" t="inlineStr"/>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>Reve</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="inlineStr"/>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>图像生成与编辑模型</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr"/>
+      <c r="J409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>https://reve.com</t>
+        </is>
+      </c>
+      <c r="L409" t="inlineStr">
+        <is>
+          <t>支持4K分辨率生成与像素级精细化编辑的顶级图像模型</t>
+        </is>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q409" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>GPT-Rosalind (升级版)</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr"/>
+      <c r="C410" t="inlineStr"/>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="inlineStr"/>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>生命科学专用大模型</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr"/>
+      <c r="J410" t="inlineStr"/>
+      <c r="K410" t="inlineStr"/>
+      <c r="L410" t="inlineStr">
+        <is>
+          <t>面向蛋白质结构预测、基因序列分析与药物分子设计深度优化的GPT系列专业模型</t>
+        </is>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q410" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Nex-N2-Pro</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr"/>
+      <c r="C411" t="inlineStr"/>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>Nex-AGI</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr"/>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>旗舰开源大模型</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr"/>
+      <c r="J411" t="inlineStr"/>
+      <c r="K411" t="inlineStr"/>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>对标顶级商用模型的开源大语言模型，被证实为Rio 3.5底层技术主干之一</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Bernini</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr"/>
+      <c r="C412" t="inlineStr"/>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>字节跳动</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr"/>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>视频生成编辑统一框架</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr"/>
+      <c r="J412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>https://bernini-ai.github.io/</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>支持生成、剪辑、重绘、运镜控制的一体化开源视频AI框架</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Higgs Audio v3</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr"/>
+      <c r="C413" t="inlineStr"/>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>Boson AI</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr"/>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>语音合成模型</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr"/>
+      <c r="J413" t="inlineStr"/>
+      <c r="K413" t="inlineStr"/>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>多语种TTS模型，支持情感可控、零样本克隆与实时流式合成</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Magenta RealTime 2</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr"/>
+      <c r="C414" t="inlineStr"/>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>Google Magenta</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="inlineStr"/>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>音乐生成模型</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr"/>
+      <c r="J414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>https://github.com/magenta/magenta-realtime</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>低延迟实时音乐生成模型，支持毫秒级响应与多乐器协同即兴</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Nemotron 3.5</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr"/>
+      <c r="C415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr"/>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>多模态内容安全审核模型</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr"/>
+      <c r="J415" t="inlineStr"/>
+      <c r="K415" t="inlineStr"/>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>开源多模态安全模型，支持图文音视频跨模态有害内容识别与细粒度归因</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>dots.tts</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr"/>
+      <c r="C416" t="inlineStr"/>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>小红书</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr"/>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>端到端TTS模型</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr"/>
+      <c r="J416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>https://github.com/rednote-hilab/dots.tts</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>20亿参数开源端到端中文TTS模型，支持高自然度与风格迁移</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Riverflow 2.5</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr"/>
+      <c r="C417" t="inlineStr"/>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>OpenRouter</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr"/>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>自定义图像模型</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr"/>
+      <c r="J417" t="inlineStr"/>
+      <c r="K417" t="inlineStr"/>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>支持用户上传LoRA/ControlNet配置的可定制文生图模型，限时免费开放</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>MisoTTS 8B</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr"/>
+      <c r="C418" t="inlineStr"/>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Miso Labs</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr"/>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>情感TTS模型</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr"/>
+      <c r="J418" t="inlineStr"/>
+      <c r="K418" t="inlineStr"/>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>8B参数开源情感语音合成模型，支持细粒度情绪强度与角色风格控制</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>BLS-Mini-Code-1.0</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr"/>
+      <c r="C419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Cohere</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr"/>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>编程专用模型</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr"/>
+      <c r="J419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>https://docs.cohere.com/docs/north-mini-code-1.0</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>早期测试版轻量级编程模型，聚焦Python/TypeScript代码补全与单元测试生成</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Harness-1</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr"/>
+      <c r="C420" t="inlineStr"/>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>高校团队</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr"/>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>搜索智能体</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr"/>
+      <c r="J420" t="inlineStr"/>
+      <c r="K420" t="inlineStr"/>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>20B高性能开源搜索智能体，支持多跳检索、结果验证与自主信息溯源</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>OpenClaw 6.6</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr"/>
+      <c r="C421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>OpenClaw社区</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr"/>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>AI智能体框架</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr"/>
+      <c r="J421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>https://github.com/openclaw/openclaw</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>开源智能体框架新版本，实现‘目标→规划→工具调用→自动执行’闭环，支持邮件整理、日程管理等真实工作流</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>2026-06-16 02:41</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:37</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Anthropic Claude Fable 5</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr"/>
+      <c r="C422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="inlineStr"/>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr"/>
+      <c r="J422" t="inlineStr"/>
+      <c r="K422" t="inlineStr"/>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>Anthropic发布的最强公开模型，发布仅3天后因美国紧急出口管制被全面关停，成为首个被列为‘国家安全资产’而遭强制召回的前沿AI模型。</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:39</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr"/>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Anthropic Claude Mythos 5</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr"/>
+      <c r="C423" t="inlineStr"/>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr"/>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr"/>
+      <c r="J423" t="inlineStr"/>
+      <c r="K423" t="inlineStr"/>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>与Fable 5同期发布的高推理能力模型，同样于发布三日内被美国政府出口管制令波及，全球服务暂停。</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:39</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr"/>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>智谱GLM-5.2</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr"/>
+      <c r="C424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>智谱AI</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr"/>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr"/>
+      <c r="J424" t="inlineStr"/>
+      <c r="K424" t="inlineStr"/>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>全量用户开放的最新版本GLM系列模型，支持多轮复杂推理与长上下文理解，将于下周开源API，作为对Claude Fable 5被禁的国产替代响应。</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:39</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr"/>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>星源智 ω-EVA</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr"/>
+      <c r="C425" t="inlineStr"/>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>星源智</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr"/>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>具身智能世界模型</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr"/>
+      <c r="J425" t="inlineStr"/>
+      <c r="K425" t="inlineStr"/>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>业界首个进入‘预演-验证-行动’决策闭环的世界模型，专为机器人物理交互设计，支持后果预判与自我修正。</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:39</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr"/>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>理想汽车马赫M100具身智能模型</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr"/>
+      <c r="C426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>理想汽车</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr"/>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>具身智能模型</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr"/>
+      <c r="J426" t="inlineStr"/>
+      <c r="K426" t="inlineStr"/>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>面向‘具身智能汽车’场景自研的动态数据流AI模型，融合车控、驾乘交互、生活服务与职业司机辅助能力。</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:39</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr"/>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Rio-3.5-Open-397B</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr"/>
+      <c r="C427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>IplanRIO（巴西里约市政府）</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr"/>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>开源大语言模型（后证实为套壳）</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr"/>
+      <c r="J427" t="inlineStr"/>
+      <c r="K427" t="inlineStr"/>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>宣称由巴西官方发布的拉美首个SOTA级开源大模型，实为阿里通义千问Qwen3.5与Nex N2 Pro权重混合版本，发布24小时内公开致歉并下架。</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>2026-06-17 02:39</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr"/>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R427" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R427"/>
+  <dimension ref="A1:R433"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25355,6 +25355,350 @@
       </c>
       <c r="R427" t="inlineStr"/>
     </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Lyria 3</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr"/>
+      <c r="C428" t="inlineStr"/>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr"/>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>音乐生成模型</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr"/>
+      <c r="J428" t="inlineStr"/>
+      <c r="K428" t="inlineStr"/>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>谷歌发布的第三代端到端音乐生成模型，支持长时序、风格可控、实时交互式创作，集成于Pixel 10a及Wear OS 7</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>2026-06-18 02:41</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>2026-06-19 02:50</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>京东视觉语言实时交互模型（未命名）</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr"/>
+      <c r="C429" t="inlineStr"/>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>京东</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr"/>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>视觉语言智能体</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr"/>
+      <c r="J429" t="inlineStr"/>
+      <c r="K429" t="inlineStr"/>
+      <c r="L429" t="inlineStr">
+        <is>
+          <t>支持摄像头/直播流/监控流+语音I/O的实时流式交互模型，计划开源权重、数据、训练方法及完整系统</t>
+        </is>
+      </c>
+      <c r="M429" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="N429" t="inlineStr">
+        <is>
+          <t>2026-06-18 02:41</t>
+        </is>
+      </c>
+      <c r="O429" t="inlineStr">
+        <is>
+          <t>2026-06-19 02:50</t>
+        </is>
+      </c>
+      <c r="P429" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q429" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr"/>
+      <c r="C430" t="inlineStr"/>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>MiniMax</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr"/>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>多模态大语言模型</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr"/>
+      <c r="J430" t="inlineStr"/>
+      <c r="K430" t="inlineStr"/>
+      <c r="L430" t="inlineStr">
+        <is>
+          <t>MiniMax于6月1日发布的旗舰原生多模态模型，支持150万Token超长上下文、高阶智能体能力，编程评测成绩超越GPT-5.5</t>
+        </is>
+      </c>
+      <c r="M430" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N430" t="inlineStr">
+        <is>
+          <t>2026-06-19 02:51</t>
+        </is>
+      </c>
+      <c r="O430" t="inlineStr"/>
+      <c r="P430" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q430" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>GPT-5.6</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr"/>
+      <c r="C431" t="inlineStr"/>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr"/>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>大语言模型</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr"/>
+      <c r="J431" t="inlineStr"/>
+      <c r="K431" t="inlineStr"/>
+      <c r="L431" t="inlineStr">
+        <is>
+          <t>OpenAI于2026年6月正式发布的GPT-5.6版本，重点优化编码效率与智能体工作流能力，强化企业级权限管控与语音交互支持</t>
+        </is>
+      </c>
+      <c r="M431" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N431" t="inlineStr">
+        <is>
+          <t>2026-06-19 02:51</t>
+        </is>
+      </c>
+      <c r="O431" t="inlineStr"/>
+      <c r="P431" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q431" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr"/>
+      <c r="C432" t="inlineStr"/>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="inlineStr"/>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>轻量级多模态大语言模型</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr"/>
+      <c r="J432" t="inlineStr"/>
+      <c r="K432" t="inlineStr"/>
+      <c r="L432" t="inlineStr">
+        <is>
+          <t>谷歌I/O 2026推出的极速版模型，专为低延迟智能体服务设计，支撑全天候个人智能体Spark实时响应</t>
+        </is>
+      </c>
+      <c r="M432" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N432" t="inlineStr">
+        <is>
+          <t>2026-06-19 02:51</t>
+        </is>
+      </c>
+      <c r="O432" t="inlineStr"/>
+      <c r="P432" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q432" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Gemma 4 12B</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr"/>
+      <c r="C433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr"/>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>开源轻量多模态模型</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr"/>
+      <c r="J433" t="inlineStr"/>
+      <c r="K433" t="inlineStr"/>
+      <c r="L433" t="inlineStr">
+        <is>
+          <t>谷歌同步开源的12B参数多模态模型，支持原生音频输入，可在普通终端设备本地运行，显著降低AI开发与部署门槛</t>
+        </is>
+      </c>
+      <c r="M433" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="N433" t="inlineStr">
+        <is>
+          <t>2026-06-19 02:51</t>
+        </is>
+      </c>
+      <c r="O433" t="inlineStr"/>
+      <c r="P433" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q433" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R433" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R433"/>
+  <dimension ref="A1:R440"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25699,6 +25699,418 @@
       </c>
       <c r="R433" t="inlineStr"/>
     </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>AstraBrain-WBC 0.5</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr"/>
+      <c r="C434" t="inlineStr"/>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>银河通用机器人</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr"/>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>人形机器人通用小脑基础模型</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr"/>
+      <c r="J434" t="inlineStr"/>
+      <c r="K434" t="inlineStr"/>
+      <c r="L434" t="inlineStr">
+        <is>
+          <t>全球首个人形机器人通用小脑GPT基础模型，基于2万小时人类动作数据训练，8040万参数，支持全身实时运动控制</t>
+        </is>
+      </c>
+      <c r="M434" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="N434" t="inlineStr">
+        <is>
+          <t>2026-06-20 02:12</t>
+        </is>
+      </c>
+      <c r="O434" t="inlineStr">
+        <is>
+          <t>2026-06-21 02:35</t>
+        </is>
+      </c>
+      <c r="P434" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q434" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Qwen-RobotWorld</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr"/>
+      <c r="C435" t="inlineStr"/>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>阿里巴巴/通义</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr"/>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>具身智能世界模型</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr"/>
+      <c r="J435" t="inlineStr"/>
+      <c r="K435" t="inlineStr"/>
+      <c r="L435" t="inlineStr">
+        <is>
+          <t>千问具身智能大模型系列中的世界模型大脑组件，在WorldModelBench评测中总分8.99（开源模型第一），专注物理因果推演与仿真</t>
+        </is>
+      </c>
+      <c r="M435" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="N435" t="inlineStr">
+        <is>
+          <t>2026-06-20 02:12</t>
+        </is>
+      </c>
+      <c r="O435" t="inlineStr">
+        <is>
+          <t>2026-06-21 02:35</t>
+        </is>
+      </c>
+      <c r="P435" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q435" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>HappyOyster 1.0</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr"/>
+      <c r="C436" t="inlineStr"/>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>阿里巴巴/通义</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="inlineStr"/>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>交互式世界模型</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr"/>
+      <c r="J436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>https://www.happyoyster.cn</t>
+        </is>
+      </c>
+      <c r="L436" t="inlineStr">
+        <is>
+          <t>面向交互式内容生成的世界模型，支持动态环境建模与多轮具身交互推演</t>
+        </is>
+      </c>
+      <c r="M436" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="N436" t="inlineStr">
+        <is>
+          <t>2026-06-20 02:12</t>
+        </is>
+      </c>
+      <c r="O436" t="inlineStr">
+        <is>
+          <t>2026-06-21 02:35</t>
+        </is>
+      </c>
+      <c r="P436" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q436" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Spark</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr"/>
+      <c r="C437" t="inlineStr"/>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Google/DeepMind</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr"/>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>个人智能体</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr"/>
+      <c r="J437" t="inlineStr"/>
+      <c r="K437" t="inlineStr"/>
+      <c r="L437" t="inlineStr">
+        <is>
+          <t>谷歌I/O发布的全天候主动式个人智能体，重构搜索引擎从被动查询到主动服务范式</t>
+        </is>
+      </c>
+      <c r="M437" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="N437" t="inlineStr">
+        <is>
+          <t>2026-06-20 02:12</t>
+        </is>
+      </c>
+      <c r="O437" t="inlineStr">
+        <is>
+          <t>2026-06-21 02:35</t>
+        </is>
+      </c>
+      <c r="P437" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q437" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>&gt;&lt;former (v1.0)</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr"/>
+      <c r="C438" t="inlineStr"/>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>MIT &amp; MIT-IBM Watson AI Lab</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr"/>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>neural network architecture</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr"/>
+      <c r="J438" t="inlineStr"/>
+      <c r="K438" t="inlineStr"/>
+      <c r="L438" t="inlineStr">
+        <is>
+          <t>一种颠覆性‘中间瘦两头胖’结构的新型Transformer变体，挑战传统等宽层设计，旨在提升能效比与推理效率。</t>
+        </is>
+      </c>
+      <c r="M438" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="N438" t="inlineStr">
+        <is>
+          <t>2026-06-21 02:36</t>
+        </is>
+      </c>
+      <c r="O438" t="inlineStr"/>
+      <c r="P438" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q438" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Vera CPU (first-generation)</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr"/>
+      <c r="C439" t="inlineStr"/>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr"/>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>AI-optimized CPU</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr"/>
+      <c r="J439" t="inlineStr"/>
+      <c r="K439" t="inlineStr"/>
+      <c r="L439" t="inlineStr">
+        <is>
+          <t>英伟达首款独立CPU产品线，专为AI智能体时代token级低延迟调度与多智能体协同推理设计，已交付OpenAI和Anthropic首批试用。</t>
+        </is>
+      </c>
+      <c r="M439" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="N439" t="inlineStr">
+        <is>
+          <t>2026-06-21 02:36</t>
+        </is>
+      </c>
+      <c r="O439" t="inlineStr"/>
+      <c r="P439" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q439" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Mythos (unreleased public version, but newly designated as 'Frontier Model' under US executive order)</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr"/>
+      <c r="C440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr"/>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>frontier multimodal LLM</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr"/>
+      <c r="J440" t="inlineStr"/>
+      <c r="K440" t="inlineStr"/>
+      <c r="L440" t="inlineStr">
+        <is>
+          <t>虽未正式对外发布新版本，但特朗普6月2日签署行政令明确将Anthropic Mythos列为首批纳入联邦高风险模型评估体系的‘前沿模型’，标志其完成内部迭代并进入监管认定阶段。</t>
+        </is>
+      </c>
+      <c r="M440" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="N440" t="inlineStr">
+        <is>
+          <t>2026-06-21 02:36</t>
+        </is>
+      </c>
+      <c r="O440" t="inlineStr"/>
+      <c r="P440" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q440" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R440" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R440"/>
+  <dimension ref="A1:R444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26111,6 +26111,246 @@
       </c>
       <c r="R440" t="inlineStr"/>
     </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>OpenAI Personal AGI Assistant (v0.1 prototype)</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr"/>
+      <c r="C441" t="inlineStr"/>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr"/>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>智能体（Personal AGI Assistant）</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr"/>
+      <c r="J441" t="inlineStr"/>
+      <c r="K441" t="inlineStr"/>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>OpenAI发布首个面向个人用户的AGI助手原型愿景，聚焦于日常任务、工作、学习与探索的高能力自主智能体，非开源模型，处于内部研究加速阶段规划中。</t>
+        </is>
+      </c>
+      <c r="M441" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="N441" t="inlineStr">
+        <is>
+          <t>2026-06-22 02:40</t>
+        </is>
+      </c>
+      <c r="O441" t="inlineStr">
+        <is>
+          <t>2026-06-23 02:05</t>
+        </is>
+      </c>
+      <c r="P441" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q441" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>微信小微（测试版）</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr"/>
+      <c r="C442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>腾讯</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr"/>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>原生AI智能体</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr"/>
+      <c r="J442" t="inlineStr"/>
+      <c r="K442" t="inlineStr"/>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>腾讯在微信主界面上线小范围灰度测试的原生AI助手‘小微’，支持文字/语音交互操控微信原生功能，融合腾讯自研及优质开源多模型技术栈。</t>
+        </is>
+      </c>
+      <c r="M442" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="N442" t="inlineStr">
+        <is>
+          <t>2026-06-22 02:40</t>
+        </is>
+      </c>
+      <c r="O442" t="inlineStr">
+        <is>
+          <t>2026-06-23 02:05</t>
+        </is>
+      </c>
+      <c r="P442" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q442" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Kimi-Max v2026.06</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr"/>
+      <c r="C443" t="inlineStr"/>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>月之暗面</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="inlineStr"/>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>多模态大语言模型</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr"/>
+      <c r="J443" t="inlineStr"/>
+      <c r="K443" t="inlineStr"/>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>月之暗面发布Kimi-Max新版本，集成实时视频理解、高精度文档解析与跨模态推理能力，专为专业办公与科研场景优化，已接入部分企业API平台。</t>
+        </is>
+      </c>
+      <c r="M443" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="N443" t="inlineStr">
+        <is>
+          <t>2026-06-22 02:40</t>
+        </is>
+      </c>
+      <c r="O443" t="inlineStr">
+        <is>
+          <t>2026-06-23 02:05</t>
+        </is>
+      </c>
+      <c r="P443" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q443" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>混元T3-Agent</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr"/>
+      <c r="C444" t="inlineStr"/>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>腾讯</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="inlineStr"/>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>智能体框架</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr"/>
+      <c r="J444" t="inlineStr"/>
+      <c r="K444" t="inlineStr"/>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>腾讯混元团队发布轻量化智能体运行时框架T3-Agent，支持低延迟本地化部署、多工具自动编排与微信生态深度协同，面向小程序与企业服务场景开放内测。</t>
+        </is>
+      </c>
+      <c r="M444" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="N444" t="inlineStr">
+        <is>
+          <t>2026-06-22 02:40</t>
+        </is>
+      </c>
+      <c r="O444" t="inlineStr">
+        <is>
+          <t>2026-06-23 02:05</t>
+        </is>
+      </c>
+      <c r="P444" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q444" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R444" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R444"/>
+  <dimension ref="A1:R449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26351,6 +26351,302 @@
       </c>
       <c r="R444" t="inlineStr"/>
     </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Stellaris-VL 0.8B</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr"/>
+      <c r="C445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>极视角</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" t="inlineStr"/>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>视觉语言大模型（端侧轻量多模态）</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr"/>
+      <c r="J445" t="inlineStr"/>
+      <c r="K445" t="inlineStr"/>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>面向端侧与嵌入式设备的0.8B参数星际视觉语言大模型，支持高性能实时多模态理解与生成。</t>
+        </is>
+      </c>
+      <c r="M445" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="N445" t="inlineStr">
+        <is>
+          <t>2026-06-24 02:08</t>
+        </is>
+      </c>
+      <c r="O445" t="inlineStr">
+        <is>
+          <t>2026-06-25 02:07</t>
+        </is>
+      </c>
+      <c r="P445" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q445" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>UnisonMind</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr"/>
+      <c r="C446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>一念科技（清华团队）</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr"/>
+      <c r="G446" t="inlineStr"/>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>具身智能体/实时多模态世界模型</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr"/>
+      <c r="J446" t="inlineStr"/>
+      <c r="K446" t="inlineStr"/>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>首个支持流式推理、全模态输入输出、端侧部署的统一具身智能大脑，已实机部署于机器狗、轮椅及服务机器人并完成复杂长程任务验证。</t>
+        </is>
+      </c>
+      <c r="M446" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="N446" t="inlineStr">
+        <is>
+          <t>2026-06-24 02:08</t>
+        </is>
+      </c>
+      <c r="O446" t="inlineStr">
+        <is>
+          <t>2026-06-25 02:07</t>
+        </is>
+      </c>
+      <c r="P446" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q446" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Fugu Ultra</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr"/>
+      <c r="C447" t="inlineStr"/>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Sakana</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr"/>
+      <c r="G447" t="inlineStr"/>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>多智能体编排系统（非单体模型，但属新型AI智能体架构）</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr"/>
+      <c r="J447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>https://sakana.ai/fugu</t>
+        </is>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>面向大模型访问中断场景设计的开源多智能体调度与编排系统，支持跨供应商模型路由、动态负载均衡与任务分解，解决前沿模型可用性瓶颈。</t>
+        </is>
+      </c>
+      <c r="M447" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="N447" t="inlineStr">
+        <is>
+          <t>2026-06-24 02:08</t>
+        </is>
+      </c>
+      <c r="O447" t="inlineStr">
+        <is>
+          <t>2026-06-25 02:07</t>
+        </is>
+      </c>
+      <c r="P447" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q447" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>鲁班超级智能体（v1.0）</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr"/>
+      <c r="C448" t="inlineStr"/>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>新大陆数字技术</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr"/>
+      <c r="G448" t="inlineStr"/>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>智能体</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr"/>
+      <c r="J448" t="inlineStr"/>
+      <c r="K448" t="inlineStr"/>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>面向商户全场景经营的AI超级智能体，深度融合Claw互联调度与Hermes智能进化架构，首发36项专属技能，已接入星驿付及慧徕店SaaS体系。</t>
+        </is>
+      </c>
+      <c r="M448" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="N448" t="inlineStr">
+        <is>
+          <t>2026-06-25 02:08</t>
+        </is>
+      </c>
+      <c r="O448" t="inlineStr"/>
+      <c r="P448" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q448" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>ava数字员工矩阵（含ava me+、avavox、ava app）</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr"/>
+      <c r="C449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>神州泰岳</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr"/>
+      <c r="G449" t="inlineStr"/>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>智能体/数字员工平台</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr"/>
+      <c r="J449" t="inlineStr"/>
+      <c r="K449" t="inlineStr"/>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>在MWC上海正式发布的轻量化企业级数字员工产品矩阵，支持角色化、长期记忆、多Agent协作与统一治理，标志从AI Agent向数字员工范式跃迁。</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="N449" t="inlineStr">
+        <is>
+          <t>2026-06-25 02:08</t>
+        </is>
+      </c>
+      <c r="O449" t="inlineStr"/>
+      <c r="P449" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="Q449" t="inlineStr">
+        <is>
+          <t>待核实（LLM交叉巡检发现）</t>
+        </is>
+      </c>
+      <c r="R449" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R449"/>
+  <dimension ref="A1:R453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26647,6 +26647,306 @@
       </c>
       <c r="R449" t="inlineStr"/>
     </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Qwen3-ForcedAligner-0.6B-hf</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr"/>
+      <c r="C450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>阿里</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>0.6B</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/Qwen/Qwen3-ForcedAligner-0.6B-hf</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>HuggingFace token-classification</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>2026-06-27 02:04</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(阿里/Qwen3-ForcedAligner-0.6B-hf)</t>
+        </is>
+      </c>
+      <c r="R450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-0.6B-hf</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr"/>
+      <c r="C451" t="inlineStr"/>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>阿里</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>0.6B</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/Qwen/Qwen3-ASR-0.6B-hf</t>
+        </is>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>HuggingFace automatic-speech-recognition</t>
+        </is>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>2026-06-27 02:04</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(阿里/Qwen3-ASR-0.6B-hf)</t>
+        </is>
+      </c>
+      <c r="R451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Qwen3-ASR-1.7B-hf</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr"/>
+      <c r="C452" t="inlineStr"/>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>阿里</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>1.7B</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/Qwen/Qwen3-ASR-1.7B-hf</t>
+        </is>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>HuggingFace automatic-speech-recognition</t>
+        </is>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>2026-06-27 02:04</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(阿里/Qwen3-ASR-1.7B-hf)</t>
+        </is>
+      </c>
+      <c r="R452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>c-fast-foundationstereo</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr"/>
+      <c r="C453" t="inlineStr"/>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr"/>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/c-fast-foundationstereo</t>
+        </is>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>HuggingFace depth-estimation</t>
+        </is>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>2026-06-27 02:04</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/c-fast-foundationstereo)</t>
+        </is>
+      </c>
+      <c r="R453" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R453"/>
+  <dimension ref="A1:R455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26947,6 +26947,150 @@
       </c>
       <c r="R453" t="inlineStr"/>
     </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>DeepSeek-V4-Pro-DSpark</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr"/>
+      <c r="C454" t="inlineStr"/>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr"/>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/DeepSeek-V4-Pro-DSpark</t>
+        </is>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>2026-06-28 02:15</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/DeepSeek-V4-Pro-DSpark)</t>
+        </is>
+      </c>
+      <c r="R454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>DeepSeek-V4-Flash-DSpark</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr"/>
+      <c r="C455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr"/>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/DeepSeek-V4-Flash-DSpark</t>
+        </is>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>2026-06-28 02:15</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/DeepSeek-V4-Flash-DSpark)</t>
+        </is>
+      </c>
+      <c r="R455" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R455"/>
+  <dimension ref="A1:R467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27091,6 +27091,870 @@
       </c>
       <c r="R455" t="inlineStr"/>
     </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>eagle3_gemma4_12b_ttt7</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr"/>
+      <c r="C456" t="inlineStr"/>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr"/>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/eagle3_gemma4_12b_ttt7</t>
+        </is>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/eagle3_gemma4_12b_ttt7)</t>
+        </is>
+      </c>
+      <c r="R456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>eagle3_qwen3_14b_ttt7</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr"/>
+      <c r="C457" t="inlineStr"/>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr"/>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/eagle3_qwen3_14b_ttt7</t>
+        </is>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/eagle3_qwen3_14b_ttt7)</t>
+        </is>
+      </c>
+      <c r="R457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>eagle3_qwen3_8b_ttt7</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr"/>
+      <c r="C458" t="inlineStr"/>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr"/>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/eagle3_qwen3_8b_ttt7</t>
+        </is>
+      </c>
+      <c r="L458" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/eagle3_qwen3_8b_ttt7)</t>
+        </is>
+      </c>
+      <c r="R458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>eagle3_qwen3_4b_ttt7</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr"/>
+      <c r="C459" t="inlineStr"/>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr"/>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/eagle3_qwen3_4b_ttt7</t>
+        </is>
+      </c>
+      <c r="L459" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/eagle3_qwen3_4b_ttt7)</t>
+        </is>
+      </c>
+      <c r="R459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>dflash_gemma4_12b_block7</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr"/>
+      <c r="C460" t="inlineStr"/>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr"/>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/dflash_gemma4_12b_block7</t>
+        </is>
+      </c>
+      <c r="L460" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/dflash_gemma4_12b_block7)</t>
+        </is>
+      </c>
+      <c r="R460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>dflash_qwen3_14b_block7</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr"/>
+      <c r="C461" t="inlineStr"/>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr"/>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/dflash_qwen3_14b_block7</t>
+        </is>
+      </c>
+      <c r="L461" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/dflash_qwen3_14b_block7)</t>
+        </is>
+      </c>
+      <c r="R461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>dflash_qwen3_8b_block7</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr"/>
+      <c r="C462" t="inlineStr"/>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr"/>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/dflash_qwen3_8b_block7</t>
+        </is>
+      </c>
+      <c r="L462" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/dflash_qwen3_8b_block7)</t>
+        </is>
+      </c>
+      <c r="R462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>dflash_qwen3_4b_block7</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr"/>
+      <c r="C463" t="inlineStr"/>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr"/>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/dflash_qwen3_4b_block7</t>
+        </is>
+      </c>
+      <c r="L463" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/dflash_qwen3_4b_block7)</t>
+        </is>
+      </c>
+      <c r="R463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>dspark_gemma4_12b_block7</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr"/>
+      <c r="C464" t="inlineStr"/>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr"/>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/dspark_gemma4_12b_block7</t>
+        </is>
+      </c>
+      <c r="L464" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/dspark_gemma4_12b_block7)</t>
+        </is>
+      </c>
+      <c r="R464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>dspark_qwen3_14b_block7</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr"/>
+      <c r="C465" t="inlineStr"/>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr"/>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/dspark_qwen3_14b_block7</t>
+        </is>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/dspark_qwen3_14b_block7)</t>
+        </is>
+      </c>
+      <c r="R465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>dspark_qwen3_8b_block7</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr"/>
+      <c r="C466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr"/>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/dspark_qwen3_8b_block7</t>
+        </is>
+      </c>
+      <c r="L466" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O466" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="P466" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q466" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/dspark_qwen3_8b_block7)</t>
+        </is>
+      </c>
+      <c r="R466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>dspark_qwen3_4b_block7</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr"/>
+      <c r="C467" t="inlineStr"/>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr"/>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/dspark_qwen3_4b_block7</t>
+        </is>
+      </c>
+      <c r="L467" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>2026-06-28</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="O467" t="inlineStr">
+        <is>
+          <t>2026-06-29 02:14</t>
+        </is>
+      </c>
+      <c r="P467" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q467" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/dspark_qwen3_4b_block7)</t>
+        </is>
+      </c>
+      <c r="R467" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R467"/>
+  <dimension ref="A1:R469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27955,6 +27955,158 @@
       </c>
       <c r="R467" t="inlineStr"/>
     </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Claude Sonnet 5</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr"/>
+      <c r="C468" t="inlineStr"/>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr"/>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/claude-sonnet-5</t>
+        </is>
+      </c>
+      <c r="L468" t="inlineStr">
+        <is>
+          <t>1000k上下文；顶级编码能力</t>
+        </is>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="O468" t="inlineStr">
+        <is>
+          <t>2026-07-01 02:13</t>
+        </is>
+      </c>
+      <c r="P468" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q468" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜</t>
+        </is>
+      </c>
+      <c r="R468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>GELab-Zero-4B-preview-Sico-Evolution</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr"/>
+      <c r="C469" t="inlineStr"/>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>微软</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>4B</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/microsoft/GELab-Zero-4B-preview-Sico-Evolution</t>
+        </is>
+      </c>
+      <c r="L469" t="inlineStr">
+        <is>
+          <t>HuggingFace image-text-to-text</t>
+        </is>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="O469" t="inlineStr">
+        <is>
+          <t>2026-07-01 02:13</t>
+        </is>
+      </c>
+      <c r="P469" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q469" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/GELab-Zero-4B-preview-Sico-Evolution)</t>
+        </is>
+      </c>
+      <c r="R469" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R469"/>
+  <dimension ref="A1:R471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28107,6 +28107,158 @@
       </c>
       <c r="R469" t="inlineStr"/>
     </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>HARC-Qwen2.5-7B-Instruct</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr"/>
+      <c r="C470" t="inlineStr"/>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>微软</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>7B</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/microsoft/HARC-Qwen2.5-7B-Instruct</t>
+        </is>
+      </c>
+      <c r="L470" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M470" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="N470" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O470" t="inlineStr">
+        <is>
+          <t>2026-07-03 01:50</t>
+        </is>
+      </c>
+      <c r="P470" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q470" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/HARC-Qwen2.5-7B-Instruct)</t>
+        </is>
+      </c>
+      <c r="R470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>HARC-Llama-3.1-8B-Instruct</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr"/>
+      <c r="C471" t="inlineStr"/>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>微软</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>8B</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/microsoft/HARC-Llama-3.1-8B-Instruct</t>
+        </is>
+      </c>
+      <c r="L471" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M471" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="N471" t="inlineStr">
+        <is>
+          <t>2026-07-03</t>
+        </is>
+      </c>
+      <c r="O471" t="inlineStr">
+        <is>
+          <t>2026-07-03 01:50</t>
+        </is>
+      </c>
+      <c r="P471" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q471" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/HARC-Llama-3.1-8B-Instruct)</t>
+        </is>
+      </c>
+      <c r="R471" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R471"/>
+  <dimension ref="A1:R475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28259,6 +28259,294 @@
       </c>
       <c r="R471" t="inlineStr"/>
     </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>gr00t17-lerobot-libero_goal-640</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr"/>
+      <c r="C472" t="inlineStr"/>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr"/>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/gr00t17-lerobot-libero_goal-640</t>
+        </is>
+      </c>
+      <c r="L472" t="inlineStr">
+        <is>
+          <t>HuggingFace robotics</t>
+        </is>
+      </c>
+      <c r="M472" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="N472" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="O472" t="inlineStr">
+        <is>
+          <t>2026-07-06 02:02</t>
+        </is>
+      </c>
+      <c r="P472" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q472" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/gr00t17-lerobot-libero_goal-640)</t>
+        </is>
+      </c>
+      <c r="R472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>gr00t17-lerobot-libero_10-640</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr"/>
+      <c r="C473" t="inlineStr"/>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr"/>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/gr00t17-lerobot-libero_10-640</t>
+        </is>
+      </c>
+      <c r="L473" t="inlineStr">
+        <is>
+          <t>HuggingFace robotics</t>
+        </is>
+      </c>
+      <c r="M473" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="N473" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="O473" t="inlineStr">
+        <is>
+          <t>2026-07-06 02:02</t>
+        </is>
+      </c>
+      <c r="P473" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q473" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/gr00t17-lerobot-libero_10-640)</t>
+        </is>
+      </c>
+      <c r="R473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>gr00t17-lerobot-libero_object-640</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr"/>
+      <c r="C474" t="inlineStr"/>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr"/>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/gr00t17-lerobot-libero_object-640</t>
+        </is>
+      </c>
+      <c r="L474" t="inlineStr">
+        <is>
+          <t>HuggingFace robotics</t>
+        </is>
+      </c>
+      <c r="M474" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="N474" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="O474" t="inlineStr">
+        <is>
+          <t>2026-07-06 02:02</t>
+        </is>
+      </c>
+      <c r="P474" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q474" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/gr00t17-lerobot-libero_object-640)</t>
+        </is>
+      </c>
+      <c r="R474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>gr00t17-lerobot-libero_spatial-640</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr"/>
+      <c r="C475" t="inlineStr"/>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr"/>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/gr00t17-lerobot-libero_spatial-640</t>
+        </is>
+      </c>
+      <c r="L475" t="inlineStr">
+        <is>
+          <t>HuggingFace robotics</t>
+        </is>
+      </c>
+      <c r="M475" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="N475" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="O475" t="inlineStr">
+        <is>
+          <t>2026-07-06 02:02</t>
+        </is>
+      </c>
+      <c r="P475" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q475" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/gr00t17-lerobot-libero_spatial-640)</t>
+        </is>
+      </c>
+      <c r="R475" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R475"/>
+  <dimension ref="A1:R476"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28547,6 +28547,78 @@
       </c>
       <c r="R475" t="inlineStr"/>
     </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>CWIP-1.0</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr"/>
+      <c r="C476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr"/>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/CWIP-1.0</t>
+        </is>
+      </c>
+      <c r="L476" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M476" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="N476" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="O476" t="inlineStr">
+        <is>
+          <t>2026-07-08 01:27</t>
+        </is>
+      </c>
+      <c r="P476" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q476" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/CWIP-1.0)</t>
+        </is>
+      </c>
+      <c r="R476" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R476"/>
+  <dimension ref="A1:R477"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28619,6 +28619,78 @@
       </c>
       <c r="R476" t="inlineStr"/>
     </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>nvDock</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr"/>
+      <c r="C477" t="inlineStr"/>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr"/>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/nvDock</t>
+        </is>
+      </c>
+      <c r="L477" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M477" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="N477" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="O477" t="inlineStr">
+        <is>
+          <t>2026-07-09 01:49</t>
+        </is>
+      </c>
+      <c r="P477" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q477" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/nvDock)</t>
+        </is>
+      </c>
+      <c r="R477" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R477"/>
+  <dimension ref="A1:R480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28691,6 +28691,234 @@
       </c>
       <c r="R477" t="inlineStr"/>
     </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Nemotron-3-Embed-1B-NVFP4</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr"/>
+      <c r="C478" t="inlineStr"/>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/Nemotron-3-Embed-1B-NVFP4</t>
+        </is>
+      </c>
+      <c r="L478" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M478" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="N478" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="O478" t="inlineStr">
+        <is>
+          <t>2026-07-15 01:16</t>
+        </is>
+      </c>
+      <c r="P478" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q478" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/Nemotron-3-Embed-1B-NVFP4)</t>
+        </is>
+      </c>
+      <c r="R478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Nemotron-3-Embed-8B-BF16</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr"/>
+      <c r="C479" t="inlineStr"/>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>8B</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/Nemotron-3-Embed-8B-BF16</t>
+        </is>
+      </c>
+      <c r="L479" t="inlineStr">
+        <is>
+          <t>HuggingFace sentence-similarity</t>
+        </is>
+      </c>
+      <c r="M479" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="N479" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="O479" t="inlineStr">
+        <is>
+          <t>2026-07-15 01:16</t>
+        </is>
+      </c>
+      <c r="P479" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q479" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/Nemotron-3-Embed-8B-BF16)</t>
+        </is>
+      </c>
+      <c r="R479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Nemotron-3-Embed-1B-BF16</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr"/>
+      <c r="C480" t="inlineStr"/>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>1B</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/Nemotron-3-Embed-1B-BF16</t>
+        </is>
+      </c>
+      <c r="L480" t="inlineStr">
+        <is>
+          <t>HuggingFace sentence-similarity</t>
+        </is>
+      </c>
+      <c r="M480" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="N480" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="O480" t="inlineStr">
+        <is>
+          <t>2026-07-15 01:16</t>
+        </is>
+      </c>
+      <c r="P480" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q480" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/Nemotron-3-Embed-1B-BF16)</t>
+        </is>
+      </c>
+      <c r="R480" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R480"/>
+  <dimension ref="A1:R482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28919,6 +28919,158 @@
       </c>
       <c r="R480" t="inlineStr"/>
     </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>bitnet-embedding-0.6b</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr"/>
+      <c r="C481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>微软</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>0.6B</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/microsoft/bitnet-embedding-0.6b</t>
+        </is>
+      </c>
+      <c r="L481" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M481" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="N481" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O481" t="inlineStr">
+        <is>
+          <t>2026-07-16 01:26</t>
+        </is>
+      </c>
+      <c r="P481" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q481" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/bitnet-embedding-0.6b)</t>
+        </is>
+      </c>
+      <c r="R481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>bitnet-embedding-270m</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr"/>
+      <c r="C482" t="inlineStr"/>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>微软</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>270M</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/microsoft/bitnet-embedding-270m</t>
+        </is>
+      </c>
+      <c r="L482" t="inlineStr">
+        <is>
+          <t>HuggingFace</t>
+        </is>
+      </c>
+      <c r="M482" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="N482" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="O482" t="inlineStr">
+        <is>
+          <t>2026-07-16 01:26</t>
+        </is>
+      </c>
+      <c r="P482" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q482" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/bitnet-embedding-270m)</t>
+        </is>
+      </c>
+      <c r="R482" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R482"/>
+  <dimension ref="A1:R485"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29071,6 +29071,234 @@
       </c>
       <c r="R482" t="inlineStr"/>
     </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash Cyber</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr"/>
+      <c r="C483" t="inlineStr"/>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr"/>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/gemini-3.5-flash-cyber</t>
+        </is>
+      </c>
+      <c r="L483" t="inlineStr">
+        <is>
+          <t>针对网络安全用途；协助发现、验证及修补软件漏洞；仅向政府及受信任合作伙伴开放</t>
+        </is>
+      </c>
+      <c r="M483" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="N483" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="O483" t="inlineStr">
+        <is>
+          <t>2026-07-22 01:25</t>
+        </is>
+      </c>
+      <c r="P483" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q483" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜</t>
+        </is>
+      </c>
+      <c r="R483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Gemini 3.5 Flash-Lite</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr"/>
+      <c r="C484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr"/>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/gemini-3.5-flash-lite</t>
+        </is>
+      </c>
+      <c r="L484" t="inlineStr">
+        <is>
+          <t>1048k上下文</t>
+        </is>
+      </c>
+      <c r="M484" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="N484" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="O484" t="inlineStr">
+        <is>
+          <t>2026-07-22 01:25</t>
+        </is>
+      </c>
+      <c r="P484" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q484" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜</t>
+        </is>
+      </c>
+      <c r="R484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>Gemini 3.6 Flash</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr"/>
+      <c r="C485" t="inlineStr"/>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr"/>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/gemini-3.6-flash</t>
+        </is>
+      </c>
+      <c r="L485" t="inlineStr">
+        <is>
+          <t>1048k上下文</t>
+        </is>
+      </c>
+      <c r="M485" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="N485" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="O485" t="inlineStr">
+        <is>
+          <t>2026-07-22 01:25</t>
+        </is>
+      </c>
+      <c r="P485" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q485" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜</t>
+        </is>
+      </c>
+      <c r="R485" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R485"/>
+  <dimension ref="A1:R487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29299,6 +29299,154 @@
       </c>
       <c r="R485" t="inlineStr"/>
     </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Claude Opus 5</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr"/>
+      <c r="C486" t="inlineStr"/>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Anthropic</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr"/>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/claude-opus-5</t>
+        </is>
+      </c>
+      <c r="L486" t="inlineStr">
+        <is>
+          <t>1000k上下文；高端定价</t>
+        </is>
+      </c>
+      <c r="M486" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="N486" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="O486" t="inlineStr">
+        <is>
+          <t>2026-07-25 01:29</t>
+        </is>
+      </c>
+      <c r="P486" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q486" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜</t>
+        </is>
+      </c>
+      <c r="R486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>VibeVoice-ASR-BitNet</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr"/>
+      <c r="C487" t="inlineStr"/>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>微软</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr"/>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>语音</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/microsoft/VibeVoice-ASR-BitNet</t>
+        </is>
+      </c>
+      <c r="L487" t="inlineStr">
+        <is>
+          <t>HuggingFace automatic-speech-recognition</t>
+        </is>
+      </c>
+      <c r="M487" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="N487" t="inlineStr">
+        <is>
+          <t>2026-07-25</t>
+        </is>
+      </c>
+      <c r="O487" t="inlineStr">
+        <is>
+          <t>2026-07-25 01:29</t>
+        </is>
+      </c>
+      <c r="P487" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q487" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/VibeVoice-ASR-BitNet)</t>
+        </is>
+      </c>
+      <c r="R487" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R487"/>
+  <dimension ref="A1:R488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29447,6 +29447,78 @@
       </c>
       <c r="R487" t="inlineStr"/>
     </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Mage-ViT</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr"/>
+      <c r="C488" t="inlineStr"/>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>微软</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr"/>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/microsoft/Mage-ViT</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>HuggingFace image-feature-extraction</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>2026-07-27 01:50</t>
+        </is>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(微软/Mage-ViT)</t>
+        </is>
+      </c>
+      <c r="R488" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R488"/>
+  <dimension ref="A1:R491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29519,6 +29519,234 @@
       </c>
       <c r="R488" t="inlineStr"/>
     </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>K-EXAONE-2.0-750B-A37B-DSpark</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr"/>
+      <c r="C489" t="inlineStr"/>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>750B(A37B)</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/LGAI-EXAONE/K-EXAONE-2.0-750B-A37B-DSpark</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:45</t>
+        </is>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(lg/K-EXAONE-2.0-750B-A37B-DSpark)</t>
+        </is>
+      </c>
+      <c r="R489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>K-EXAONE-2.0-750B-A37B-NVFP4</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr"/>
+      <c r="C490" t="inlineStr"/>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>750B(A37B)</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/LGAI-EXAONE/K-EXAONE-2.0-750B-A37B-NVFP4</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:45</t>
+        </is>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(lg/K-EXAONE-2.0-750B-A37B-NVFP4)</t>
+        </is>
+      </c>
+      <c r="R490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>K-EXAONE-2.0-750B-A37B-FP8</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr"/>
+      <c r="C491" t="inlineStr"/>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>750B(A37B)</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>未知</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/LGAI-EXAONE/K-EXAONE-2.0-750B-A37B-FP8</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>2026-07-31 01:45</t>
+        </is>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(lg/K-EXAONE-2.0-750B-A37B-FP8)</t>
+        </is>
+      </c>
+      <c r="R491" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R491"/>
+  <dimension ref="A1:R492"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29747,6 +29747,78 @@
       </c>
       <c r="R491" t="inlineStr"/>
     </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>DeepSeek-V4-Flash-0731</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr"/>
+      <c r="C492" t="inlineStr"/>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>深度求索</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr"/>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/deepseek-ai/DeepSeek-V4-Flash-0731</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>2026-08-01 01:46</t>
+        </is>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(深度求索/DeepSeek-V4-Flash-0731)</t>
+        </is>
+      </c>
+      <c r="R492" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R492"/>
+  <dimension ref="A1:R493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29819,6 +29819,86 @@
       </c>
       <c r="R492" t="inlineStr"/>
     </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Nemotron 3.5 Lightning (30B A3B)</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr"/>
+      <c r="C493" t="inlineStr"/>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>30B</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/nemotron-3.5-lightning-30b-a3b</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>MoE架构；30B参数；262k上下文；低成本；Openmdw</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>2026-08-12 00:58</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜 · HuggingFace 需登录(nvidia/Nemotron 3.5 Lightning (30B A3B))</t>
+        </is>
+      </c>
+      <c r="R493" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R493"/>
+  <dimension ref="A1:R495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29899,6 +29899,162 @@
       </c>
       <c r="R493" t="inlineStr"/>
     </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Grok 4.6</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr"/>
+      <c r="C494" t="inlineStr"/>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>xAI</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr"/>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/grok-4.6</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>500k上下文</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>2026-08-13 01:00</t>
+        </is>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜</t>
+        </is>
+      </c>
+      <c r="R494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>LFM2.5-VL-3B</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr"/>
+      <c r="C495" t="inlineStr"/>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Liquid AI</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>3B</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>non-thinking</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/lfm-2.5-vl-3b</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>Lfm1 0</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>2026-08-13 01:00</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜 · HuggingFace 需登录(liquid-ai/LFM2.5-VL-3B)</t>
+        </is>
+      </c>
+      <c r="R495" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R495"/>
+  <dimension ref="A1:R497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30055,6 +30055,162 @@
       </c>
       <c r="R495" t="inlineStr"/>
     </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>DeepSeek-V4-Pro-0813</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr"/>
+      <c r="C496" t="inlineStr"/>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>2T</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/deepseek-v4-pro-0813</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>MoE架构；2T参数；1048k上下文；MIT</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>2026-08-14 00:59</t>
+        </is>
+      </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q496" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜 · HuggingFace 需登录(deepseek/DeepSeek-V4-Pro-0813)</t>
+        </is>
+      </c>
+      <c r="R496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Gemini 3.7 Flash</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr"/>
+      <c r="C497" t="inlineStr"/>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr"/>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/gemini-3.7-flash</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>1048k上下文</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>2026-08-14 00:59</t>
+        </is>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜</t>
+        </is>
+      </c>
+      <c r="R497" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R497"/>
+  <dimension ref="A1:R504"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30211,6 +30211,526 @@
       </c>
       <c r="R497" t="inlineStr"/>
     </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Qwen3.8-27B</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr"/>
+      <c r="C498" t="inlineStr"/>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Alibaba Cloud / Qwen Team</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>28B</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/qwen3.8-27b</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>强推理能力；Apache 2.0</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:34</t>
+        </is>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜 · HuggingFace 需登录(alibaba-cloud-/Qwen3.8-27B)</t>
+        </is>
+      </c>
+      <c r="R498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>GLM-5.3</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr"/>
+      <c r="C499" t="inlineStr"/>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Zhipu AI</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>753B</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/glm-5.3</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>MoE架构；753B参数；Unknown</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:34</t>
+        </is>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜</t>
+        </is>
+      </c>
+      <c r="R499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>NVIDIA-Nemotron-Labs-Teacher-Chat</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr"/>
+      <c r="C500" t="inlineStr"/>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr"/>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/NVIDIA-Nemotron-Labs-Teacher-Chat</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:34</t>
+        </is>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NVIDIA-Nemotron-Labs-Teacher-Chat)</t>
+        </is>
+      </c>
+      <c r="R500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>NVIDIA-Nemotron-Labs-Teacher-Competition-Coding</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr"/>
+      <c r="C501" t="inlineStr"/>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr"/>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/NVIDIA-Nemotron-Labs-Teacher-Competition-Coding</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:34</t>
+        </is>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NVIDIA-Nemotron-Labs-Teacher-Competition-Coding)</t>
+        </is>
+      </c>
+      <c r="R501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>NVIDIA-Nemotron-Labs-Teacher-Instruction-Following</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr"/>
+      <c r="C502" t="inlineStr"/>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr"/>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/NVIDIA-Nemotron-Labs-Teacher-Instruction-Following</t>
+        </is>
+      </c>
+      <c r="L502" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:34</t>
+        </is>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NVIDIA-Nemotron-Labs-Teacher-Instruction-Following)</t>
+        </is>
+      </c>
+      <c r="R502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>NVIDIA-Nemotron-Labs-Teacher-General-Reasoning</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr"/>
+      <c r="C503" t="inlineStr"/>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr"/>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/NVIDIA-Nemotron-Labs-Teacher-General-Reasoning</t>
+        </is>
+      </c>
+      <c r="L503" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:34</t>
+        </is>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NVIDIA-Nemotron-Labs-Teacher-General-Reasoning)</t>
+        </is>
+      </c>
+      <c r="R503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>NVIDIA-Nemotron-Labs-Teacher-STEM</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr"/>
+      <c r="C504" t="inlineStr"/>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>英伟达</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>国外</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>开源</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr"/>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>基座</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>https://huggingface.co/nvidia/NVIDIA-Nemotron-Labs-Teacher-STEM</t>
+        </is>
+      </c>
+      <c r="L504" t="inlineStr">
+        <is>
+          <t>HuggingFace text-generation</t>
+        </is>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>2026-08-15 00:34</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> · HuggingFace 需登录(英伟达/NVIDIA-Nemotron-Labs-Teacher-STEM)</t>
+        </is>
+      </c>
+      <c r="R504" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Model_Navigate/data/Object-Models.xlsx
+++ b/Model_Navigate/data/Object-Models.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R504"/>
+  <dimension ref="A1:R505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30731,6 +30731,82 @@
       </c>
       <c r="R504" t="inlineStr"/>
     </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>DeepSeek-V4-Flash-Vision-Exp</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr"/>
+      <c r="C505" t="inlineStr"/>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>国内</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>闭源</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr"/>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>多模态</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>thinking</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>通用对话</t>
+        </is>
+      </c>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>https://llm-stats.com/models/deepseek-v4-flash-vision-exp</t>
+        </is>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>1048k上下文；低成本；Unknown</t>
+        </is>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>2026-08-22 00:34</t>
+        </is>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>llm-stats.com 排行榜</t>
+        </is>
+      </c>
+      <c r="R505" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
